--- a/database_penyimpanan_aman/database_master_referensi.xlsx
+++ b/database_penyimpanan_aman/database_master_referensi.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,7 +473,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-16 19:57:17</t>
+          <t>2026-08-21 15:40:13</t>
         </is>
       </c>
     </row>
@@ -502,7 +502,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-16 19:45:26</t>
+          <t>2026-08-21 15:40:13</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-16 19:46:17</t>
+          <t>2026-08-21 15:40:13</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-16 19:46:56</t>
+          <t>2026-08-21 15:40:13</t>
         </is>
       </c>
     </row>
@@ -589,7 +589,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-16 19:47:53</t>
+          <t>2026-08-21 15:40:13</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-16 19:51:20</t>
+          <t>2026-08-21 15:40:13</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-16 19:58:23</t>
+          <t>2026-08-21 15:40:13</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-16 19:59:11</t>
+          <t>2026-08-21 15:40:13</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-16 20:00:20</t>
+          <t>2026-08-21 15:40:13</t>
         </is>
       </c>
     </row>
@@ -734,7 +734,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-16 20:01:11</t>
+          <t>2026-08-21 15:40:13</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-16 20:01:49</t>
+          <t>2026-08-21 15:40:13</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-16 20:02:46</t>
+          <t>2026-08-21 15:40:13</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-16 20:03:56</t>
+          <t>2026-08-21 15:40:13</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-16 20:04:35</t>
+          <t>2026-08-21 15:40:13</t>
         </is>
       </c>
     </row>
@@ -879,7 +879,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-16 20:04:39</t>
+          <t>2026-08-21 15:40:13</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-16 20:05:44</t>
+          <t>2026-08-21 15:40:13</t>
         </is>
       </c>
     </row>
@@ -937,7 +937,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-16 20:07:26</t>
+          <t>2026-08-21 15:40:13</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-16 20:08:41</t>
+          <t>2026-08-21 15:40:13</t>
         </is>
       </c>
     </row>
@@ -995,15 +995,13 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-16 20:09:33</t>
+          <t>2026-08-21 15:40:13</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>7207250142</t>
-        </is>
+      <c r="A21" t="n">
+        <v>7207250142</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1026,7 +1024,64 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-16 20:10:25</t>
+          <t>2026-08-21 15:40:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>7203250036</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>MONTHLY BASIS</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Daily Rate
+</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1197000</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-08-21 15:40:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>7203250036</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>MONTHLY BASIS</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Standby Rate</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Ls</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>598500</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-08-21 15:40:13</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_master_referensi.xlsx
+++ b/database_penyimpanan_aman/database_master_referensi.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,7 +473,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-21 15:40:13</t>
+          <t>2026-08-22 18:17:40</t>
         </is>
       </c>
     </row>
@@ -502,7 +502,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-21 15:40:13</t>
+          <t>2026-08-22 18:17:40</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:40:13</t>
+          <t>2026-08-22 18:17:40</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-21 15:40:13</t>
+          <t>2026-08-22 18:17:40</t>
         </is>
       </c>
     </row>
@@ -589,7 +589,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-21 15:40:13</t>
+          <t>2026-08-22 18:17:40</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-21 15:40:13</t>
+          <t>2026-08-22 18:17:40</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-21 15:40:13</t>
+          <t>2026-08-22 18:17:40</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-21 15:40:13</t>
+          <t>2026-08-22 18:17:40</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-21 15:40:13</t>
+          <t>2026-08-22 18:17:40</t>
         </is>
       </c>
     </row>
@@ -734,7 +734,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:40:13</t>
+          <t>2026-08-22 18:17:40</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-21 15:40:13</t>
+          <t>2026-08-22 18:17:40</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-21 15:40:13</t>
+          <t>2026-08-22 18:17:40</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-21 15:40:13</t>
+          <t>2026-08-22 18:17:40</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-21 15:40:13</t>
+          <t>2026-08-22 18:17:40</t>
         </is>
       </c>
     </row>
@@ -879,7 +879,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-21 15:40:13</t>
+          <t>2026-08-22 18:17:40</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-21 15:40:13</t>
+          <t>2026-08-22 18:17:40</t>
         </is>
       </c>
     </row>
@@ -937,7 +937,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-21 15:40:13</t>
+          <t>2026-08-22 18:17:40</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-21 15:40:13</t>
+          <t>2026-08-22 18:17:40</t>
         </is>
       </c>
     </row>
@@ -995,7 +995,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-21 15:40:13</t>
+          <t>2026-08-22 18:17:40</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-21 15:40:13</t>
+          <t>2026-08-22 18:17:40</t>
         </is>
       </c>
     </row>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-21 15:40:13</t>
+          <t>2026-08-22 18:17:40</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,241 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-21 15:40:13</t>
+          <t>2026-08-22 18:17:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>SAFETY EQUIPMENT</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PPE - Safety rubber boot
+</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-08-22 18:17:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>SAFETY EQUIPMENT</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PPE - Safety boot
+</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>850000</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-08-22 18:17:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>SAFETY EQUIPMENT</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PPE - Safety helmet
+</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-08-22 18:17:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>SAFETY EQUIPMENT</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PPE - Safety helmet, white, full brim
+</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>750000</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-08-22 18:17:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>SAFETY EQUIPMENT</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PPE - Safety glasses
+</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>200000</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-08-22 18:17:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>SAFETY EQUIPMENT</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PPE - PVC Cotton hand glove
+</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100000</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-08-22 18:17:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>SAFETY EQUIPMENT</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PPE - PVC Dotted Hand Gloves
+</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>150000</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-08-22 18:17:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>SAFETY EQUIPMENT</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ear Plug, Reusable 
+</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-08-22 18:17:40</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_master_referensi.xlsx
+++ b/database_penyimpanan_aman/database_master_referensi.xlsx
@@ -8,19 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\98 PROFORMA INVOICE\Dashboard Proforma Invoice General Services\database_penyimpanan_aman\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CD4B2F6-26C7-485B-ADE8-E1746C1AE0F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB760097-6717-4C83-B237-1D09D2F0333F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$453</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1815" uniqueCount="472">
   <si>
     <t>Nomor Kontrak</t>
   </si>
@@ -50,7 +53,7 @@
     <t>Month</t>
   </si>
   <si>
-    <t>2026-08-22 20:09:31</t>
+    <t>2026-08-23 12:36:06</t>
   </si>
   <si>
     <t xml:space="preserve">Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Man Lift Capacity 227 Kg
@@ -718,10 +721,1156 @@
 </t>
   </si>
   <si>
+    <t xml:space="preserve">trailer 40" atau tronton 15 ton, call out, Cluster Senoro 2 - Tankian Jetty atau sebaliknya c/w BBM &amp; driver
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trailer 40" atau tronton 15 ton, call out, Cluster Senoro 2 - CPP Senoro atau sebaliknya c/w BBM &amp; driver
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trailer 40" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 3 atau sebaliknya c/w BBM &amp; driver
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trailer 40" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 4 atau sebaliknya c/w BBM &amp; driver
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trailer 40" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 5 atau sebaliknya c/w BBM &amp; driver
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trailer 40" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trailer 40" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster B atau sebaliknya c/w BBM &amp; driver
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trailer 40" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Cendanapura 1 atau sebaliknya c/w BBM &amp; driver
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trailer 40" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Cendanapura 2 atau sebaliknya c/w BBM &amp; driver
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trailer 40" atau tronton 15 ton, call out, Cluster Senoro 3 - Contractor's alternative jetty atau sebaliknya c/w BBM &amp; driver
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trailer 40" atau tronton 15 ton, call out, Cluster Senoro 3 - Tankian Jetty atau sebaliknya c/w BBM &amp; driver
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ttrailer 40" atau tronton 15 ton, call out, Cluster Senoro 3 - CPP Senoro atau sebaliknya c/w BBM &amp; driver
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trailer 40" atau tronton 15 ton, call out, Cluster Senoro 3 - Cluster Senoro 4 atau sebaliknya c/w BBM &amp; driver
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trailer 40" atau tronton 15 ton, call out, Cluster Senoro 3 - Cluster Senoro 5 atau sebaliknya c/w BBM &amp; driver
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trailer 40" atau tronton 15 ton, call out, Cluster Senoro 3 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trailer 40" atau tronton 15 ton, call out, Cluster Senoro 3 - Cluster B atau sebaliknya c/w BBM &amp; driver
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trailer 40" atau tronton 15 ton, call out, Cluster Senoro 3 - Cluster Cendanapura 1 atau sebaliknya c/w BBM &amp; driver
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trailer 40" atau tronton 15 ton, call out, Cluster Senoro 3 - Cluster Cendanapura 2 atau sebaliknya c/w BBM &amp; driver
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trailer 40" atau tronton 15 ton, call out, Cluster Senoro 4 - Contractor's alternative jetty atau sebaliknya c/w BBM &amp; driver
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trailer 40" atau tronton 15 ton, call out, Cluster Senoro 4 - Tankian Jetty atau sebaliknya c/w BBM &amp; driver
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trailer 40" atau tronton 15 ton, call out, Cluster Senoro 4 - CPP Senoro atau sebaliknya c/w BBM &amp; driver
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trailer 40" atau tronton 15 ton, call out, Cluster Senoro 4 - Cluster Senoro 5 atau sebaliknya c/w BBM &amp; driver
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trailer 40" atau tronton 15 ton, call out, Cluster Senoro 4 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trailer 40" atau tronton 15 ton, call out, Cluster Senoro 4 - Cluster B atau sebaliknya c/w BBM &amp; driver
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trailer 40" atau tronton 15 ton, call out, Cluster Senoro 4 - Cluster Cendanapura 1 atau sebaliknya c/w BBM &amp; driver
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trailer 40" atau tronton 15 ton, call out, Cluster Senoro 4 - Cluster Cendanapura 2 atau sebaliknya c/w BBM &amp; driver
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trailer 40" atau tronton 15 ton, call out, Cluster Senoro 5 - Contractor's alternative jetty atau sebaliknya c/w BBM &amp; driver
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trailer 40" atau tronton 15 ton, call out, Cluster Senoro 5 - Tankian Jetty atau sebaliknya c/w BBM &amp; driver
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trailer 40" atau tronton 15 ton, call out, Cluster Senoro 5 - CPP Senoro atau sebaliknya c/w BBM &amp; driver
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trailer 40" atau tronton 15 ton, call out, Cluster Senoro 5 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trailer 40" atau tronton 15 ton, call out, Cluster Senoro 5 - Cluster B atau sebaliknya c/w BBM &amp; driver
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trailer 40" atau tronton 15 ton, call out, Cluster Senoro 5 - Cluster Cendanapura 1 atau sebaliknya c/w BBM &amp; driver
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trailer 40" atau tronton 15 ton, call out, Cluster Senoro 5 - Cluster Cendanapura 2 atau sebaliknya c/w BBM &amp; driver
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Contractor's alternative jetty atau sebaliknya c/w BBM &amp; driver
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Tankian Jetty atau sebaliknya c/w BBM &amp; driver
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - CPP Senoro atau sebaliknya c/w BBM &amp; driver
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster Cendanapura 1 atau sebaliknya c/w BBM &amp; driver
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster Cendanapura 2 atau sebaliknya c/w BBM &amp; driver
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trailer 40" atau tronton 15 ton, call out, Cluster B - Contractor's alternative jetty atau sebaliknya c/w BBM &amp; driver
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trailer 40" atau tronton 15 ton, call out, Cluster B - Tankian Jetty atau sebaliknya c/w BBM &amp; driver
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trailer 40" atau tronton 15 ton, call out, Cluster B - CPP Senoro atau sebaliknya c/w BBM &amp; driver
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trailer 40" atau tronton 15 ton, call out, Cluster B - Cluster Cendanapura 1 atau sebaliknya c/w BBM &amp; driver
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trailer 40" atau tronton 15 ton, call out, Cluster B - Cluster Cendanapura 2 atau sebaliknya c/w BBM &amp; driver
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trailer 40" atau tronton 15 ton, call out, Cluster Cendanapura 1 - Contractor's alternative jetty atau sebaliknya c/w BBM &amp; driver
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trailer 40" atau tronton 15 ton, call out, Cluster Cendanapura 1 - Tankian Jetty atau sebaliknya c/w BBM &amp; driver
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trailer 40" atau tronton 15 ton, call out, Cluster Cendanapura 1 - CPP Senoro atau sebaliknya c/w BBM &amp; driver
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trailer 40" atau tronton 15 ton, call out, Cluster Cendanapura 1 - Cluster Cendanapura 2 atau sebaliknya c/w BBM &amp; driver
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trailer 40" atau tronton 15 ton, call out, Cluster Cendanapura 2 - Contractor's alternative jetty atau sebaliknya c/w BBM &amp; driver
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trailer 40" atau tronton 15 ton, call out, Cluster Cendanapura 2 - Tankian Jetty atau sebaliknya c/w BBM &amp; driver
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trailer 40" atau tronton 15 ton, call out, Cluster Cendanapura 2 - CPP Senoro atau sebaliknya c/w BBM &amp; driver
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trailer 40" atau tronton 15 ton, call out, Contractor's alternative jetty - Tankian Jetty atau sebaliknya c/w BBM &amp; driver
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trailer 40" atau tronton 15 ton, call out, Contractor's alternative jetty - CPP Senoro atau sebaliknya c/w BBM &amp; driver
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trailer 40" atau tronton 15 ton, call out, Tankian Jetty - CPP Senoro atau sebaliknya c/w BBM &amp; driver
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PBM Luwuk atau Tangkiang (Barang Berbahaya/Barang Khusus), termasuk crane, buruh, administrasi pelabuhan, jasa dermaga , ea = ton/m3
+</t>
+  </si>
+  <si>
+    <t>Ton/M3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PBM Luwuk atau Tangkiang (Barang Standard), termasuk crane, buruh, administrasi pelabuhan, jasa dermaga, ea = ton/m3
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alternative Jetty Facilities (alternatif jetty sesuai propose Kontraktor untuk bongkar muat)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bongkar - muat di lokasi jetty alternatif, termasuk  lifting equipment, crew bongkar muat , ea = ton/m3
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bongkar - muat di lokasi jetty alternatif, termasuk  lifting equipment, crew bongkar muat , ea = ton/m3
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bongkar - muat equipment dijetty alternative barang yang bergerak sendiri , ea = ton/m3
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jasa sewa Open Yard di Jetty Alternative untuk Staging Area (minimun Ukuran 15x15 M2)/day
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jasa sewa CloseYard di Jetty Alternative untuk Staging Area (minimun Ukuran 15x15 M2)/day
+</t>
+  </si>
+  <si>
+    <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobilisasi/ Demobilisasi crane min 70 ton to/from Company Wellsite/ Contractor base
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobilisasi/ Demobilisasi crane min 50 ton to/from Company Wellsite/ Contractor base
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobilisasi/ Demobilisasi Rental Equipment (forklift-loader / excavator/ Vibrator Roller/ Motor Grader/ TMC. Etc) to/from Company Wellsite/ Contractor base
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">crane min 70 ton, call out, (hanya unit)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">crane min 50 ton, call out, (hanya unit)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">forklift-loader cap min 5 Ton, call out, (hanya unit)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">excavator 80-140 HP, call out, (hanya unit)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tronton Flatbed 15 ton, call out (Senoro), c/w winch + operator
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vibrator Roller 5-8 T, call out, (hanya unit)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Motor-Grader, call out, (hanya unit)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fire Jeep Type M,4WD,Call Out, Cap min: Water Tender up to 500L, premix foam up to 500 L, Dry Powder up to 400 Kg, c/w operators, (hanya unit)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vacuum Truck , Call out, Cap  5000 ltr c/w vacuum pump &amp; acessories, call out, (hanya unit)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hiboy Trailer 40 Ft, Call Out, c/w operator
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Light / Medium truck 8T, Call Out, c/w operators
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Truck mounted crane,minimum capacity 5 Ton
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genset, cap min 40 KVA, silent type, include maintenance
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genset, cap min 80 KVA, silent type, include maintenance
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portable Air Compressor
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fuel Tank cap 20 KL c/w transfer pump, hose, flow meter, and connection
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Survey verticality, include surveyor, transport PP, dan equipment
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Penyambungan HDPE/ terpaulin, include personel, transport PP, dan equipment
+</t>
+  </si>
+  <si>
+    <t>PENGADAAN MATERIAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee, 
+</t>
+  </si>
+  <si>
+    <t>Ltr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Besi Plat 3 mm (240 x 120 cm), 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Besi Plat 2 mm,
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cat Besi, 5kg
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cat Kayu, 5kg
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cat Tembok, 5kg
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minyak Tiner
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kawat bronjong galvanis, SNI
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kawat Las, E-6010/ E-6011 (5 kg)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kawat Las - E-6012 (5kg)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kawat Las - E-6013 (5kg)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kawat Las - E-7024 (5kg)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kawat Las - LB52U/E7018 (5kg)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kayu Balok, 6x12x400  Kayu kelas 1
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kayu Balok, 5x10x400 Kayu kelas 1
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kayu Balok, 6x12x400  Kayu kelas 2
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kayu Balok, 6x12x400  Kayu kelas 2
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kayu Reng 2x3x400 Kayu kelas 1
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kayu Kaso/lata, 4x6x400 Kayu kelas 1
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kayu Kaso/lata, 5x5x400 Kayu kelas 1
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kayu Reng 2x3x400 Kayu kelas 2
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kayu Kaso/lata, 4x6x400 Kayu kelas 2
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kayu Kaso/lata, 5x5x400 Kayu kelas 2
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kayu Papan, 2x20x400 Kayu kelas 1
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kayu Papan, 3x20x400 Kayu kelas 1
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kayu Papan, 2x20x400 Kayu kelas 2
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kayu Papan, 3x20x400 Kayu kelas 2
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kuas 2"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kuas 3"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pipa Besi 1,5"x2mmx 6meter, 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pipa Besi 2"x2mmx6 meter, 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pipa Besi 2"x2mmx6 meter, Pipa Galvanis ukuran 1"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pipa PVC AW 2"  (4m)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pipa PVC AW 1/2" (4m)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pipa PVC AW 3/4" (4m)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pipa PVC AW 1" (4m) 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pipa PVC AW 4" (4m) 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pipa PVC AW 6" (4m) 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pipa PVC AW 3" 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pipa PVC AW 1 1/2" 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Knee PVC 2" 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Knee PVC 1/2" 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Knee PVC 3/4" 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Knee PVC 1" 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Knee PVC 4" 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Knee PVC 6"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Knee PVC 3"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Knee PVC 1 1/2" 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tee  PVC 2" 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tee PVC 1/2" 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tee PVC 3/4" 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tee PVC 1" 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tee PVC 4" 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tee PVC 6"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tee PVC 3"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tee PVC 1 1/2" 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lem pipa PVC
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seal tape
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sock Drat luar PVC 1"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sock Drat luar PVC 1/2"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sock Operan 1" ke 3/4"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sock Operan 1-1/2" - 2"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sock PVC 2"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sock PVC 3/4"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sock PVC 4"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plastik   rope 6 mm
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kran 1/2"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kran 3/4"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stop kran 1/2"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stop kran 3/4"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tawas
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HDPE Geomembrane 0.75mm
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terpaulin A12
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thinner @ 5 Ltr
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasir
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Semen PC 50 kg
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Batu Split 3-5 atau 5-7
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Batu Agregate A
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Batu Agregate B
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sirtu
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Batu Kali
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tanah timbunan
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paku Zeng
+</t>
+  </si>
+  <si>
+    <t>Kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zeng Gelombang BJLS 0.2  
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paku Tripleks
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Batu Bata,
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paving Block
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baja Ringan C75 0.75mm @ 6 meter
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spandex thk. 0.3mm @6m
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bubungan Spandex 0.3mm @3 m
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baut baja ringan
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Besi 10mm SNI
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Besi 13mm SNI
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kawat bendrat
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cangkul
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skop
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sendok adukan
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jarum karung
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tali Rafia rope
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meteran @5m
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pompa air 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Foot valve/klep
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kabel 2x1.5mm NYA/NYM @50m
+</t>
+  </si>
+  <si>
+    <t>Roll</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isolasi kabel 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gembok kunci
+</t>
+  </si>
+  <si>
+    <t>ADDITIONAL CAMP SERVICES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fogging Harga termasuk personil, kebutuhan transportasi dari/ke lokasi pemboran serta PPE personil
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobilization/ Demobilization 20 ft Additional Camp to/from Company Wellsite/ Contractor base
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portacamp - Living camp,ukuran 40FT (4 sleepers)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portacamp - Living camp,ukuran 40FT (8 sleepers)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portacamp - Living camp,  ukuran 20FT (4 sleepers)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portacamp - Dining room, ukuran 20FT
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portacamp - Kitchen ukuran 40FT
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portacamp - Office Camp,  ukuran 40 FT
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Food &amp; beverage, main course 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Food &amp; beverage, snack coffee/ tea &amp; desert
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laundry services
+</t>
+  </si>
+  <si>
+    <t>PERSONEL ON CALL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personnel GS in-charge di lokasi pemboran/ wellservices/ workover, personnel in charge  
+</t>
+  </si>
+  <si>
+    <t>man-days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helper Local (non Skilled)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helper Local (Skilled)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security - Local personnel
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Welder (GTAW)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Welder (SMAW)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Welder (Non Categories)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operator Crane
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rigger
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operator Heavy Equipment (Motor Grader)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operator Heavy Equipment ( Excavator)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operator Heavy Equipment ( Vibro Compactor)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operator Heavy Equipment (Fire Jeep)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operator Heavy Equipment (Vacuum Truck)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operator Heavy Equipment (Forklift)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mechanic/ Electrician
+</t>
+  </si>
+  <si>
+    <t>MOVING AIR FREIGHT TRANSPORT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jabodetabek - Palembang/Lematang atau sebaliknya
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jabodetabek - Luwuk/ Senoro atau sebaliknya
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jabodetabek - Balikpapan atau sebaliknya
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jabodetabek - Batam atau sebaliknya
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Batam - Luwuk/ Senoro atau sebaliknya
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balikpapan - Luwuk/ Senoro atau sebaliknya
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balikpapan - Batam atau sebaliknya
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Surabaya - Luwuk/ Senoro atau sebaliknya
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Surabaya - Balikpapan atau sebaliknya
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Surabaya - Batam atau sebaliknya
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Surabaya - Jabodetabek atau sebaliknya
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jasa repacking for Airfreight, estimasi ukuran pallet 100x100x100 cm
+</t>
+  </si>
+  <si>
+    <t>Pallet</t>
+  </si>
+  <si>
+    <t>MOVING SEA FREIGHT TRANSPORT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jabodetabek - Palembang/Lematang atau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jabodetabek - Luwuk/ Senoro atau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jabodetabek - Balikpapan atau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jabodetabek - Batam atau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jabodetabek - Surabaya atau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Batam - Luwuk/ Senoro atau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balikpapan - Luwuk/ Senoro atau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balikpapan - Batam atau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Surabaya - Luwuk/ Senoro atau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Surabaya - Balikpapanatau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Surabaya - Batam atau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)
+</t>
+  </si>
+  <si>
     <t>7201250141</t>
   </si>
   <si>
-    <t xml:space="preserve">trailer 40" atau tronton 15 ton, call out, Cluster Senoro 2 - Tankian Jetty atau sebaliknya c/w BBM &amp; driver
+    <t xml:space="preserve">Jasa repacking for Seafreight, estimasi ukuran pallet 100x100x100 cm
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aqua 600 ml 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aqua Galon Segel 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indocafe Coffemix Renteng 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kopi Kapal Api 380 g 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nescafe Classic renteng 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gulaku 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hand Soap 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pop Mie 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stella Pengharum Ruangan 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tisu Kering 200 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tisu Basah 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chitato 68 g 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pocari Sweat
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teh Kotak 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Susu Beruang
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fanta
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coca Cola
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coffe Nescafe Kaleng 220 ml 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roti Tawar Sari Roti 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roti Sari Roti Coklat 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roti Sari Roti Keju 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kabel NYM 2x2,5 mm @50 mtr
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balok Beton ukuran 40x40 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pos Sweeper  2x2 meter
+</t>
+  </si>
+  <si>
+    <t>JASA TRANSPORTASI DARI DAN KE BANDARA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jasa transportasi menggunakan Pickup Air Port Cengkareng ke Jabodetabek dan sebaliknya
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jasa transportasi menggunakan Pickup Air Port Balikpapan ke Kota dan sebaliknya
+</t>
+  </si>
+  <si>
+    <t>TRANSPORTASI DARI SURABAYA KE JABODETABEK:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cold Diesel 4 Meter
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cold Diesel Long 6 Meter
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fuso Bak Max 6 ton
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fuso 8 Meter berat Max 10 ton
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wbox Max 15 ton
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tronton Max 7 Meter Max 14 ton
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tronton Max 9,5 meter Max 20 ton
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trailler 20 feet 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trailler 40 feet
 </t>
   </si>
 </sst>
@@ -1062,13 +2211,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F168"/>
+  <dimension ref="A1:F453"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="13" customWidth="1"/>
-    <col min="2" max="2" width="26.53125" customWidth="1"/>
-    <col min="3" max="3" width="23.06640625" customWidth="1"/>
-    <col min="5" max="5" width="21.33203125" customWidth="1"/>
+    <col min="1" max="1" width="21.6640625" customWidth="1"/>
+    <col min="2" max="2" width="21.33203125" customWidth="1"/>
+    <col min="3" max="3" width="46.73046875" customWidth="1"/>
+    <col min="4" max="4" width="21.265625" customWidth="1"/>
+    <col min="5" max="5" width="16.1328125" customWidth="1"/>
+    <col min="6" max="6" width="13.53125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
@@ -2322,7 +3473,7 @@
         <v>78</v>
       </c>
       <c r="D63" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E63">
         <v>1600000</v>
@@ -2339,10 +3490,10 @@
         <v>77</v>
       </c>
       <c r="C64" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D64" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E64">
         <v>1600000</v>
@@ -2356,16 +3507,16 @@
         <v>7201250141</v>
       </c>
       <c r="B65" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C65" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D65" t="s">
         <v>16</v>
       </c>
       <c r="E65">
-        <v>1600000</v>
+        <v>6900000</v>
       </c>
       <c r="F65" t="s">
         <v>9</v>
@@ -2376,16 +3527,16 @@
         <v>7201250141</v>
       </c>
       <c r="B66" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C66" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D66" t="s">
         <v>16</v>
       </c>
       <c r="E66">
-        <v>1600000</v>
+        <v>6900000</v>
       </c>
       <c r="F66" t="s">
         <v>9</v>
@@ -2396,13 +3547,13 @@
         <v>7201250141</v>
       </c>
       <c r="B67" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C67" t="s">
         <v>80</v>
       </c>
       <c r="D67" t="s">
-        <v>16</v>
+        <v>65</v>
       </c>
       <c r="E67">
         <v>6900000</v>
@@ -2419,13 +3570,13 @@
         <v>81</v>
       </c>
       <c r="C68" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D68" t="s">
-        <v>16</v>
+        <v>65</v>
       </c>
       <c r="E68">
-        <v>6900000</v>
+        <v>5290000</v>
       </c>
       <c r="F68" t="s">
         <v>9</v>
@@ -2439,13 +3590,13 @@
         <v>81</v>
       </c>
       <c r="C69" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D69" t="s">
         <v>65</v>
       </c>
       <c r="E69">
-        <v>6900000</v>
+        <v>5750000</v>
       </c>
       <c r="F69" t="s">
         <v>9</v>
@@ -2459,13 +3610,13 @@
         <v>81</v>
       </c>
       <c r="C70" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D70" t="s">
         <v>65</v>
       </c>
       <c r="E70">
-        <v>5290000</v>
+        <v>7000000</v>
       </c>
       <c r="F70" t="s">
         <v>9</v>
@@ -2479,13 +3630,13 @@
         <v>81</v>
       </c>
       <c r="C71" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D71" t="s">
         <v>65</v>
       </c>
       <c r="E71">
-        <v>5750000</v>
+        <v>7130000</v>
       </c>
       <c r="F71" t="s">
         <v>9</v>
@@ -2499,13 +3650,13 @@
         <v>81</v>
       </c>
       <c r="C72" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D72" t="s">
         <v>65</v>
       </c>
       <c r="E72">
-        <v>7000000</v>
+        <v>7590000</v>
       </c>
       <c r="F72" t="s">
         <v>9</v>
@@ -2519,13 +3670,13 @@
         <v>81</v>
       </c>
       <c r="C73" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D73" t="s">
         <v>65</v>
       </c>
       <c r="E73">
-        <v>7130000</v>
+        <v>7000000</v>
       </c>
       <c r="F73" t="s">
         <v>9</v>
@@ -2539,13 +3690,13 @@
         <v>81</v>
       </c>
       <c r="C74" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D74" t="s">
         <v>65</v>
       </c>
       <c r="E74">
-        <v>7590000</v>
+        <v>6900000</v>
       </c>
       <c r="F74" t="s">
         <v>9</v>
@@ -2559,7 +3710,7 @@
         <v>81</v>
       </c>
       <c r="C75" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D75" t="s">
         <v>65</v>
@@ -2579,13 +3730,13 @@
         <v>81</v>
       </c>
       <c r="C76" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D76" t="s">
         <v>65</v>
       </c>
       <c r="E76">
-        <v>6900000</v>
+        <v>8250000</v>
       </c>
       <c r="F76" t="s">
         <v>9</v>
@@ -2599,7 +3750,7 @@
         <v>81</v>
       </c>
       <c r="C77" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D77" t="s">
         <v>65</v>
@@ -2619,13 +3770,13 @@
         <v>81</v>
       </c>
       <c r="C78" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D78" t="s">
         <v>65</v>
       </c>
       <c r="E78">
-        <v>8250000</v>
+        <v>7000000</v>
       </c>
       <c r="F78" t="s">
         <v>9</v>
@@ -2639,13 +3790,13 @@
         <v>81</v>
       </c>
       <c r="C79" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D79" t="s">
         <v>65</v>
       </c>
       <c r="E79">
-        <v>7000000</v>
+        <v>5060000</v>
       </c>
       <c r="F79" t="s">
         <v>9</v>
@@ -2659,13 +3810,13 @@
         <v>81</v>
       </c>
       <c r="C80" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D80" t="s">
         <v>65</v>
       </c>
       <c r="E80">
-        <v>7000000</v>
+        <v>5980000</v>
       </c>
       <c r="F80" t="s">
         <v>9</v>
@@ -2679,13 +3830,13 @@
         <v>81</v>
       </c>
       <c r="C81" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D81" t="s">
         <v>65</v>
       </c>
       <c r="E81">
-        <v>5060000</v>
+        <v>5290000</v>
       </c>
       <c r="F81" t="s">
         <v>9</v>
@@ -2699,13 +3850,13 @@
         <v>81</v>
       </c>
       <c r="C82" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D82" t="s">
         <v>65</v>
       </c>
       <c r="E82">
-        <v>5980000</v>
+        <v>5060000</v>
       </c>
       <c r="F82" t="s">
         <v>9</v>
@@ -2719,13 +3870,13 @@
         <v>81</v>
       </c>
       <c r="C83" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D83" t="s">
         <v>65</v>
       </c>
       <c r="E83">
-        <v>5290000</v>
+        <v>5520000</v>
       </c>
       <c r="F83" t="s">
         <v>9</v>
@@ -2736,16 +3887,16 @@
         <v>7201250141</v>
       </c>
       <c r="B84" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C84" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D84" t="s">
         <v>65</v>
       </c>
       <c r="E84">
-        <v>5060000</v>
+        <v>5520000</v>
       </c>
       <c r="F84" t="s">
         <v>9</v>
@@ -2756,16 +3907,16 @@
         <v>7201250141</v>
       </c>
       <c r="B85" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C85" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D85" t="s">
         <v>65</v>
       </c>
       <c r="E85">
-        <v>5520000</v>
+        <v>5060000</v>
       </c>
       <c r="F85" t="s">
         <v>9</v>
@@ -2776,16 +3927,16 @@
         <v>7201250141</v>
       </c>
       <c r="B86" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C86" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D86" t="s">
         <v>65</v>
       </c>
       <c r="E86">
-        <v>5520000</v>
+        <v>5290000</v>
       </c>
       <c r="F86" t="s">
         <v>9</v>
@@ -2796,16 +3947,16 @@
         <v>7201250141</v>
       </c>
       <c r="B87" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C87" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D87" t="s">
         <v>65</v>
       </c>
       <c r="E87">
-        <v>5060000</v>
+        <v>5980000</v>
       </c>
       <c r="F87" t="s">
         <v>9</v>
@@ -2816,16 +3967,16 @@
         <v>7201250141</v>
       </c>
       <c r="B88" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C88" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D88" t="s">
         <v>65</v>
       </c>
       <c r="E88">
-        <v>5290000</v>
+        <v>5980000</v>
       </c>
       <c r="F88" t="s">
         <v>9</v>
@@ -2836,10 +3987,10 @@
         <v>7201250141</v>
       </c>
       <c r="B89" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C89" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D89" t="s">
         <v>65</v>
@@ -2856,16 +4007,16 @@
         <v>7201250141</v>
       </c>
       <c r="B90" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C90" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D90" t="s">
         <v>65</v>
       </c>
       <c r="E90">
-        <v>5980000</v>
+        <v>5520000</v>
       </c>
       <c r="F90" t="s">
         <v>9</v>
@@ -2876,16 +4027,16 @@
         <v>7201250141</v>
       </c>
       <c r="B91" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C91" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D91" t="s">
         <v>65</v>
       </c>
       <c r="E91">
-        <v>5980000</v>
+        <v>6440000</v>
       </c>
       <c r="F91" t="s">
         <v>9</v>
@@ -2896,16 +4047,16 @@
         <v>7201250141</v>
       </c>
       <c r="B92" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C92" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D92" t="s">
         <v>65</v>
       </c>
       <c r="E92">
-        <v>5520000</v>
+        <v>5060000</v>
       </c>
       <c r="F92" t="s">
         <v>9</v>
@@ -2916,16 +4067,16 @@
         <v>7201250141</v>
       </c>
       <c r="B93" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C93" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D93" t="s">
         <v>65</v>
       </c>
       <c r="E93">
-        <v>6440000</v>
+        <v>5060000</v>
       </c>
       <c r="F93" t="s">
         <v>9</v>
@@ -2936,16 +4087,16 @@
         <v>7201250141</v>
       </c>
       <c r="B94" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C94" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D94" t="s">
         <v>65</v>
       </c>
       <c r="E94">
-        <v>5060000</v>
+        <v>5290000</v>
       </c>
       <c r="F94" t="s">
         <v>9</v>
@@ -2956,10 +4107,10 @@
         <v>7201250141</v>
       </c>
       <c r="B95" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C95" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D95" t="s">
         <v>65</v>
@@ -2976,10 +4127,10 @@
         <v>7201250141</v>
       </c>
       <c r="B96" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C96" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D96" t="s">
         <v>65</v>
@@ -2996,16 +4147,16 @@
         <v>7201250141</v>
       </c>
       <c r="B97" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C97" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D97" t="s">
         <v>65</v>
       </c>
       <c r="E97">
-        <v>5060000</v>
+        <v>6440000</v>
       </c>
       <c r="F97" t="s">
         <v>9</v>
@@ -3016,16 +4167,16 @@
         <v>7201250141</v>
       </c>
       <c r="B98" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C98" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D98" t="s">
         <v>65</v>
       </c>
       <c r="E98">
-        <v>5290000</v>
+        <v>5520000</v>
       </c>
       <c r="F98" t="s">
         <v>9</v>
@@ -3036,16 +4187,16 @@
         <v>7201250141</v>
       </c>
       <c r="B99" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C99" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D99" t="s">
         <v>65</v>
       </c>
       <c r="E99">
-        <v>6440000</v>
+        <v>5520000</v>
       </c>
       <c r="F99" t="s">
         <v>9</v>
@@ -3056,10 +4207,10 @@
         <v>7201250141</v>
       </c>
       <c r="B100" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C100" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D100" t="s">
         <v>65</v>
@@ -3076,16 +4227,16 @@
         <v>7201250141</v>
       </c>
       <c r="B101" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C101" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D101" t="s">
         <v>65</v>
       </c>
       <c r="E101">
-        <v>5520000</v>
+        <v>6440000</v>
       </c>
       <c r="F101" t="s">
         <v>9</v>
@@ -3096,16 +4247,16 @@
         <v>7201250141</v>
       </c>
       <c r="B102" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C102" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D102" t="s">
         <v>65</v>
       </c>
       <c r="E102">
-        <v>5520000</v>
+        <v>5290000</v>
       </c>
       <c r="F102" t="s">
         <v>9</v>
@@ -3116,16 +4267,16 @@
         <v>7201250141</v>
       </c>
       <c r="B103" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C103" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D103" t="s">
         <v>65</v>
       </c>
       <c r="E103">
-        <v>6440000</v>
+        <v>5290000</v>
       </c>
       <c r="F103" t="s">
         <v>9</v>
@@ -3136,10 +4287,10 @@
         <v>7201250141</v>
       </c>
       <c r="B104" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C104" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D104" t="s">
         <v>65</v>
@@ -3156,10 +4307,10 @@
         <v>7201250141</v>
       </c>
       <c r="B105" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C105" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D105" t="s">
         <v>65</v>
@@ -3176,10 +4327,10 @@
         <v>7201250141</v>
       </c>
       <c r="B106" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C106" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D106" t="s">
         <v>65</v>
@@ -3196,10 +4347,10 @@
         <v>7201250141</v>
       </c>
       <c r="B107" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C107" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D107" t="s">
         <v>65</v>
@@ -3216,16 +4367,16 @@
         <v>7201250141</v>
       </c>
       <c r="B108" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C108" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D108" t="s">
         <v>65</v>
       </c>
       <c r="E108">
-        <v>5290000</v>
+        <v>5520000</v>
       </c>
       <c r="F108" t="s">
         <v>9</v>
@@ -3236,16 +4387,16 @@
         <v>7201250141</v>
       </c>
       <c r="B109" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C109" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D109" t="s">
         <v>65</v>
       </c>
       <c r="E109">
-        <v>5290000</v>
+        <v>6440000</v>
       </c>
       <c r="F109" t="s">
         <v>9</v>
@@ -3256,16 +4407,16 @@
         <v>7201250141</v>
       </c>
       <c r="B110" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C110" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D110" t="s">
         <v>65</v>
       </c>
       <c r="E110">
-        <v>5520000</v>
+        <v>5060000</v>
       </c>
       <c r="F110" t="s">
         <v>9</v>
@@ -3276,16 +4427,16 @@
         <v>7201250141</v>
       </c>
       <c r="B111" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C111" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D111" t="s">
         <v>65</v>
       </c>
       <c r="E111">
-        <v>6440000</v>
+        <v>5060000</v>
       </c>
       <c r="F111" t="s">
         <v>9</v>
@@ -3296,16 +4447,16 @@
         <v>7201250141</v>
       </c>
       <c r="B112" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C112" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D112" t="s">
         <v>65</v>
       </c>
       <c r="E112">
-        <v>5060000</v>
+        <v>5290000</v>
       </c>
       <c r="F112" t="s">
         <v>9</v>
@@ -3316,16 +4467,16 @@
         <v>7201250141</v>
       </c>
       <c r="B113" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C113" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D113" t="s">
         <v>65</v>
       </c>
       <c r="E113">
-        <v>5060000</v>
+        <v>5750000</v>
       </c>
       <c r="F113" t="s">
         <v>9</v>
@@ -3336,10 +4487,10 @@
         <v>7201250141</v>
       </c>
       <c r="B114" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C114" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D114" t="s">
         <v>65</v>
@@ -3356,16 +4507,16 @@
         <v>7201250141</v>
       </c>
       <c r="B115" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C115" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D115" t="s">
         <v>65</v>
       </c>
       <c r="E115">
-        <v>5750000</v>
+        <v>5290000</v>
       </c>
       <c r="F115" t="s">
         <v>9</v>
@@ -3376,10 +4527,10 @@
         <v>7201250141</v>
       </c>
       <c r="B116" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C116" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D116" t="s">
         <v>65</v>
@@ -3396,10 +4547,10 @@
         <v>7201250141</v>
       </c>
       <c r="B117" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C117" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D117" t="s">
         <v>65</v>
@@ -3416,10 +4567,10 @@
         <v>7201250141</v>
       </c>
       <c r="B118" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C118" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D118" t="s">
         <v>65</v>
@@ -3436,16 +4587,16 @@
         <v>7201250141</v>
       </c>
       <c r="B119" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C119" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D119" t="s">
         <v>65</v>
       </c>
       <c r="E119">
-        <v>5290000</v>
+        <v>5520000</v>
       </c>
       <c r="F119" t="s">
         <v>9</v>
@@ -3456,10 +4607,10 @@
         <v>7201250141</v>
       </c>
       <c r="B120" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C120" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D120" t="s">
         <v>65</v>
@@ -3476,16 +4627,16 @@
         <v>7201250141</v>
       </c>
       <c r="B121" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C121" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D121" t="s">
         <v>65</v>
       </c>
       <c r="E121">
-        <v>5520000</v>
+        <v>5290000</v>
       </c>
       <c r="F121" t="s">
         <v>9</v>
@@ -3496,16 +4647,16 @@
         <v>7201250141</v>
       </c>
       <c r="B122" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C122" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D122" t="s">
         <v>65</v>
       </c>
       <c r="E122">
-        <v>5290000</v>
+        <v>5060000</v>
       </c>
       <c r="F122" t="s">
         <v>9</v>
@@ -3516,16 +4667,16 @@
         <v>7201250141</v>
       </c>
       <c r="B123" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C123" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D123" t="s">
         <v>65</v>
       </c>
       <c r="E123">
-        <v>5290000</v>
+        <v>5980000</v>
       </c>
       <c r="F123" t="s">
         <v>9</v>
@@ -3536,16 +4687,16 @@
         <v>7201250141</v>
       </c>
       <c r="B124" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C124" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D124" t="s">
         <v>65</v>
       </c>
       <c r="E124">
-        <v>5060000</v>
+        <v>5290000</v>
       </c>
       <c r="F124" t="s">
         <v>9</v>
@@ -3556,16 +4707,16 @@
         <v>7201250141</v>
       </c>
       <c r="B125" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C125" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D125" t="s">
         <v>65</v>
       </c>
       <c r="E125">
-        <v>5980000</v>
+        <v>5290000</v>
       </c>
       <c r="F125" t="s">
         <v>9</v>
@@ -3576,10 +4727,10 @@
         <v>7201250141</v>
       </c>
       <c r="B126" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C126" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D126" t="s">
         <v>65</v>
@@ -3596,10 +4747,10 @@
         <v>7201250141</v>
       </c>
       <c r="B127" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C127" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D127" t="s">
         <v>65</v>
@@ -3616,16 +4767,16 @@
         <v>7201250141</v>
       </c>
       <c r="B128" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C128" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D128" t="s">
         <v>65</v>
       </c>
       <c r="E128">
-        <v>5290000</v>
+        <v>5750000</v>
       </c>
       <c r="F128" t="s">
         <v>9</v>
@@ -3636,16 +4787,16 @@
         <v>7201250141</v>
       </c>
       <c r="B129" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C129" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D129" t="s">
         <v>65</v>
       </c>
       <c r="E129">
-        <v>5290000</v>
+        <v>6670000</v>
       </c>
       <c r="F129" t="s">
         <v>9</v>
@@ -3656,16 +4807,16 @@
         <v>7201250141</v>
       </c>
       <c r="B130" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C130" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D130" t="s">
         <v>65</v>
       </c>
       <c r="E130">
-        <v>5750000</v>
+        <v>5520000</v>
       </c>
       <c r="F130" t="s">
         <v>9</v>
@@ -3676,16 +4827,16 @@
         <v>7201250141</v>
       </c>
       <c r="B131" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C131" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D131" t="s">
         <v>65</v>
       </c>
       <c r="E131">
-        <v>6670000</v>
+        <v>5290000</v>
       </c>
       <c r="F131" t="s">
         <v>9</v>
@@ -3696,16 +4847,16 @@
         <v>7201250141</v>
       </c>
       <c r="B132" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C132" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D132" t="s">
         <v>65</v>
       </c>
       <c r="E132">
-        <v>5520000</v>
+        <v>5290000</v>
       </c>
       <c r="F132" t="s">
         <v>9</v>
@@ -3716,10 +4867,10 @@
         <v>7201250141</v>
       </c>
       <c r="B133" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C133" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D133" t="s">
         <v>65</v>
@@ -3736,16 +4887,16 @@
         <v>7201250141</v>
       </c>
       <c r="B134" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C134" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D134" t="s">
         <v>65</v>
       </c>
       <c r="E134">
-        <v>5290000</v>
+        <v>6210000</v>
       </c>
       <c r="F134" t="s">
         <v>9</v>
@@ -3756,10 +4907,10 @@
         <v>7201250141</v>
       </c>
       <c r="B135" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C135" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D135" t="s">
         <v>65</v>
@@ -3776,16 +4927,16 @@
         <v>7201250141</v>
       </c>
       <c r="B136" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C136" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D136" t="s">
         <v>65</v>
       </c>
       <c r="E136">
-        <v>6210000</v>
+        <v>5290000</v>
       </c>
       <c r="F136" t="s">
         <v>9</v>
@@ -3796,10 +4947,10 @@
         <v>7201250141</v>
       </c>
       <c r="B137" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C137" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D137" t="s">
         <v>65</v>
@@ -3816,16 +4967,16 @@
         <v>7201250141</v>
       </c>
       <c r="B138" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C138" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D138" t="s">
         <v>65</v>
       </c>
       <c r="E138">
-        <v>5290000</v>
+        <v>6210000</v>
       </c>
       <c r="F138" t="s">
         <v>9</v>
@@ -3836,10 +4987,10 @@
         <v>7201250141</v>
       </c>
       <c r="B139" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C139" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D139" t="s">
         <v>65</v>
@@ -3856,16 +5007,16 @@
         <v>7201250141</v>
       </c>
       <c r="B140" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C140" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D140" t="s">
         <v>65</v>
       </c>
       <c r="E140">
-        <v>6210000</v>
+        <v>5290000</v>
       </c>
       <c r="F140" t="s">
         <v>9</v>
@@ -3876,10 +5027,10 @@
         <v>7201250141</v>
       </c>
       <c r="B141" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C141" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D141" t="s">
         <v>65</v>
@@ -3896,16 +5047,16 @@
         <v>7201250141</v>
       </c>
       <c r="B142" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C142" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D142" t="s">
         <v>65</v>
       </c>
       <c r="E142">
-        <v>5290000</v>
+        <v>5520000</v>
       </c>
       <c r="F142" t="s">
         <v>9</v>
@@ -3916,16 +5067,16 @@
         <v>7201250141</v>
       </c>
       <c r="B143" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C143" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D143" t="s">
         <v>65</v>
       </c>
       <c r="E143">
-        <v>5290000</v>
+        <v>8165000</v>
       </c>
       <c r="F143" t="s">
         <v>9</v>
@@ -3936,16 +5087,16 @@
         <v>7201250141</v>
       </c>
       <c r="B144" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C144" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D144" t="s">
         <v>65</v>
       </c>
       <c r="E144">
-        <v>5520000</v>
+        <v>6555000</v>
       </c>
       <c r="F144" t="s">
         <v>9</v>
@@ -3956,16 +5107,16 @@
         <v>7201250141</v>
       </c>
       <c r="B145" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C145" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D145" t="s">
         <v>65</v>
       </c>
       <c r="E145">
-        <v>8165000</v>
+        <v>7015000</v>
       </c>
       <c r="F145" t="s">
         <v>9</v>
@@ -3976,16 +5127,16 @@
         <v>7201250141</v>
       </c>
       <c r="B146" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C146" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D146" t="s">
         <v>65</v>
       </c>
       <c r="E146">
-        <v>6555000</v>
+        <v>8250000</v>
       </c>
       <c r="F146" t="s">
         <v>9</v>
@@ -3996,16 +5147,16 @@
         <v>7201250141</v>
       </c>
       <c r="B147" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C147" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D147" t="s">
         <v>65</v>
       </c>
       <c r="E147">
-        <v>7015000</v>
+        <v>8250000</v>
       </c>
       <c r="F147" t="s">
         <v>9</v>
@@ -4016,10 +5167,10 @@
         <v>7201250141</v>
       </c>
       <c r="B148" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C148" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D148" t="s">
         <v>65</v>
@@ -4036,10 +5187,10 @@
         <v>7201250141</v>
       </c>
       <c r="B149" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C149" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D149" t="s">
         <v>65</v>
@@ -4056,16 +5207,16 @@
         <v>7201250141</v>
       </c>
       <c r="B150" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C150" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D150" t="s">
         <v>65</v>
       </c>
       <c r="E150">
-        <v>8250000</v>
+        <v>8165000</v>
       </c>
       <c r="F150" t="s">
         <v>9</v>
@@ -4076,10 +5227,10 @@
         <v>7201250141</v>
       </c>
       <c r="B151" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C151" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D151" t="s">
         <v>65</v>
@@ -4096,16 +5247,16 @@
         <v>7201250141</v>
       </c>
       <c r="B152" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C152" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D152" t="s">
         <v>65</v>
       </c>
       <c r="E152">
-        <v>8165000</v>
+        <v>9500000</v>
       </c>
       <c r="F152" t="s">
         <v>9</v>
@@ -4116,10 +5267,10 @@
         <v>7201250141</v>
       </c>
       <c r="B153" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C153" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D153" t="s">
         <v>65</v>
@@ -4136,16 +5287,16 @@
         <v>7201250141</v>
       </c>
       <c r="B154" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C154" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D154" t="s">
         <v>65</v>
       </c>
       <c r="E154">
-        <v>9500000</v>
+        <v>8250000</v>
       </c>
       <c r="F154" t="s">
         <v>9</v>
@@ -4156,16 +5307,16 @@
         <v>7201250141</v>
       </c>
       <c r="B155" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C155" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D155" t="s">
         <v>65</v>
       </c>
       <c r="E155">
-        <v>8250000</v>
+        <v>6325000</v>
       </c>
       <c r="F155" t="s">
         <v>9</v>
@@ -4176,16 +5327,16 @@
         <v>7201250141</v>
       </c>
       <c r="B156" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C156" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D156" t="s">
         <v>65</v>
       </c>
       <c r="E156">
-        <v>8250000</v>
+        <v>6555000</v>
       </c>
       <c r="F156" t="s">
         <v>9</v>
@@ -4196,10 +5347,10 @@
         <v>7201250141</v>
       </c>
       <c r="B157" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C157" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D157" t="s">
         <v>65</v>
@@ -4216,16 +5367,16 @@
         <v>7201250141</v>
       </c>
       <c r="B158" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C158" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D158" t="s">
         <v>65</v>
       </c>
       <c r="E158">
-        <v>6555000</v>
+        <v>6785000</v>
       </c>
       <c r="F158" t="s">
         <v>9</v>
@@ -4236,16 +5387,16 @@
         <v>7201250141</v>
       </c>
       <c r="B159" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C159" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D159" t="s">
         <v>65</v>
       </c>
       <c r="E159">
-        <v>6325000</v>
+        <v>6785000</v>
       </c>
       <c r="F159" t="s">
         <v>9</v>
@@ -4256,16 +5407,16 @@
         <v>7201250141</v>
       </c>
       <c r="B160" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C160" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D160" t="s">
         <v>65</v>
       </c>
       <c r="E160">
-        <v>6785000</v>
+        <v>6325000</v>
       </c>
       <c r="F160" t="s">
         <v>9</v>
@@ -4276,16 +5427,16 @@
         <v>7201250141</v>
       </c>
       <c r="B161" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C161" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D161" t="s">
         <v>65</v>
       </c>
       <c r="E161">
-        <v>6785000</v>
+        <v>6555000</v>
       </c>
       <c r="F161" t="s">
         <v>9</v>
@@ -4296,16 +5447,16 @@
         <v>7201250141</v>
       </c>
       <c r="B162" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C162" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D162" t="s">
         <v>65</v>
       </c>
       <c r="E162">
-        <v>6325000</v>
+        <v>7245000</v>
       </c>
       <c r="F162" t="s">
         <v>9</v>
@@ -4316,16 +5467,16 @@
         <v>7201250141</v>
       </c>
       <c r="B163" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C163" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D163" t="s">
         <v>65</v>
       </c>
       <c r="E163">
-        <v>6555000</v>
+        <v>7245000</v>
       </c>
       <c r="F163" t="s">
         <v>9</v>
@@ -4336,10 +5487,10 @@
         <v>7201250141</v>
       </c>
       <c r="B164" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C164" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D164" t="s">
         <v>65</v>
@@ -4356,16 +5507,16 @@
         <v>7201250141</v>
       </c>
       <c r="B165" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C165" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D165" t="s">
         <v>65</v>
       </c>
       <c r="E165">
-        <v>7245000</v>
+        <v>6785000</v>
       </c>
       <c r="F165" t="s">
         <v>9</v>
@@ -4376,16 +5527,16 @@
         <v>7201250141</v>
       </c>
       <c r="B166" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C166" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D166" t="s">
         <v>65</v>
       </c>
       <c r="E166">
-        <v>7245000</v>
+        <v>7705000</v>
       </c>
       <c r="F166" t="s">
         <v>9</v>
@@ -4396,42 +5547,5743 @@
         <v>7201250141</v>
       </c>
       <c r="B167" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C167" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D167" t="s">
         <v>65</v>
       </c>
       <c r="E167">
+        <v>6325000</v>
+      </c>
+      <c r="F167" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A168">
+        <v>7201250141</v>
+      </c>
+      <c r="B168" t="s">
+        <v>81</v>
+      </c>
+      <c r="C168" t="s">
+        <v>182</v>
+      </c>
+      <c r="D168" t="s">
+        <v>65</v>
+      </c>
+      <c r="E168">
+        <v>6325000</v>
+      </c>
+      <c r="F168" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A169">
+        <v>7201250141</v>
+      </c>
+      <c r="B169" t="s">
+        <v>81</v>
+      </c>
+      <c r="C169" t="s">
+        <v>183</v>
+      </c>
+      <c r="D169" t="s">
+        <v>65</v>
+      </c>
+      <c r="E169">
+        <v>6555000</v>
+      </c>
+      <c r="F169" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A170">
+        <v>7201250141</v>
+      </c>
+      <c r="B170" t="s">
+        <v>81</v>
+      </c>
+      <c r="C170" t="s">
+        <v>184</v>
+      </c>
+      <c r="D170" t="s">
+        <v>65</v>
+      </c>
+      <c r="E170">
+        <v>6325000</v>
+      </c>
+      <c r="F170" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A171">
+        <v>7201250141</v>
+      </c>
+      <c r="B171" t="s">
+        <v>81</v>
+      </c>
+      <c r="C171" t="s">
+        <v>185</v>
+      </c>
+      <c r="D171" t="s">
+        <v>65</v>
+      </c>
+      <c r="E171">
+        <v>6555000</v>
+      </c>
+      <c r="F171" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A172">
+        <v>7201250141</v>
+      </c>
+      <c r="B172" t="s">
+        <v>81</v>
+      </c>
+      <c r="C172" t="s">
+        <v>186</v>
+      </c>
+      <c r="D172" t="s">
+        <v>65</v>
+      </c>
+      <c r="E172">
+        <v>7705000</v>
+      </c>
+      <c r="F172" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A173">
+        <v>7201250141</v>
+      </c>
+      <c r="B173" t="s">
+        <v>81</v>
+      </c>
+      <c r="C173" t="s">
+        <v>187</v>
+      </c>
+      <c r="D173" t="s">
+        <v>65</v>
+      </c>
+      <c r="E173">
         <v>6785000</v>
       </c>
-      <c r="F167" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A168" t="s">
-        <v>180</v>
-      </c>
-      <c r="B168" t="s">
-        <v>77</v>
-      </c>
-      <c r="C168" t="s">
-        <v>181</v>
-      </c>
-      <c r="D168" t="s">
-        <v>65</v>
-      </c>
-      <c r="E168">
+      <c r="F173" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A174">
+        <v>7201250141</v>
+      </c>
+      <c r="B174" t="s">
+        <v>81</v>
+      </c>
+      <c r="C174" t="s">
+        <v>188</v>
+      </c>
+      <c r="D174" t="s">
+        <v>65</v>
+      </c>
+      <c r="E174">
+        <v>6785000</v>
+      </c>
+      <c r="F174" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A175">
+        <v>7201250141</v>
+      </c>
+      <c r="B175" t="s">
+        <v>81</v>
+      </c>
+      <c r="C175" t="s">
+        <v>189</v>
+      </c>
+      <c r="D175" t="s">
+        <v>65</v>
+      </c>
+      <c r="E175">
+        <v>6785000</v>
+      </c>
+      <c r="F175" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A176">
+        <v>7201250141</v>
+      </c>
+      <c r="B176" t="s">
+        <v>81</v>
+      </c>
+      <c r="C176" t="s">
+        <v>190</v>
+      </c>
+      <c r="D176" t="s">
+        <v>65</v>
+      </c>
+      <c r="E176">
         <v>7705000</v>
       </c>
-      <c r="F168" t="s">
+      <c r="F176" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A177">
+        <v>7201250141</v>
+      </c>
+      <c r="B177" t="s">
+        <v>81</v>
+      </c>
+      <c r="C177" t="s">
+        <v>191</v>
+      </c>
+      <c r="D177" t="s">
+        <v>65</v>
+      </c>
+      <c r="E177">
+        <v>6555000</v>
+      </c>
+      <c r="F177" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A178">
+        <v>7201250141</v>
+      </c>
+      <c r="B178" t="s">
+        <v>81</v>
+      </c>
+      <c r="C178" t="s">
+        <v>192</v>
+      </c>
+      <c r="D178" t="s">
+        <v>65</v>
+      </c>
+      <c r="E178">
+        <v>6555000</v>
+      </c>
+      <c r="F178" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A179">
+        <v>7201250141</v>
+      </c>
+      <c r="B179" t="s">
+        <v>81</v>
+      </c>
+      <c r="C179" t="s">
+        <v>193</v>
+      </c>
+      <c r="D179" t="s">
+        <v>65</v>
+      </c>
+      <c r="E179">
+        <v>6555000</v>
+      </c>
+      <c r="F179" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A180">
+        <v>7201250141</v>
+      </c>
+      <c r="B180" t="s">
+        <v>81</v>
+      </c>
+      <c r="C180" t="s">
+        <v>194</v>
+      </c>
+      <c r="D180" t="s">
+        <v>65</v>
+      </c>
+      <c r="E180">
+        <v>6555000</v>
+      </c>
+      <c r="F180" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A181">
+        <v>7201250141</v>
+      </c>
+      <c r="B181" t="s">
+        <v>81</v>
+      </c>
+      <c r="C181" t="s">
+        <v>195</v>
+      </c>
+      <c r="D181" t="s">
+        <v>65</v>
+      </c>
+      <c r="E181">
+        <v>6555000</v>
+      </c>
+      <c r="F181" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A182">
+        <v>7201250141</v>
+      </c>
+      <c r="B182" t="s">
+        <v>81</v>
+      </c>
+      <c r="C182" t="s">
+        <v>196</v>
+      </c>
+      <c r="D182" t="s">
+        <v>65</v>
+      </c>
+      <c r="E182">
+        <v>6555000</v>
+      </c>
+      <c r="F182" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A183">
+        <v>7201250141</v>
+      </c>
+      <c r="B183" t="s">
+        <v>81</v>
+      </c>
+      <c r="C183" t="s">
+        <v>197</v>
+      </c>
+      <c r="D183" t="s">
+        <v>65</v>
+      </c>
+      <c r="E183">
+        <v>6555000</v>
+      </c>
+      <c r="F183" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A184">
+        <v>7201250141</v>
+      </c>
+      <c r="B184" t="s">
+        <v>81</v>
+      </c>
+      <c r="C184" t="s">
+        <v>198</v>
+      </c>
+      <c r="D184" t="s">
+        <v>65</v>
+      </c>
+      <c r="E184">
+        <v>6785000</v>
+      </c>
+      <c r="F184" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A185">
+        <v>7201250141</v>
+      </c>
+      <c r="B185" t="s">
+        <v>81</v>
+      </c>
+      <c r="C185" t="s">
+        <v>199</v>
+      </c>
+      <c r="D185" t="s">
+        <v>65</v>
+      </c>
+      <c r="E185">
+        <v>7705000</v>
+      </c>
+      <c r="F185" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A186">
+        <v>7201250141</v>
+      </c>
+      <c r="B186" t="s">
+        <v>81</v>
+      </c>
+      <c r="C186" t="s">
+        <v>200</v>
+      </c>
+      <c r="D186" t="s">
+        <v>65</v>
+      </c>
+      <c r="E186">
+        <v>6325000</v>
+      </c>
+      <c r="F186" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A187">
+        <v>7201250141</v>
+      </c>
+      <c r="B187" t="s">
+        <v>81</v>
+      </c>
+      <c r="C187" t="s">
+        <v>201</v>
+      </c>
+      <c r="D187" t="s">
+        <v>65</v>
+      </c>
+      <c r="E187">
+        <v>6325000</v>
+      </c>
+      <c r="F187" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A188">
+        <v>7201250141</v>
+      </c>
+      <c r="B188" t="s">
+        <v>81</v>
+      </c>
+      <c r="C188" t="s">
+        <v>202</v>
+      </c>
+      <c r="D188" t="s">
+        <v>65</v>
+      </c>
+      <c r="E188">
+        <v>6555000</v>
+      </c>
+      <c r="F188" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A189">
+        <v>7201250141</v>
+      </c>
+      <c r="B189" t="s">
+        <v>81</v>
+      </c>
+      <c r="C189" t="s">
+        <v>203</v>
+      </c>
+      <c r="D189" t="s">
+        <v>65</v>
+      </c>
+      <c r="E189">
+        <v>7015000</v>
+      </c>
+      <c r="F189" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A190">
+        <v>7201250141</v>
+      </c>
+      <c r="B190" t="s">
+        <v>81</v>
+      </c>
+      <c r="C190" t="s">
+        <v>204</v>
+      </c>
+      <c r="D190" t="s">
+        <v>65</v>
+      </c>
+      <c r="E190">
+        <v>6555000</v>
+      </c>
+      <c r="F190" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A191">
+        <v>7201250141</v>
+      </c>
+      <c r="B191" t="s">
+        <v>81</v>
+      </c>
+      <c r="C191" t="s">
+        <v>205</v>
+      </c>
+      <c r="D191" t="s">
+        <v>65</v>
+      </c>
+      <c r="E191">
+        <v>6555000</v>
+      </c>
+      <c r="F191" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A192">
+        <v>7201250141</v>
+      </c>
+      <c r="B192" t="s">
+        <v>81</v>
+      </c>
+      <c r="C192" t="s">
+        <v>206</v>
+      </c>
+      <c r="D192" t="s">
+        <v>65</v>
+      </c>
+      <c r="E192">
+        <v>6555000</v>
+      </c>
+      <c r="F192" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A193">
+        <v>7201250141</v>
+      </c>
+      <c r="B193" t="s">
+        <v>81</v>
+      </c>
+      <c r="C193" t="s">
+        <v>207</v>
+      </c>
+      <c r="D193" t="s">
+        <v>65</v>
+      </c>
+      <c r="E193">
+        <v>6785000</v>
+      </c>
+      <c r="F193" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A194">
+        <v>7201250141</v>
+      </c>
+      <c r="B194" t="s">
+        <v>81</v>
+      </c>
+      <c r="C194" t="s">
+        <v>208</v>
+      </c>
+      <c r="D194" t="s">
+        <v>65</v>
+      </c>
+      <c r="E194">
+        <v>6555000</v>
+      </c>
+      <c r="F194" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A195">
+        <v>7201250141</v>
+      </c>
+      <c r="B195" t="s">
+        <v>81</v>
+      </c>
+      <c r="C195" t="s">
+        <v>209</v>
+      </c>
+      <c r="D195" t="s">
+        <v>65</v>
+      </c>
+      <c r="E195">
+        <v>6555000</v>
+      </c>
+      <c r="F195" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A196">
+        <v>7201250141</v>
+      </c>
+      <c r="B196" t="s">
+        <v>81</v>
+      </c>
+      <c r="C196" t="s">
+        <v>210</v>
+      </c>
+      <c r="D196" t="s">
+        <v>65</v>
+      </c>
+      <c r="E196">
+        <v>6785000</v>
+      </c>
+      <c r="F196" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A197">
+        <v>7201250141</v>
+      </c>
+      <c r="B197" t="s">
+        <v>81</v>
+      </c>
+      <c r="C197" t="s">
+        <v>211</v>
+      </c>
+      <c r="D197" t="s">
+        <v>65</v>
+      </c>
+      <c r="E197">
+        <v>6555000</v>
+      </c>
+      <c r="F197" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A198">
+        <v>7201250141</v>
+      </c>
+      <c r="B198" t="s">
+        <v>81</v>
+      </c>
+      <c r="C198" t="s">
+        <v>212</v>
+      </c>
+      <c r="D198" t="s">
+        <v>65</v>
+      </c>
+      <c r="E198">
+        <v>6555000</v>
+      </c>
+      <c r="F198" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A199">
+        <v>7201250141</v>
+      </c>
+      <c r="B199" t="s">
+        <v>81</v>
+      </c>
+      <c r="C199" t="s">
+        <v>213</v>
+      </c>
+      <c r="D199" t="s">
+        <v>65</v>
+      </c>
+      <c r="E199">
+        <v>6325000</v>
+      </c>
+      <c r="F199" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A200">
+        <v>7201250141</v>
+      </c>
+      <c r="B200" t="s">
+        <v>81</v>
+      </c>
+      <c r="C200" t="s">
+        <v>214</v>
+      </c>
+      <c r="D200" t="s">
+        <v>65</v>
+      </c>
+      <c r="E200">
+        <v>7245000</v>
+      </c>
+      <c r="F200" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A201">
+        <v>7201250141</v>
+      </c>
+      <c r="B201" t="s">
+        <v>81</v>
+      </c>
+      <c r="C201" t="s">
+        <v>215</v>
+      </c>
+      <c r="D201" t="s">
+        <v>65</v>
+      </c>
+      <c r="E201">
+        <v>6555000</v>
+      </c>
+      <c r="F201" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A202">
+        <v>7201250141</v>
+      </c>
+      <c r="B202" t="s">
+        <v>81</v>
+      </c>
+      <c r="C202" t="s">
+        <v>216</v>
+      </c>
+      <c r="D202" t="s">
+        <v>65</v>
+      </c>
+      <c r="E202">
+        <v>6555000</v>
+      </c>
+      <c r="F202" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A203">
+        <v>7201250141</v>
+      </c>
+      <c r="B203" t="s">
+        <v>81</v>
+      </c>
+      <c r="C203" t="s">
+        <v>217</v>
+      </c>
+      <c r="D203" t="s">
+        <v>65</v>
+      </c>
+      <c r="E203">
+        <v>6555000</v>
+      </c>
+      <c r="F203" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A204">
+        <v>7201250141</v>
+      </c>
+      <c r="B204" t="s">
+        <v>81</v>
+      </c>
+      <c r="C204" t="s">
+        <v>218</v>
+      </c>
+      <c r="D204" t="s">
+        <v>65</v>
+      </c>
+      <c r="E204">
+        <v>6555000</v>
+      </c>
+      <c r="F204" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A205">
+        <v>7201250141</v>
+      </c>
+      <c r="B205" t="s">
+        <v>81</v>
+      </c>
+      <c r="C205" t="s">
+        <v>219</v>
+      </c>
+      <c r="D205" t="s">
+        <v>65</v>
+      </c>
+      <c r="E205">
+        <v>7015000</v>
+      </c>
+      <c r="F205" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A206">
+        <v>7201250141</v>
+      </c>
+      <c r="B206" t="s">
+        <v>81</v>
+      </c>
+      <c r="C206" t="s">
+        <v>220</v>
+      </c>
+      <c r="D206" t="s">
+        <v>65</v>
+      </c>
+      <c r="E206">
+        <v>7935000</v>
+      </c>
+      <c r="F206" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A207">
+        <v>7201250141</v>
+      </c>
+      <c r="B207" t="s">
+        <v>81</v>
+      </c>
+      <c r="C207" t="s">
+        <v>221</v>
+      </c>
+      <c r="D207" t="s">
+        <v>65</v>
+      </c>
+      <c r="E207">
+        <v>6785000</v>
+      </c>
+      <c r="F207" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A208">
+        <v>7201250141</v>
+      </c>
+      <c r="B208" t="s">
+        <v>81</v>
+      </c>
+      <c r="C208" t="s">
+        <v>222</v>
+      </c>
+      <c r="D208" t="s">
+        <v>65</v>
+      </c>
+      <c r="E208">
+        <v>6555000</v>
+      </c>
+      <c r="F208" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A209">
+        <v>7201250141</v>
+      </c>
+      <c r="B209" t="s">
+        <v>81</v>
+      </c>
+      <c r="C209" t="s">
+        <v>223</v>
+      </c>
+      <c r="D209" t="s">
+        <v>65</v>
+      </c>
+      <c r="E209">
+        <v>6555000</v>
+      </c>
+      <c r="F209" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A210">
+        <v>7201250141</v>
+      </c>
+      <c r="B210" t="s">
+        <v>81</v>
+      </c>
+      <c r="C210" t="s">
+        <v>224</v>
+      </c>
+      <c r="D210" t="s">
+        <v>65</v>
+      </c>
+      <c r="E210">
+        <v>6555000</v>
+      </c>
+      <c r="F210" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A211">
+        <v>7201250141</v>
+      </c>
+      <c r="B211" t="s">
+        <v>81</v>
+      </c>
+      <c r="C211" t="s">
+        <v>225</v>
+      </c>
+      <c r="D211" t="s">
+        <v>65</v>
+      </c>
+      <c r="E211">
+        <v>7475000</v>
+      </c>
+      <c r="F211" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A212">
+        <v>7201250141</v>
+      </c>
+      <c r="B212" t="s">
+        <v>81</v>
+      </c>
+      <c r="C212" t="s">
+        <v>226</v>
+      </c>
+      <c r="D212" t="s">
+        <v>65</v>
+      </c>
+      <c r="E212">
+        <v>6555000</v>
+      </c>
+      <c r="F212" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A213">
+        <v>7201250141</v>
+      </c>
+      <c r="B213" t="s">
+        <v>81</v>
+      </c>
+      <c r="C213" t="s">
+        <v>227</v>
+      </c>
+      <c r="D213" t="s">
+        <v>65</v>
+      </c>
+      <c r="E213">
+        <v>6555000</v>
+      </c>
+      <c r="F213" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A214">
+        <v>7201250141</v>
+      </c>
+      <c r="B214" t="s">
+        <v>81</v>
+      </c>
+      <c r="C214" t="s">
+        <v>228</v>
+      </c>
+      <c r="D214" t="s">
+        <v>65</v>
+      </c>
+      <c r="E214">
+        <v>6555000</v>
+      </c>
+      <c r="F214" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A215">
+        <v>7201250141</v>
+      </c>
+      <c r="B215" t="s">
+        <v>81</v>
+      </c>
+      <c r="C215" t="s">
+        <v>229</v>
+      </c>
+      <c r="D215" t="s">
+        <v>65</v>
+      </c>
+      <c r="E215">
+        <v>7475000</v>
+      </c>
+      <c r="F215" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A216">
+        <v>7201250141</v>
+      </c>
+      <c r="B216" t="s">
+        <v>81</v>
+      </c>
+      <c r="C216" t="s">
+        <v>230</v>
+      </c>
+      <c r="D216" t="s">
+        <v>65</v>
+      </c>
+      <c r="E216">
+        <v>6555000</v>
+      </c>
+      <c r="F216" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A217">
+        <v>7201250141</v>
+      </c>
+      <c r="B217" t="s">
+        <v>81</v>
+      </c>
+      <c r="C217" t="s">
+        <v>231</v>
+      </c>
+      <c r="D217" t="s">
+        <v>65</v>
+      </c>
+      <c r="E217">
+        <v>6555000</v>
+      </c>
+      <c r="F217" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A218">
+        <v>7201250141</v>
+      </c>
+      <c r="B218" t="s">
+        <v>81</v>
+      </c>
+      <c r="C218" t="s">
+        <v>232</v>
+      </c>
+      <c r="D218" t="s">
+        <v>65</v>
+      </c>
+      <c r="E218">
+        <v>6555000</v>
+      </c>
+      <c r="F218" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A219">
+        <v>7201250141</v>
+      </c>
+      <c r="B219" t="s">
+        <v>81</v>
+      </c>
+      <c r="C219" t="s">
+        <v>233</v>
+      </c>
+      <c r="D219" t="s">
+        <v>65</v>
+      </c>
+      <c r="E219">
+        <v>6785000</v>
+      </c>
+      <c r="F219" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A220">
+        <v>7201250141</v>
+      </c>
+      <c r="B220" t="s">
+        <v>81</v>
+      </c>
+      <c r="C220" t="s">
+        <v>234</v>
+      </c>
+      <c r="D220" t="s">
+        <v>235</v>
+      </c>
+      <c r="E220">
+        <v>350000</v>
+      </c>
+      <c r="F220" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A221">
+        <v>7201250141</v>
+      </c>
+      <c r="B221" t="s">
+        <v>81</v>
+      </c>
+      <c r="C221" t="s">
+        <v>234</v>
+      </c>
+      <c r="D221" t="s">
+        <v>235</v>
+      </c>
+      <c r="E221">
+        <v>350000</v>
+      </c>
+      <c r="F221" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A222">
+        <v>7201250141</v>
+      </c>
+      <c r="B222" t="s">
+        <v>81</v>
+      </c>
+      <c r="C222" t="s">
+        <v>236</v>
+      </c>
+      <c r="D222" t="s">
+        <v>235</v>
+      </c>
+      <c r="E222">
+        <v>300000</v>
+      </c>
+      <c r="F222" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A223">
+        <v>7201250141</v>
+      </c>
+      <c r="B223" t="s">
+        <v>81</v>
+      </c>
+      <c r="C223" t="s">
+        <v>237</v>
+      </c>
+      <c r="D223" t="s">
+        <v>16</v>
+      </c>
+      <c r="E223">
+        <v>1500000</v>
+      </c>
+      <c r="F223" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A224">
+        <v>7201250141</v>
+      </c>
+      <c r="B224" t="s">
+        <v>81</v>
+      </c>
+      <c r="C224" t="s">
+        <v>238</v>
+      </c>
+      <c r="D224" t="s">
+        <v>235</v>
+      </c>
+      <c r="E224">
+        <v>300000</v>
+      </c>
+      <c r="F224" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A225">
+        <v>7201250141</v>
+      </c>
+      <c r="B225" t="s">
+        <v>81</v>
+      </c>
+      <c r="C225" t="s">
+        <v>239</v>
+      </c>
+      <c r="D225" t="s">
+        <v>235</v>
+      </c>
+      <c r="E225">
+        <v>300000</v>
+      </c>
+      <c r="F225" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A226">
+        <v>7201250141</v>
+      </c>
+      <c r="B226" t="s">
+        <v>81</v>
+      </c>
+      <c r="C226" t="s">
+        <v>240</v>
+      </c>
+      <c r="D226" t="s">
+        <v>235</v>
+      </c>
+      <c r="E226">
+        <v>200000</v>
+      </c>
+      <c r="F226" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A227">
+        <v>7201250141</v>
+      </c>
+      <c r="B227" t="s">
+        <v>81</v>
+      </c>
+      <c r="C227" t="s">
+        <v>241</v>
+      </c>
+      <c r="D227" t="s">
+        <v>16</v>
+      </c>
+      <c r="E227">
+        <v>1500000</v>
+      </c>
+      <c r="F227" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A228">
+        <v>7201250141</v>
+      </c>
+      <c r="B228" t="s">
+        <v>81</v>
+      </c>
+      <c r="C228" t="s">
+        <v>242</v>
+      </c>
+      <c r="D228" t="s">
+        <v>16</v>
+      </c>
+      <c r="E228">
+        <v>1500000</v>
+      </c>
+      <c r="F228" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A229">
+        <v>7201250141</v>
+      </c>
+      <c r="B229" t="s">
+        <v>243</v>
+      </c>
+      <c r="C229" t="s">
+        <v>244</v>
+      </c>
+      <c r="D229" t="s">
+        <v>65</v>
+      </c>
+      <c r="E229">
+        <v>12500000</v>
+      </c>
+      <c r="F229" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A230">
+        <v>7201250141</v>
+      </c>
+      <c r="B230" t="s">
+        <v>243</v>
+      </c>
+      <c r="C230" t="s">
+        <v>245</v>
+      </c>
+      <c r="D230" t="s">
+        <v>65</v>
+      </c>
+      <c r="E230">
+        <v>12500000</v>
+      </c>
+      <c r="F230" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A231">
+        <v>7201250141</v>
+      </c>
+      <c r="B231" t="s">
+        <v>243</v>
+      </c>
+      <c r="C231" t="s">
+        <v>246</v>
+      </c>
+      <c r="D231" t="s">
+        <v>65</v>
+      </c>
+      <c r="E231">
+        <v>7500000</v>
+      </c>
+      <c r="F231" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A232">
+        <v>7201250141</v>
+      </c>
+      <c r="B232" t="s">
+        <v>243</v>
+      </c>
+      <c r="C232" t="s">
+        <v>247</v>
+      </c>
+      <c r="D232" t="s">
+        <v>65</v>
+      </c>
+      <c r="E232">
+        <v>7500000</v>
+      </c>
+      <c r="F232" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A233">
+        <v>7201250141</v>
+      </c>
+      <c r="B233" t="s">
+        <v>243</v>
+      </c>
+      <c r="C233" t="s">
+        <v>248</v>
+      </c>
+      <c r="D233" t="s">
+        <v>16</v>
+      </c>
+      <c r="E233">
+        <v>8500000</v>
+      </c>
+      <c r="F233" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A234">
+        <v>7201250141</v>
+      </c>
+      <c r="B234" t="s">
+        <v>243</v>
+      </c>
+      <c r="C234" t="s">
+        <v>249</v>
+      </c>
+      <c r="D234" t="s">
+        <v>16</v>
+      </c>
+      <c r="E234">
+        <v>8000000</v>
+      </c>
+      <c r="F234" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A235">
+        <v>7201250141</v>
+      </c>
+      <c r="B235" t="s">
+        <v>243</v>
+      </c>
+      <c r="C235" t="s">
+        <v>250</v>
+      </c>
+      <c r="D235" t="s">
+        <v>16</v>
+      </c>
+      <c r="E235">
+        <v>3500000</v>
+      </c>
+      <c r="F235" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A236">
+        <v>7201250141</v>
+      </c>
+      <c r="B236" t="s">
+        <v>243</v>
+      </c>
+      <c r="C236" t="s">
+        <v>251</v>
+      </c>
+      <c r="D236" t="s">
+        <v>16</v>
+      </c>
+      <c r="E236">
+        <v>3000000</v>
+      </c>
+      <c r="F236" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A237">
+        <v>7201250141</v>
+      </c>
+      <c r="B237" t="s">
+        <v>243</v>
+      </c>
+      <c r="C237" t="s">
+        <v>252</v>
+      </c>
+      <c r="D237" t="s">
+        <v>16</v>
+      </c>
+      <c r="E237">
+        <v>3000000</v>
+      </c>
+      <c r="F237" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A238">
+        <v>7201250141</v>
+      </c>
+      <c r="B238" t="s">
+        <v>243</v>
+      </c>
+      <c r="C238" t="s">
+        <v>253</v>
+      </c>
+      <c r="D238" t="s">
+        <v>16</v>
+      </c>
+      <c r="E238">
+        <v>2500000</v>
+      </c>
+      <c r="F238" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A239">
+        <v>7201250141</v>
+      </c>
+      <c r="B239" t="s">
+        <v>243</v>
+      </c>
+      <c r="C239" t="s">
+        <v>254</v>
+      </c>
+      <c r="D239" t="s">
+        <v>16</v>
+      </c>
+      <c r="E239">
+        <v>3000000</v>
+      </c>
+      <c r="F239" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A240">
+        <v>7201250141</v>
+      </c>
+      <c r="B240" t="s">
+        <v>243</v>
+      </c>
+      <c r="C240" t="s">
+        <v>255</v>
+      </c>
+      <c r="D240" t="s">
+        <v>16</v>
+      </c>
+      <c r="E240">
+        <v>3500000</v>
+      </c>
+      <c r="F240" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A241">
+        <v>7201250141</v>
+      </c>
+      <c r="B241" t="s">
+        <v>243</v>
+      </c>
+      <c r="C241" t="s">
+        <v>256</v>
+      </c>
+      <c r="D241" t="s">
+        <v>16</v>
+      </c>
+      <c r="E241">
+        <v>2750000</v>
+      </c>
+      <c r="F241" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A242">
+        <v>7201250141</v>
+      </c>
+      <c r="B242" t="s">
+        <v>243</v>
+      </c>
+      <c r="C242" t="s">
+        <v>257</v>
+      </c>
+      <c r="D242" t="s">
+        <v>16</v>
+      </c>
+      <c r="E242">
+        <v>4000000</v>
+      </c>
+      <c r="F242" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A243">
+        <v>7201250141</v>
+      </c>
+      <c r="B243" t="s">
+        <v>243</v>
+      </c>
+      <c r="C243" t="s">
+        <v>258</v>
+      </c>
+      <c r="D243" t="s">
+        <v>16</v>
+      </c>
+      <c r="E243">
+        <v>2250000</v>
+      </c>
+      <c r="F243" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A244">
+        <v>7201250141</v>
+      </c>
+      <c r="B244" t="s">
+        <v>243</v>
+      </c>
+      <c r="C244" t="s">
+        <v>259</v>
+      </c>
+      <c r="D244" t="s">
+        <v>16</v>
+      </c>
+      <c r="E244">
+        <v>5000000</v>
+      </c>
+      <c r="F244" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A245">
+        <v>7201250141</v>
+      </c>
+      <c r="B245" t="s">
+        <v>243</v>
+      </c>
+      <c r="C245" t="s">
+        <v>260</v>
+      </c>
+      <c r="D245" t="s">
+        <v>8</v>
+      </c>
+      <c r="E245">
+        <v>50000000</v>
+      </c>
+      <c r="F245" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A246">
+        <v>7201250141</v>
+      </c>
+      <c r="B246" t="s">
+        <v>243</v>
+      </c>
+      <c r="C246" t="s">
+        <v>261</v>
+      </c>
+      <c r="D246" t="s">
+        <v>8</v>
+      </c>
+      <c r="E246">
+        <v>60000000</v>
+      </c>
+      <c r="F246" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A247">
+        <v>7201250141</v>
+      </c>
+      <c r="B247" t="s">
+        <v>243</v>
+      </c>
+      <c r="C247" t="s">
+        <v>262</v>
+      </c>
+      <c r="D247" t="s">
+        <v>8</v>
+      </c>
+      <c r="E247">
+        <v>40000000</v>
+      </c>
+      <c r="F247" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A248">
+        <v>7201250141</v>
+      </c>
+      <c r="B248" t="s">
+        <v>243</v>
+      </c>
+      <c r="C248" t="s">
+        <v>263</v>
+      </c>
+      <c r="D248" t="s">
+        <v>8</v>
+      </c>
+      <c r="E248">
+        <v>15000000</v>
+      </c>
+      <c r="F248" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A249">
+        <v>7201250141</v>
+      </c>
+      <c r="B249" t="s">
+        <v>243</v>
+      </c>
+      <c r="C249" t="s">
+        <v>264</v>
+      </c>
+      <c r="D249" t="s">
+        <v>8</v>
+      </c>
+      <c r="E249">
+        <v>25000000</v>
+      </c>
+      <c r="F249" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A250">
+        <v>7201250141</v>
+      </c>
+      <c r="B250" t="s">
+        <v>243</v>
+      </c>
+      <c r="C250" t="s">
+        <v>265</v>
+      </c>
+      <c r="D250" t="s">
+        <v>65</v>
+      </c>
+      <c r="E250">
+        <v>7500000</v>
+      </c>
+      <c r="F250" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A251">
+        <v>7201250141</v>
+      </c>
+      <c r="B251" t="s">
+        <v>243</v>
+      </c>
+      <c r="C251" t="s">
+        <v>266</v>
+      </c>
+      <c r="D251" t="s">
+        <v>16</v>
+      </c>
+      <c r="E251">
+        <v>750000</v>
+      </c>
+      <c r="F251" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A252">
+        <v>7201250141</v>
+      </c>
+      <c r="B252" t="s">
+        <v>267</v>
+      </c>
+      <c r="C252" t="s">
+        <v>268</v>
+      </c>
+      <c r="D252" t="s">
+        <v>16</v>
+      </c>
+      <c r="E252">
+        <v>750000</v>
+      </c>
+      <c r="F252" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A253">
+        <v>7201250141</v>
+      </c>
+      <c r="B253" t="s">
+        <v>267</v>
+      </c>
+      <c r="C253" t="s">
+        <v>268</v>
+      </c>
+      <c r="D253" t="s">
+        <v>269</v>
+      </c>
+      <c r="E253">
+        <v>25000</v>
+      </c>
+      <c r="F253" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A254">
+        <v>7201250141</v>
+      </c>
+      <c r="B254" t="s">
+        <v>267</v>
+      </c>
+      <c r="C254" t="s">
+        <v>268</v>
+      </c>
+      <c r="D254" t="s">
+        <v>269</v>
+      </c>
+      <c r="E254">
+        <v>25000</v>
+      </c>
+      <c r="F254" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A255">
+        <v>7201250141</v>
+      </c>
+      <c r="B255" t="s">
+        <v>267</v>
+      </c>
+      <c r="C255" t="s">
+        <v>270</v>
+      </c>
+      <c r="D255" t="s">
+        <v>37</v>
+      </c>
+      <c r="E255">
+        <v>1500000</v>
+      </c>
+      <c r="F255" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A256">
+        <v>7201250141</v>
+      </c>
+      <c r="B256" t="s">
+        <v>267</v>
+      </c>
+      <c r="C256" t="s">
+        <v>271</v>
+      </c>
+      <c r="D256" t="s">
+        <v>37</v>
+      </c>
+      <c r="E256">
+        <v>1200000</v>
+      </c>
+      <c r="F256" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A257">
+        <v>7201250141</v>
+      </c>
+      <c r="B257" t="s">
+        <v>267</v>
+      </c>
+      <c r="C257" t="s">
+        <v>272</v>
+      </c>
+      <c r="D257" t="s">
+        <v>37</v>
+      </c>
+      <c r="E257">
+        <v>344500</v>
+      </c>
+      <c r="F257" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A258">
+        <v>7201250141</v>
+      </c>
+      <c r="B258" t="s">
+        <v>267</v>
+      </c>
+      <c r="C258" t="s">
+        <v>273</v>
+      </c>
+      <c r="D258" t="s">
+        <v>37</v>
+      </c>
+      <c r="E258">
+        <v>344500</v>
+      </c>
+      <c r="F258" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A259">
+        <v>7201250141</v>
+      </c>
+      <c r="B259" t="s">
+        <v>267</v>
+      </c>
+      <c r="C259" t="s">
+        <v>274</v>
+      </c>
+      <c r="D259" t="s">
+        <v>37</v>
+      </c>
+      <c r="E259">
+        <v>150000</v>
+      </c>
+      <c r="F259" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A260">
+        <v>7201250141</v>
+      </c>
+      <c r="B260" t="s">
+        <v>267</v>
+      </c>
+      <c r="C260" t="s">
+        <v>275</v>
+      </c>
+      <c r="D260" t="s">
+        <v>37</v>
+      </c>
+      <c r="E260">
+        <v>195000</v>
+      </c>
+      <c r="F260" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A261">
+        <v>7201250141</v>
+      </c>
+      <c r="B261" t="s">
+        <v>267</v>
+      </c>
+      <c r="C261" t="s">
+        <v>276</v>
+      </c>
+      <c r="D261" t="s">
+        <v>74</v>
+      </c>
+      <c r="E261">
+        <v>37500</v>
+      </c>
+      <c r="F261" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A262">
+        <v>7201250141</v>
+      </c>
+      <c r="B262" t="s">
+        <v>267</v>
+      </c>
+      <c r="C262" t="s">
+        <v>277</v>
+      </c>
+      <c r="D262" t="s">
+        <v>37</v>
+      </c>
+      <c r="E262">
+        <v>312000</v>
+      </c>
+      <c r="F262" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A263">
+        <v>7201250141</v>
+      </c>
+      <c r="B263" t="s">
+        <v>267</v>
+      </c>
+      <c r="C263" t="s">
+        <v>278</v>
+      </c>
+      <c r="D263" t="s">
+        <v>37</v>
+      </c>
+      <c r="E263">
+        <v>250000</v>
+      </c>
+      <c r="F263" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A264">
+        <v>7201250141</v>
+      </c>
+      <c r="B264" t="s">
+        <v>267</v>
+      </c>
+      <c r="C264" t="s">
+        <v>279</v>
+      </c>
+      <c r="D264" t="s">
+        <v>37</v>
+      </c>
+      <c r="E264">
+        <v>250000</v>
+      </c>
+      <c r="F264" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A265">
+        <v>7201250141</v>
+      </c>
+      <c r="B265" t="s">
+        <v>267</v>
+      </c>
+      <c r="C265" t="s">
+        <v>280</v>
+      </c>
+      <c r="D265" t="s">
+        <v>37</v>
+      </c>
+      <c r="E265">
+        <v>450000</v>
+      </c>
+      <c r="F265" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A266">
+        <v>7201250141</v>
+      </c>
+      <c r="B266" t="s">
+        <v>267</v>
+      </c>
+      <c r="C266" t="s">
+        <v>281</v>
+      </c>
+      <c r="D266" t="s">
+        <v>37</v>
+      </c>
+      <c r="E266">
+        <v>400000</v>
+      </c>
+      <c r="F266" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A267">
+        <v>7201250141</v>
+      </c>
+      <c r="B267" t="s">
+        <v>267</v>
+      </c>
+      <c r="C267" t="s">
+        <v>282</v>
+      </c>
+      <c r="D267" t="s">
+        <v>68</v>
+      </c>
+      <c r="E267">
+        <v>4375000</v>
+      </c>
+      <c r="F267" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A268">
+        <v>7201250141</v>
+      </c>
+      <c r="B268" t="s">
+        <v>267</v>
+      </c>
+      <c r="C268" t="s">
+        <v>283</v>
+      </c>
+      <c r="D268" t="s">
+        <v>68</v>
+      </c>
+      <c r="E268">
+        <v>4375000</v>
+      </c>
+      <c r="F268" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A269">
+        <v>7201250141</v>
+      </c>
+      <c r="B269" t="s">
+        <v>267</v>
+      </c>
+      <c r="C269" t="s">
+        <v>284</v>
+      </c>
+      <c r="D269" t="s">
+        <v>68</v>
+      </c>
+      <c r="E269">
+        <v>3125000</v>
+      </c>
+      <c r="F269" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A270">
+        <v>7201250141</v>
+      </c>
+      <c r="B270" t="s">
+        <v>267</v>
+      </c>
+      <c r="C270" t="s">
+        <v>285</v>
+      </c>
+      <c r="D270" t="s">
+        <v>68</v>
+      </c>
+      <c r="E270">
+        <v>3125000</v>
+      </c>
+      <c r="F270" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A271">
+        <v>7201250141</v>
+      </c>
+      <c r="B271" t="s">
+        <v>267</v>
+      </c>
+      <c r="C271" t="s">
+        <v>286</v>
+      </c>
+      <c r="D271" t="s">
+        <v>68</v>
+      </c>
+      <c r="E271">
+        <v>4375000</v>
+      </c>
+      <c r="F271" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A272">
+        <v>7201250141</v>
+      </c>
+      <c r="B272" t="s">
+        <v>267</v>
+      </c>
+      <c r="C272" t="s">
+        <v>287</v>
+      </c>
+      <c r="D272" t="s">
+        <v>68</v>
+      </c>
+      <c r="E272">
+        <v>4375000</v>
+      </c>
+      <c r="F272" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A273">
+        <v>7201250141</v>
+      </c>
+      <c r="B273" t="s">
+        <v>267</v>
+      </c>
+      <c r="C273" t="s">
+        <v>288</v>
+      </c>
+      <c r="D273" t="s">
+        <v>68</v>
+      </c>
+      <c r="E273">
+        <v>4375000</v>
+      </c>
+      <c r="F273" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="274" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A274">
+        <v>7201250141</v>
+      </c>
+      <c r="B274" t="s">
+        <v>267</v>
+      </c>
+      <c r="C274" t="s">
+        <v>289</v>
+      </c>
+      <c r="D274" t="s">
+        <v>68</v>
+      </c>
+      <c r="E274">
+        <v>3125000</v>
+      </c>
+      <c r="F274" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="275" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A275">
+        <v>7201250141</v>
+      </c>
+      <c r="B275" t="s">
+        <v>267</v>
+      </c>
+      <c r="C275" t="s">
+        <v>290</v>
+      </c>
+      <c r="D275" t="s">
+        <v>68</v>
+      </c>
+      <c r="E275">
+        <v>3125000</v>
+      </c>
+      <c r="F275" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="276" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A276">
+        <v>7201250141</v>
+      </c>
+      <c r="B276" t="s">
+        <v>267</v>
+      </c>
+      <c r="C276" t="s">
+        <v>291</v>
+      </c>
+      <c r="D276" t="s">
+        <v>68</v>
+      </c>
+      <c r="E276">
+        <v>3125000</v>
+      </c>
+      <c r="F276" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="277" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A277">
+        <v>7201250141</v>
+      </c>
+      <c r="B277" t="s">
+        <v>267</v>
+      </c>
+      <c r="C277" t="s">
+        <v>292</v>
+      </c>
+      <c r="D277" t="s">
+        <v>68</v>
+      </c>
+      <c r="E277">
+        <v>4375000</v>
+      </c>
+      <c r="F277" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="278" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A278">
+        <v>7201250141</v>
+      </c>
+      <c r="B278" t="s">
+        <v>267</v>
+      </c>
+      <c r="C278" t="s">
+        <v>293</v>
+      </c>
+      <c r="D278" t="s">
+        <v>68</v>
+      </c>
+      <c r="E278">
+        <v>4375000</v>
+      </c>
+      <c r="F278" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="279" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A279">
+        <v>7201250141</v>
+      </c>
+      <c r="B279" t="s">
+        <v>267</v>
+      </c>
+      <c r="C279" t="s">
+        <v>294</v>
+      </c>
+      <c r="D279" t="s">
+        <v>68</v>
+      </c>
+      <c r="E279">
+        <v>3125000</v>
+      </c>
+      <c r="F279" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="280" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A280">
+        <v>7201250141</v>
+      </c>
+      <c r="B280" t="s">
+        <v>267</v>
+      </c>
+      <c r="C280" t="s">
+        <v>295</v>
+      </c>
+      <c r="D280" t="s">
+        <v>68</v>
+      </c>
+      <c r="E280">
+        <v>3125000</v>
+      </c>
+      <c r="F280" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="281" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A281">
+        <v>7201250141</v>
+      </c>
+      <c r="B281" t="s">
+        <v>267</v>
+      </c>
+      <c r="C281" t="s">
+        <v>296</v>
+      </c>
+      <c r="D281" t="s">
+        <v>37</v>
+      </c>
+      <c r="E281">
+        <v>19500</v>
+      </c>
+      <c r="F281" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="282" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A282">
+        <v>7201250141</v>
+      </c>
+      <c r="B282" t="s">
+        <v>267</v>
+      </c>
+      <c r="C282" t="s">
+        <v>297</v>
+      </c>
+      <c r="D282" t="s">
+        <v>37</v>
+      </c>
+      <c r="E282">
+        <v>26250</v>
+      </c>
+      <c r="F282" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="283" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A283">
+        <v>7201250141</v>
+      </c>
+      <c r="B283" t="s">
+        <v>267</v>
+      </c>
+      <c r="C283" t="s">
+        <v>298</v>
+      </c>
+      <c r="D283" t="s">
+        <v>37</v>
+      </c>
+      <c r="E283">
+        <v>562500</v>
+      </c>
+      <c r="F283" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="284" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A284">
+        <v>7201250141</v>
+      </c>
+      <c r="B284" t="s">
+        <v>267</v>
+      </c>
+      <c r="C284" t="s">
+        <v>299</v>
+      </c>
+      <c r="D284" t="s">
+        <v>37</v>
+      </c>
+      <c r="E284">
+        <v>812000</v>
+      </c>
+      <c r="F284" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="285" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A285">
+        <v>7201250141</v>
+      </c>
+      <c r="B285" t="s">
+        <v>267</v>
+      </c>
+      <c r="C285" t="s">
+        <v>300</v>
+      </c>
+      <c r="D285" t="s">
+        <v>74</v>
+      </c>
+      <c r="E285">
+        <v>312500</v>
+      </c>
+      <c r="F285" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="286" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A286">
+        <v>7201250141</v>
+      </c>
+      <c r="B286" t="s">
+        <v>267</v>
+      </c>
+      <c r="C286" t="s">
+        <v>301</v>
+      </c>
+      <c r="D286" t="s">
+        <v>37</v>
+      </c>
+      <c r="E286">
+        <v>243750</v>
+      </c>
+      <c r="F286" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="287" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A287">
+        <v>7201250141</v>
+      </c>
+      <c r="B287" t="s">
+        <v>267</v>
+      </c>
+      <c r="C287" t="s">
+        <v>302</v>
+      </c>
+      <c r="D287" t="s">
+        <v>37</v>
+      </c>
+      <c r="E287">
+        <v>55500</v>
+      </c>
+      <c r="F287" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="288" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A288">
+        <v>7201250141</v>
+      </c>
+      <c r="B288" t="s">
+        <v>267</v>
+      </c>
+      <c r="C288" t="s">
+        <v>303</v>
+      </c>
+      <c r="D288" t="s">
+        <v>37</v>
+      </c>
+      <c r="E288">
+        <v>72000</v>
+      </c>
+      <c r="F288" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="289" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A289">
+        <v>7201250141</v>
+      </c>
+      <c r="B289" t="s">
+        <v>267</v>
+      </c>
+      <c r="C289" t="s">
+        <v>304</v>
+      </c>
+      <c r="D289" t="s">
+        <v>37</v>
+      </c>
+      <c r="E289">
+        <v>75000</v>
+      </c>
+      <c r="F289" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="290" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A290">
+        <v>7201250141</v>
+      </c>
+      <c r="B290" t="s">
+        <v>267</v>
+      </c>
+      <c r="C290" t="s">
+        <v>305</v>
+      </c>
+      <c r="D290" t="s">
+        <v>37</v>
+      </c>
+      <c r="E290">
+        <v>500000</v>
+      </c>
+      <c r="F290" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="291" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A291">
+        <v>7201250141</v>
+      </c>
+      <c r="B291" t="s">
+        <v>267</v>
+      </c>
+      <c r="C291" t="s">
+        <v>306</v>
+      </c>
+      <c r="D291" t="s">
+        <v>37</v>
+      </c>
+      <c r="E291">
+        <v>950000</v>
+      </c>
+      <c r="F291" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="292" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A292">
+        <v>7201250141</v>
+      </c>
+      <c r="B292" t="s">
+        <v>267</v>
+      </c>
+      <c r="C292" t="s">
+        <v>307</v>
+      </c>
+      <c r="D292" t="s">
+        <v>37</v>
+      </c>
+      <c r="E292">
+        <v>250000</v>
+      </c>
+      <c r="F292" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="293" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A293">
+        <v>7201250141</v>
+      </c>
+      <c r="B293" t="s">
+        <v>267</v>
+      </c>
+      <c r="C293" t="s">
+        <v>308</v>
+      </c>
+      <c r="D293" t="s">
+        <v>37</v>
+      </c>
+      <c r="E293">
+        <v>122500</v>
+      </c>
+      <c r="F293" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="294" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A294">
+        <v>7201250141</v>
+      </c>
+      <c r="B294" t="s">
+        <v>267</v>
+      </c>
+      <c r="C294" t="s">
+        <v>309</v>
+      </c>
+      <c r="D294" t="s">
+        <v>37</v>
+      </c>
+      <c r="E294">
+        <v>22500</v>
+      </c>
+      <c r="F294" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="295" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A295">
+        <v>7201250141</v>
+      </c>
+      <c r="B295" t="s">
+        <v>267</v>
+      </c>
+      <c r="C295" t="s">
+        <v>310</v>
+      </c>
+      <c r="D295" t="s">
+        <v>37</v>
+      </c>
+      <c r="E295">
+        <v>4500</v>
+      </c>
+      <c r="F295" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="296" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A296">
+        <v>7201250141</v>
+      </c>
+      <c r="B296" t="s">
+        <v>267</v>
+      </c>
+      <c r="C296" t="s">
+        <v>311</v>
+      </c>
+      <c r="D296" t="s">
+        <v>37</v>
+      </c>
+      <c r="E296">
+        <v>6000</v>
+      </c>
+      <c r="F296" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="297" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A297">
+        <v>7201250141</v>
+      </c>
+      <c r="B297" t="s">
+        <v>267</v>
+      </c>
+      <c r="C297" t="s">
+        <v>312</v>
+      </c>
+      <c r="D297" t="s">
+        <v>37</v>
+      </c>
+      <c r="E297">
+        <v>7500</v>
+      </c>
+      <c r="F297" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="298" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A298">
+        <v>7201250141</v>
+      </c>
+      <c r="B298" t="s">
+        <v>267</v>
+      </c>
+      <c r="C298" t="s">
+        <v>313</v>
+      </c>
+      <c r="D298" t="s">
+        <v>37</v>
+      </c>
+      <c r="E298">
+        <v>73125</v>
+      </c>
+      <c r="F298" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="299" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A299">
+        <v>7201250141</v>
+      </c>
+      <c r="B299" t="s">
+        <v>267</v>
+      </c>
+      <c r="C299" t="s">
+        <v>314</v>
+      </c>
+      <c r="D299" t="s">
+        <v>37</v>
+      </c>
+      <c r="E299">
+        <v>62500</v>
+      </c>
+      <c r="F299" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="300" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A300">
+        <v>7201250141</v>
+      </c>
+      <c r="B300" t="s">
+        <v>267</v>
+      </c>
+      <c r="C300" t="s">
+        <v>315</v>
+      </c>
+      <c r="D300" t="s">
+        <v>37</v>
+      </c>
+      <c r="E300">
+        <v>22500</v>
+      </c>
+      <c r="F300" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="301" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A301">
+        <v>7201250141</v>
+      </c>
+      <c r="B301" t="s">
+        <v>267</v>
+      </c>
+      <c r="C301" t="s">
+        <v>316</v>
+      </c>
+      <c r="D301" t="s">
+        <v>37</v>
+      </c>
+      <c r="E301">
+        <v>12000</v>
+      </c>
+      <c r="F301" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="302" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A302">
+        <v>7201250141</v>
+      </c>
+      <c r="B302" t="s">
+        <v>267</v>
+      </c>
+      <c r="C302" t="s">
+        <v>317</v>
+      </c>
+      <c r="D302" t="s">
+        <v>37</v>
+      </c>
+      <c r="E302">
+        <v>62500</v>
+      </c>
+      <c r="F302" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="303" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A303">
+        <v>7201250141</v>
+      </c>
+      <c r="B303" t="s">
+        <v>267</v>
+      </c>
+      <c r="C303" t="s">
+        <v>318</v>
+      </c>
+      <c r="D303" t="s">
+        <v>37</v>
+      </c>
+      <c r="E303">
+        <v>6000</v>
+      </c>
+      <c r="F303" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="304" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A304">
+        <v>7201250141</v>
+      </c>
+      <c r="B304" t="s">
+        <v>267</v>
+      </c>
+      <c r="C304" t="s">
+        <v>319</v>
+      </c>
+      <c r="D304" t="s">
+        <v>37</v>
+      </c>
+      <c r="E304">
+        <v>37500</v>
+      </c>
+      <c r="F304" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="305" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A305">
+        <v>7201250141</v>
+      </c>
+      <c r="B305" t="s">
+        <v>267</v>
+      </c>
+      <c r="C305" t="s">
+        <v>320</v>
+      </c>
+      <c r="D305" t="s">
+        <v>37</v>
+      </c>
+      <c r="E305">
+        <v>10000</v>
+      </c>
+      <c r="F305" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="306" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A306">
+        <v>7201250141</v>
+      </c>
+      <c r="B306" t="s">
+        <v>267</v>
+      </c>
+      <c r="C306" t="s">
+        <v>321</v>
+      </c>
+      <c r="D306" t="s">
+        <v>37</v>
+      </c>
+      <c r="E306">
+        <v>93750</v>
+      </c>
+      <c r="F306" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="307" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A307">
+        <v>7201250141</v>
+      </c>
+      <c r="B307" t="s">
+        <v>267</v>
+      </c>
+      <c r="C307" t="s">
+        <v>322</v>
+      </c>
+      <c r="D307" t="s">
+        <v>37</v>
+      </c>
+      <c r="E307">
+        <v>112500</v>
+      </c>
+      <c r="F307" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="308" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A308">
+        <v>7201250141</v>
+      </c>
+      <c r="B308" t="s">
+        <v>267</v>
+      </c>
+      <c r="C308" t="s">
+        <v>323</v>
+      </c>
+      <c r="D308" t="s">
+        <v>37</v>
+      </c>
+      <c r="E308">
+        <v>21250</v>
+      </c>
+      <c r="F308" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="309" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A309">
+        <v>7201250141</v>
+      </c>
+      <c r="B309" t="s">
+        <v>267</v>
+      </c>
+      <c r="C309" t="s">
+        <v>324</v>
+      </c>
+      <c r="D309" t="s">
+        <v>37</v>
+      </c>
+      <c r="E309">
+        <v>12500</v>
+      </c>
+      <c r="F309" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="310" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A310">
+        <v>7201250141</v>
+      </c>
+      <c r="B310" t="s">
+        <v>267</v>
+      </c>
+      <c r="C310" t="s">
+        <v>325</v>
+      </c>
+      <c r="D310" t="s">
+        <v>37</v>
+      </c>
+      <c r="E310">
+        <v>75000</v>
+      </c>
+      <c r="F310" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="311" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A311">
+        <v>7201250141</v>
+      </c>
+      <c r="B311" t="s">
+        <v>267</v>
+      </c>
+      <c r="C311" t="s">
+        <v>326</v>
+      </c>
+      <c r="D311" t="s">
+        <v>37</v>
+      </c>
+      <c r="E311">
+        <v>10000</v>
+      </c>
+      <c r="F311" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="312" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A312">
+        <v>7201250141</v>
+      </c>
+      <c r="B312" t="s">
+        <v>267</v>
+      </c>
+      <c r="C312" t="s">
+        <v>327</v>
+      </c>
+      <c r="D312" t="s">
+        <v>37</v>
+      </c>
+      <c r="E312">
+        <v>13000</v>
+      </c>
+      <c r="F312" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="313" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A313">
+        <v>7201250141</v>
+      </c>
+      <c r="B313" t="s">
+        <v>267</v>
+      </c>
+      <c r="C313" t="s">
+        <v>328</v>
+      </c>
+      <c r="D313" t="s">
+        <v>37</v>
+      </c>
+      <c r="E313">
+        <v>10000</v>
+      </c>
+      <c r="F313" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="314" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A314">
+        <v>7201250141</v>
+      </c>
+      <c r="B314" t="s">
+        <v>267</v>
+      </c>
+      <c r="C314" t="s">
+        <v>329</v>
+      </c>
+      <c r="D314" t="s">
+        <v>37</v>
+      </c>
+      <c r="E314">
+        <v>12000</v>
+      </c>
+      <c r="F314" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="315" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A315">
+        <v>7201250141</v>
+      </c>
+      <c r="B315" t="s">
+        <v>267</v>
+      </c>
+      <c r="C315" t="s">
+        <v>330</v>
+      </c>
+      <c r="D315" t="s">
+        <v>37</v>
+      </c>
+      <c r="E315">
+        <v>28750</v>
+      </c>
+      <c r="F315" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="316" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A316">
+        <v>7201250141</v>
+      </c>
+      <c r="B316" t="s">
+        <v>267</v>
+      </c>
+      <c r="C316" t="s">
+        <v>331</v>
+      </c>
+      <c r="D316" t="s">
+        <v>37</v>
+      </c>
+      <c r="E316">
+        <v>28750</v>
+      </c>
+      <c r="F316" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="317" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A317">
+        <v>7201250141</v>
+      </c>
+      <c r="B317" t="s">
+        <v>267</v>
+      </c>
+      <c r="C317" t="s">
+        <v>332</v>
+      </c>
+      <c r="D317" t="s">
+        <v>37</v>
+      </c>
+      <c r="E317">
+        <v>10000</v>
+      </c>
+      <c r="F317" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="318" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A318">
+        <v>7201250141</v>
+      </c>
+      <c r="B318" t="s">
+        <v>267</v>
+      </c>
+      <c r="C318" t="s">
+        <v>333</v>
+      </c>
+      <c r="D318" t="s">
+        <v>37</v>
+      </c>
+      <c r="E318">
+        <v>50000</v>
+      </c>
+      <c r="F318" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="319" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A319">
+        <v>7201250141</v>
+      </c>
+      <c r="B319" t="s">
+        <v>267</v>
+      </c>
+      <c r="C319" t="s">
+        <v>334</v>
+      </c>
+      <c r="D319" t="s">
+        <v>37</v>
+      </c>
+      <c r="E319">
+        <v>156250</v>
+      </c>
+      <c r="F319" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="320" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A320">
+        <v>7201250141</v>
+      </c>
+      <c r="B320" t="s">
+        <v>267</v>
+      </c>
+      <c r="C320" t="s">
+        <v>335</v>
+      </c>
+      <c r="D320" t="s">
+        <v>37</v>
+      </c>
+      <c r="E320">
+        <v>31250</v>
+      </c>
+      <c r="F320" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="321" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A321">
+        <v>7201250141</v>
+      </c>
+      <c r="B321" t="s">
+        <v>267</v>
+      </c>
+      <c r="C321" t="s">
+        <v>336</v>
+      </c>
+      <c r="D321" t="s">
+        <v>37</v>
+      </c>
+      <c r="E321">
+        <v>43750</v>
+      </c>
+      <c r="F321" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="322" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A322">
+        <v>7201250141</v>
+      </c>
+      <c r="B322" t="s">
+        <v>267</v>
+      </c>
+      <c r="C322" t="s">
+        <v>337</v>
+      </c>
+      <c r="D322" t="s">
+        <v>37</v>
+      </c>
+      <c r="E322">
+        <v>18750</v>
+      </c>
+      <c r="F322" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="323" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A323">
+        <v>7201250141</v>
+      </c>
+      <c r="B323" t="s">
+        <v>267</v>
+      </c>
+      <c r="C323" t="s">
+        <v>338</v>
+      </c>
+      <c r="D323" t="s">
+        <v>37</v>
+      </c>
+      <c r="E323">
+        <v>25000</v>
+      </c>
+      <c r="F323" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="324" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A324">
+        <v>7201250141</v>
+      </c>
+      <c r="B324" t="s">
+        <v>267</v>
+      </c>
+      <c r="C324" t="s">
+        <v>339</v>
+      </c>
+      <c r="D324" t="s">
+        <v>37</v>
+      </c>
+      <c r="E324">
+        <v>20000</v>
+      </c>
+      <c r="F324" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="325" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A325">
+        <v>7201250141</v>
+      </c>
+      <c r="B325" t="s">
+        <v>267</v>
+      </c>
+      <c r="C325" t="s">
+        <v>340</v>
+      </c>
+      <c r="D325" t="s">
+        <v>37</v>
+      </c>
+      <c r="E325">
+        <v>70000</v>
+      </c>
+      <c r="F325" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="326" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A326">
+        <v>7201250141</v>
+      </c>
+      <c r="B326" t="s">
+        <v>267</v>
+      </c>
+      <c r="C326" t="s">
+        <v>341</v>
+      </c>
+      <c r="D326" t="s">
+        <v>37</v>
+      </c>
+      <c r="E326">
+        <v>31250</v>
+      </c>
+      <c r="F326" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="327" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A327">
+        <v>7201250141</v>
+      </c>
+      <c r="B327" t="s">
+        <v>267</v>
+      </c>
+      <c r="C327" t="s">
+        <v>342</v>
+      </c>
+      <c r="D327" t="s">
+        <v>37</v>
+      </c>
+      <c r="E327">
+        <v>181250</v>
+      </c>
+      <c r="F327" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="328" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A328">
+        <v>7201250141</v>
+      </c>
+      <c r="B328" t="s">
+        <v>267</v>
+      </c>
+      <c r="C328" t="s">
+        <v>343</v>
+      </c>
+      <c r="D328" t="s">
+        <v>68</v>
+      </c>
+      <c r="E328">
+        <v>293750</v>
+      </c>
+      <c r="F328" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="329" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A329">
+        <v>7201250141</v>
+      </c>
+      <c r="B329" t="s">
+        <v>267</v>
+      </c>
+      <c r="C329" t="s">
+        <v>344</v>
+      </c>
+      <c r="D329" t="s">
+        <v>37</v>
+      </c>
+      <c r="E329">
+        <v>120000</v>
+      </c>
+      <c r="F329" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="330" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A330">
+        <v>7201250141</v>
+      </c>
+      <c r="B330" t="s">
+        <v>267</v>
+      </c>
+      <c r="C330" t="s">
+        <v>345</v>
+      </c>
+      <c r="D330" t="s">
+        <v>68</v>
+      </c>
+      <c r="E330">
+        <v>450000</v>
+      </c>
+      <c r="F330" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="331" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A331">
+        <v>7201250141</v>
+      </c>
+      <c r="B331" t="s">
+        <v>267</v>
+      </c>
+      <c r="C331" t="s">
+        <v>346</v>
+      </c>
+      <c r="D331" t="s">
+        <v>68</v>
+      </c>
+      <c r="E331">
+        <v>400000</v>
+      </c>
+      <c r="F331" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="332" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A332">
+        <v>7201250141</v>
+      </c>
+      <c r="B332" t="s">
+        <v>267</v>
+      </c>
+      <c r="C332" t="s">
+        <v>347</v>
+      </c>
+      <c r="D332" t="s">
+        <v>68</v>
+      </c>
+      <c r="E332">
+        <v>375000</v>
+      </c>
+      <c r="F332" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="333" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A333">
+        <v>7201250141</v>
+      </c>
+      <c r="B333" t="s">
+        <v>267</v>
+      </c>
+      <c r="C333" t="s">
+        <v>348</v>
+      </c>
+      <c r="D333" t="s">
+        <v>68</v>
+      </c>
+      <c r="E333">
+        <v>300000</v>
+      </c>
+      <c r="F333" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="334" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A334">
+        <v>7201250141</v>
+      </c>
+      <c r="B334" t="s">
+        <v>267</v>
+      </c>
+      <c r="C334" t="s">
+        <v>349</v>
+      </c>
+      <c r="D334" t="s">
+        <v>68</v>
+      </c>
+      <c r="E334">
+        <v>325000</v>
+      </c>
+      <c r="F334" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="335" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A335">
+        <v>7201250141</v>
+      </c>
+      <c r="B335" t="s">
+        <v>267</v>
+      </c>
+      <c r="C335" t="s">
+        <v>350</v>
+      </c>
+      <c r="D335" t="s">
+        <v>68</v>
+      </c>
+      <c r="E335">
+        <v>150000</v>
+      </c>
+      <c r="F335" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="336" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A336">
+        <v>7201250141</v>
+      </c>
+      <c r="B336" t="s">
+        <v>267</v>
+      </c>
+      <c r="C336" t="s">
+        <v>351</v>
+      </c>
+      <c r="D336" t="s">
+        <v>352</v>
+      </c>
+      <c r="E336">
+        <v>50000</v>
+      </c>
+      <c r="F336" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="337" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A337">
+        <v>7201250141</v>
+      </c>
+      <c r="B337" t="s">
+        <v>267</v>
+      </c>
+      <c r="C337" t="s">
+        <v>351</v>
+      </c>
+      <c r="D337" t="s">
+        <v>352</v>
+      </c>
+      <c r="E337">
+        <v>50000</v>
+      </c>
+      <c r="F337" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="338" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A338">
+        <v>7201250141</v>
+      </c>
+      <c r="B338" t="s">
+        <v>267</v>
+      </c>
+      <c r="C338" t="s">
+        <v>353</v>
+      </c>
+      <c r="D338" t="s">
+        <v>37</v>
+      </c>
+      <c r="E338">
+        <v>75000</v>
+      </c>
+      <c r="F338" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="339" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A339">
+        <v>7201250141</v>
+      </c>
+      <c r="B339" t="s">
+        <v>267</v>
+      </c>
+      <c r="C339" t="s">
+        <v>354</v>
+      </c>
+      <c r="D339" t="s">
+        <v>37</v>
+      </c>
+      <c r="E339">
+        <v>50000</v>
+      </c>
+      <c r="F339" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="340" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A340">
+        <v>7201250141</v>
+      </c>
+      <c r="B340" t="s">
+        <v>267</v>
+      </c>
+      <c r="C340" t="s">
+        <v>355</v>
+      </c>
+      <c r="D340" t="s">
+        <v>37</v>
+      </c>
+      <c r="E340">
+        <v>2000</v>
+      </c>
+      <c r="F340" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="341" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A341">
+        <v>7201250141</v>
+      </c>
+      <c r="B341" t="s">
+        <v>267</v>
+      </c>
+      <c r="C341" t="s">
+        <v>356</v>
+      </c>
+      <c r="D341" t="s">
+        <v>37</v>
+      </c>
+      <c r="E341">
+        <v>7000</v>
+      </c>
+      <c r="F341" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="342" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A342">
+        <v>7201250141</v>
+      </c>
+      <c r="B342" t="s">
+        <v>267</v>
+      </c>
+      <c r="C342" t="s">
+        <v>357</v>
+      </c>
+      <c r="D342" t="s">
+        <v>37</v>
+      </c>
+      <c r="E342">
+        <v>150000</v>
+      </c>
+      <c r="F342" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="343" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A343">
+        <v>7201250141</v>
+      </c>
+      <c r="B343" t="s">
+        <v>267</v>
+      </c>
+      <c r="C343" t="s">
+        <v>358</v>
+      </c>
+      <c r="D343" t="s">
+        <v>37</v>
+      </c>
+      <c r="E343">
+        <v>300000</v>
+      </c>
+      <c r="F343" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="344" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A344">
+        <v>7201250141</v>
+      </c>
+      <c r="B344" t="s">
+        <v>267</v>
+      </c>
+      <c r="C344" t="s">
+        <v>359</v>
+      </c>
+      <c r="D344" t="s">
+        <v>37</v>
+      </c>
+      <c r="E344">
+        <v>93750</v>
+      </c>
+      <c r="F344" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="345" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A345">
+        <v>7201250141</v>
+      </c>
+      <c r="B345" t="s">
+        <v>267</v>
+      </c>
+      <c r="C345" t="s">
+        <v>360</v>
+      </c>
+      <c r="D345" t="s">
+        <v>352</v>
+      </c>
+      <c r="E345">
+        <v>162500</v>
+      </c>
+      <c r="F345" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="346" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A346">
+        <v>7201250141</v>
+      </c>
+      <c r="B346" t="s">
+        <v>267</v>
+      </c>
+      <c r="C346" t="s">
+        <v>361</v>
+      </c>
+      <c r="D346" t="s">
+        <v>37</v>
+      </c>
+      <c r="E346">
+        <v>118750</v>
+      </c>
+      <c r="F346" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="347" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A347">
+        <v>7201250141</v>
+      </c>
+      <c r="B347" t="s">
+        <v>267</v>
+      </c>
+      <c r="C347" t="s">
+        <v>362</v>
+      </c>
+      <c r="D347" t="s">
+        <v>37</v>
+      </c>
+      <c r="E347">
+        <v>250000</v>
+      </c>
+      <c r="F347" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="348" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A348">
+        <v>7201250141</v>
+      </c>
+      <c r="B348" t="s">
+        <v>267</v>
+      </c>
+      <c r="C348" t="s">
+        <v>363</v>
+      </c>
+      <c r="D348" t="s">
+        <v>352</v>
+      </c>
+      <c r="E348">
+        <v>31250</v>
+      </c>
+      <c r="F348" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="349" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A349">
+        <v>7201250141</v>
+      </c>
+      <c r="B349" t="s">
+        <v>267</v>
+      </c>
+      <c r="C349" t="s">
+        <v>364</v>
+      </c>
+      <c r="D349" t="s">
+        <v>37</v>
+      </c>
+      <c r="E349">
+        <v>93750</v>
+      </c>
+      <c r="F349" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="350" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A350">
+        <v>7201250141</v>
+      </c>
+      <c r="B350" t="s">
+        <v>267</v>
+      </c>
+      <c r="C350" t="s">
+        <v>365</v>
+      </c>
+      <c r="D350" t="s">
+        <v>37</v>
+      </c>
+      <c r="E350">
+        <v>93750</v>
+      </c>
+      <c r="F350" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="351" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A351">
+        <v>7201250141</v>
+      </c>
+      <c r="B351" t="s">
+        <v>267</v>
+      </c>
+      <c r="C351" t="s">
+        <v>366</v>
+      </c>
+      <c r="D351" t="s">
+        <v>37</v>
+      </c>
+      <c r="E351">
+        <v>37500</v>
+      </c>
+      <c r="F351" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="352" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A352">
+        <v>7201250141</v>
+      </c>
+      <c r="B352" t="s">
+        <v>267</v>
+      </c>
+      <c r="C352" t="s">
+        <v>367</v>
+      </c>
+      <c r="D352" t="s">
+        <v>37</v>
+      </c>
+      <c r="E352">
+        <v>6250</v>
+      </c>
+      <c r="F352" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="353" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A353">
+        <v>7201250141</v>
+      </c>
+      <c r="B353" t="s">
+        <v>267</v>
+      </c>
+      <c r="C353" t="s">
+        <v>368</v>
+      </c>
+      <c r="D353" t="s">
+        <v>352</v>
+      </c>
+      <c r="E353">
+        <v>31250</v>
+      </c>
+      <c r="F353" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="354" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A354">
+        <v>7201250141</v>
+      </c>
+      <c r="B354" t="s">
+        <v>267</v>
+      </c>
+      <c r="C354" t="s">
+        <v>369</v>
+      </c>
+      <c r="D354" t="s">
+        <v>37</v>
+      </c>
+      <c r="E354">
+        <v>37500</v>
+      </c>
+      <c r="F354" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="355" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A355">
+        <v>7201250141</v>
+      </c>
+      <c r="B355" t="s">
+        <v>267</v>
+      </c>
+      <c r="C355" t="s">
+        <v>370</v>
+      </c>
+      <c r="D355" t="s">
+        <v>37</v>
+      </c>
+      <c r="E355">
+        <v>1875000</v>
+      </c>
+      <c r="F355" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="356" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A356">
+        <v>7201250141</v>
+      </c>
+      <c r="B356" t="s">
+        <v>267</v>
+      </c>
+      <c r="C356" t="s">
+        <v>371</v>
+      </c>
+      <c r="D356" t="s">
+        <v>37</v>
+      </c>
+      <c r="E356">
+        <v>125000</v>
+      </c>
+      <c r="F356" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="357" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A357">
+        <v>7201250141</v>
+      </c>
+      <c r="B357" t="s">
+        <v>267</v>
+      </c>
+      <c r="C357" t="s">
+        <v>372</v>
+      </c>
+      <c r="D357" t="s">
+        <v>373</v>
+      </c>
+      <c r="E357">
+        <v>712500</v>
+      </c>
+      <c r="F357" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="358" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A358">
+        <v>7201250141</v>
+      </c>
+      <c r="B358" t="s">
+        <v>267</v>
+      </c>
+      <c r="C358" t="s">
+        <v>372</v>
+      </c>
+      <c r="D358" t="s">
+        <v>373</v>
+      </c>
+      <c r="E358">
+        <v>712500</v>
+      </c>
+      <c r="F358" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="359" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A359">
+        <v>7201250141</v>
+      </c>
+      <c r="B359" t="s">
+        <v>267</v>
+      </c>
+      <c r="C359" t="s">
+        <v>374</v>
+      </c>
+      <c r="D359" t="s">
+        <v>37</v>
+      </c>
+      <c r="E359">
+        <v>22500</v>
+      </c>
+      <c r="F359" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="360" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A360">
+        <v>7201250141</v>
+      </c>
+      <c r="B360" t="s">
+        <v>267</v>
+      </c>
+      <c r="C360" t="s">
+        <v>375</v>
+      </c>
+      <c r="D360" t="s">
+        <v>37</v>
+      </c>
+      <c r="E360">
+        <v>60033</v>
+      </c>
+      <c r="F360" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="361" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A361">
+        <v>7201250141</v>
+      </c>
+      <c r="B361" t="s">
+        <v>376</v>
+      </c>
+      <c r="C361" t="s">
+        <v>377</v>
+      </c>
+      <c r="D361" t="s">
+        <v>65</v>
+      </c>
+      <c r="E361">
+        <v>1000000</v>
+      </c>
+      <c r="F361" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="362" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A362">
+        <v>7201250141</v>
+      </c>
+      <c r="B362" t="s">
+        <v>376</v>
+      </c>
+      <c r="C362" t="s">
+        <v>378</v>
+      </c>
+      <c r="D362" t="s">
+        <v>65</v>
+      </c>
+      <c r="E362">
+        <v>7600000</v>
+      </c>
+      <c r="F362" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="363" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A363">
+        <v>7201250141</v>
+      </c>
+      <c r="B363" t="s">
+        <v>376</v>
+      </c>
+      <c r="C363" t="s">
+        <v>379</v>
+      </c>
+      <c r="D363" t="s">
+        <v>65</v>
+      </c>
+      <c r="E363">
+        <v>7500000</v>
+      </c>
+      <c r="F363" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="364" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A364">
+        <v>7201250141</v>
+      </c>
+      <c r="B364" t="s">
+        <v>376</v>
+      </c>
+      <c r="C364" t="s">
+        <v>380</v>
+      </c>
+      <c r="D364" t="s">
+        <v>8</v>
+      </c>
+      <c r="E364">
+        <v>17500000</v>
+      </c>
+      <c r="F364" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="365" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A365">
+        <v>7201250141</v>
+      </c>
+      <c r="B365" t="s">
+        <v>376</v>
+      </c>
+      <c r="C365" t="s">
+        <v>381</v>
+      </c>
+      <c r="D365" t="s">
+        <v>8</v>
+      </c>
+      <c r="E365">
+        <v>20000000</v>
+      </c>
+      <c r="F365" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="366" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A366">
+        <v>7201250141</v>
+      </c>
+      <c r="B366" t="s">
+        <v>376</v>
+      </c>
+      <c r="C366" t="s">
+        <v>382</v>
+      </c>
+      <c r="D366" t="s">
+        <v>8</v>
+      </c>
+      <c r="E366">
+        <v>10000000</v>
+      </c>
+      <c r="F366" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="367" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A367">
+        <v>7201250141</v>
+      </c>
+      <c r="B367" t="s">
+        <v>376</v>
+      </c>
+      <c r="C367" t="s">
+        <v>383</v>
+      </c>
+      <c r="D367" t="s">
+        <v>8</v>
+      </c>
+      <c r="E367">
+        <v>7500000</v>
+      </c>
+      <c r="F367" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="368" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A368">
+        <v>7201250141</v>
+      </c>
+      <c r="B368" t="s">
+        <v>376</v>
+      </c>
+      <c r="C368" t="s">
+        <v>384</v>
+      </c>
+      <c r="D368" t="s">
+        <v>8</v>
+      </c>
+      <c r="E368">
+        <v>10000000</v>
+      </c>
+      <c r="F368" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="369" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A369">
+        <v>7201250141</v>
+      </c>
+      <c r="B369" t="s">
+        <v>376</v>
+      </c>
+      <c r="C369" t="s">
+        <v>385</v>
+      </c>
+      <c r="D369" t="s">
+        <v>8</v>
+      </c>
+      <c r="E369">
+        <v>25000000</v>
+      </c>
+      <c r="F369" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="370" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A370">
+        <v>7201250141</v>
+      </c>
+      <c r="B370" t="s">
+        <v>376</v>
+      </c>
+      <c r="C370" t="s">
+        <v>386</v>
+      </c>
+      <c r="D370" t="s">
+        <v>37</v>
+      </c>
+      <c r="E370">
+        <v>65000</v>
+      </c>
+      <c r="F370" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="371" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A371">
+        <v>7201250141</v>
+      </c>
+      <c r="B371" t="s">
+        <v>376</v>
+      </c>
+      <c r="C371" t="s">
+        <v>387</v>
+      </c>
+      <c r="D371" t="s">
+        <v>37</v>
+      </c>
+      <c r="E371">
+        <v>33000</v>
+      </c>
+      <c r="F371" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="372" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A372">
+        <v>7201250141</v>
+      </c>
+      <c r="B372" t="s">
+        <v>376</v>
+      </c>
+      <c r="C372" t="s">
+        <v>388</v>
+      </c>
+      <c r="D372" t="s">
+        <v>352</v>
+      </c>
+      <c r="E372">
+        <v>25000</v>
+      </c>
+      <c r="F372" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="373" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A373">
+        <v>7201250141</v>
+      </c>
+      <c r="B373" t="s">
+        <v>389</v>
+      </c>
+      <c r="C373" t="s">
+        <v>390</v>
+      </c>
+      <c r="D373" t="s">
+        <v>352</v>
+      </c>
+      <c r="E373">
+        <v>750000</v>
+      </c>
+      <c r="F373" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="374" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A374">
+        <v>7201250141</v>
+      </c>
+      <c r="B374" t="s">
+        <v>389</v>
+      </c>
+      <c r="C374" t="s">
+        <v>390</v>
+      </c>
+      <c r="D374" t="s">
+        <v>391</v>
+      </c>
+      <c r="E374">
+        <v>750000</v>
+      </c>
+      <c r="F374" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="375" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A375">
+        <v>7201250141</v>
+      </c>
+      <c r="B375" t="s">
+        <v>389</v>
+      </c>
+      <c r="C375" t="s">
+        <v>390</v>
+      </c>
+      <c r="D375" t="s">
+        <v>391</v>
+      </c>
+      <c r="E375">
+        <v>750000</v>
+      </c>
+      <c r="F375" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="376" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A376">
+        <v>7201250141</v>
+      </c>
+      <c r="B376" t="s">
+        <v>389</v>
+      </c>
+      <c r="C376" t="s">
+        <v>392</v>
+      </c>
+      <c r="D376" t="s">
+        <v>391</v>
+      </c>
+      <c r="E376">
+        <v>250000</v>
+      </c>
+      <c r="F376" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="377" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A377">
+        <v>7201250141</v>
+      </c>
+      <c r="B377" t="s">
+        <v>389</v>
+      </c>
+      <c r="C377" t="s">
+        <v>393</v>
+      </c>
+      <c r="D377" t="s">
+        <v>391</v>
+      </c>
+      <c r="E377">
+        <v>350000</v>
+      </c>
+      <c r="F377" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="378" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A378">
+        <v>7201250141</v>
+      </c>
+      <c r="B378" t="s">
+        <v>389</v>
+      </c>
+      <c r="C378" t="s">
+        <v>394</v>
+      </c>
+      <c r="D378" t="s">
+        <v>391</v>
+      </c>
+      <c r="E378">
+        <v>275000</v>
+      </c>
+      <c r="F378" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="379" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A379">
+        <v>7201250141</v>
+      </c>
+      <c r="B379" t="s">
+        <v>389</v>
+      </c>
+      <c r="C379" t="s">
+        <v>395</v>
+      </c>
+      <c r="D379" t="s">
+        <v>391</v>
+      </c>
+      <c r="E379">
+        <v>500000</v>
+      </c>
+      <c r="F379" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="380" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A380">
+        <v>7201250141</v>
+      </c>
+      <c r="B380" t="s">
+        <v>389</v>
+      </c>
+      <c r="C380" t="s">
+        <v>396</v>
+      </c>
+      <c r="D380" t="s">
+        <v>391</v>
+      </c>
+      <c r="E380">
+        <v>500000</v>
+      </c>
+      <c r="F380" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="381" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A381">
+        <v>7201250141</v>
+      </c>
+      <c r="B381" t="s">
+        <v>389</v>
+      </c>
+      <c r="C381" t="s">
+        <v>397</v>
+      </c>
+      <c r="D381" t="s">
+        <v>391</v>
+      </c>
+      <c r="E381">
+        <v>325000</v>
+      </c>
+      <c r="F381" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="382" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A382">
+        <v>7201250141</v>
+      </c>
+      <c r="B382" t="s">
+        <v>389</v>
+      </c>
+      <c r="C382" t="s">
+        <v>398</v>
+      </c>
+      <c r="D382" t="s">
+        <v>391</v>
+      </c>
+      <c r="E382">
+        <v>750000</v>
+      </c>
+      <c r="F382" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="383" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A383">
+        <v>7201250141</v>
+      </c>
+      <c r="B383" t="s">
+        <v>389</v>
+      </c>
+      <c r="C383" t="s">
+        <v>399</v>
+      </c>
+      <c r="D383" t="s">
+        <v>391</v>
+      </c>
+      <c r="E383">
+        <v>650000</v>
+      </c>
+      <c r="F383" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="384" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A384">
+        <v>7201250141</v>
+      </c>
+      <c r="B384" t="s">
+        <v>389</v>
+      </c>
+      <c r="C384" t="s">
+        <v>400</v>
+      </c>
+      <c r="D384" t="s">
+        <v>391</v>
+      </c>
+      <c r="E384">
+        <v>500000</v>
+      </c>
+      <c r="F384" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="385" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A385">
+        <v>7201250141</v>
+      </c>
+      <c r="B385" t="s">
+        <v>389</v>
+      </c>
+      <c r="C385" t="s">
+        <v>401</v>
+      </c>
+      <c r="D385" t="s">
+        <v>391</v>
+      </c>
+      <c r="E385">
+        <v>500000</v>
+      </c>
+      <c r="F385" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="386" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A386">
+        <v>7201250141</v>
+      </c>
+      <c r="B386" t="s">
+        <v>389</v>
+      </c>
+      <c r="C386" t="s">
+        <v>402</v>
+      </c>
+      <c r="D386" t="s">
+        <v>391</v>
+      </c>
+      <c r="E386">
+        <v>500000</v>
+      </c>
+      <c r="F386" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="387" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A387">
+        <v>7201250141</v>
+      </c>
+      <c r="B387" t="s">
+        <v>389</v>
+      </c>
+      <c r="C387" t="s">
+        <v>403</v>
+      </c>
+      <c r="D387" t="s">
+        <v>391</v>
+      </c>
+      <c r="E387">
+        <v>500000</v>
+      </c>
+      <c r="F387" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="388" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A388">
+        <v>7201250141</v>
+      </c>
+      <c r="B388" t="s">
+        <v>389</v>
+      </c>
+      <c r="C388" t="s">
+        <v>404</v>
+      </c>
+      <c r="D388" t="s">
+        <v>391</v>
+      </c>
+      <c r="E388">
+        <v>500000</v>
+      </c>
+      <c r="F388" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="389" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A389">
+        <v>7201250141</v>
+      </c>
+      <c r="B389" t="s">
+        <v>389</v>
+      </c>
+      <c r="C389" t="s">
+        <v>405</v>
+      </c>
+      <c r="D389" t="s">
+        <v>391</v>
+      </c>
+      <c r="E389">
+        <v>500000</v>
+      </c>
+      <c r="F389" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="390" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A390">
+        <v>7201250141</v>
+      </c>
+      <c r="B390" t="s">
+        <v>389</v>
+      </c>
+      <c r="C390" t="s">
+        <v>406</v>
+      </c>
+      <c r="D390" t="s">
+        <v>391</v>
+      </c>
+      <c r="E390">
+        <v>600000</v>
+      </c>
+      <c r="F390" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="391" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A391">
+        <v>7201250141</v>
+      </c>
+      <c r="B391" t="s">
+        <v>407</v>
+      </c>
+      <c r="C391" t="s">
+        <v>408</v>
+      </c>
+      <c r="D391" t="s">
+        <v>352</v>
+      </c>
+      <c r="E391">
+        <v>150000</v>
+      </c>
+      <c r="F391" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="392" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A392">
+        <v>7201250141</v>
+      </c>
+      <c r="B392" t="s">
+        <v>407</v>
+      </c>
+      <c r="C392" t="s">
+        <v>409</v>
+      </c>
+      <c r="D392" t="s">
+        <v>352</v>
+      </c>
+      <c r="E392">
+        <v>200000</v>
+      </c>
+      <c r="F392" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="393" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A393">
+        <v>7201250141</v>
+      </c>
+      <c r="B393" t="s">
+        <v>407</v>
+      </c>
+      <c r="C393" t="s">
+        <v>410</v>
+      </c>
+      <c r="D393" t="s">
+        <v>352</v>
+      </c>
+      <c r="E393">
+        <v>175000</v>
+      </c>
+      <c r="F393" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="394" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A394">
+        <v>7201250141</v>
+      </c>
+      <c r="B394" t="s">
+        <v>407</v>
+      </c>
+      <c r="C394" t="s">
+        <v>411</v>
+      </c>
+      <c r="D394" t="s">
+        <v>352</v>
+      </c>
+      <c r="E394">
+        <v>125000</v>
+      </c>
+      <c r="F394" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="395" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A395">
+        <v>7201250141</v>
+      </c>
+      <c r="B395" t="s">
+        <v>407</v>
+      </c>
+      <c r="C395" t="s">
+        <v>412</v>
+      </c>
+      <c r="D395" t="s">
+        <v>352</v>
+      </c>
+      <c r="E395">
+        <v>150000</v>
+      </c>
+      <c r="F395" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="396" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A396">
+        <v>7201250141</v>
+      </c>
+      <c r="B396" t="s">
+        <v>407</v>
+      </c>
+      <c r="C396" t="s">
+        <v>413</v>
+      </c>
+      <c r="D396" t="s">
+        <v>352</v>
+      </c>
+      <c r="E396">
+        <v>200000</v>
+      </c>
+      <c r="F396" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="397" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A397">
+        <v>7201250141</v>
+      </c>
+      <c r="B397" t="s">
+        <v>407</v>
+      </c>
+      <c r="C397" t="s">
+        <v>414</v>
+      </c>
+      <c r="D397" t="s">
+        <v>352</v>
+      </c>
+      <c r="E397">
+        <v>200000</v>
+      </c>
+      <c r="F397" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="398" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A398">
+        <v>7201250141</v>
+      </c>
+      <c r="B398" t="s">
+        <v>407</v>
+      </c>
+      <c r="C398" t="s">
+        <v>415</v>
+      </c>
+      <c r="D398" t="s">
+        <v>352</v>
+      </c>
+      <c r="E398">
+        <v>150000</v>
+      </c>
+      <c r="F398" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="399" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A399">
+        <v>7201250141</v>
+      </c>
+      <c r="B399" t="s">
+        <v>407</v>
+      </c>
+      <c r="C399" t="s">
+        <v>416</v>
+      </c>
+      <c r="D399" t="s">
+        <v>352</v>
+      </c>
+      <c r="E399">
+        <v>100000</v>
+      </c>
+      <c r="F399" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="400" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A400">
+        <v>7201250141</v>
+      </c>
+      <c r="B400" t="s">
+        <v>407</v>
+      </c>
+      <c r="C400" t="s">
+        <v>417</v>
+      </c>
+      <c r="D400" t="s">
+        <v>352</v>
+      </c>
+      <c r="E400">
+        <v>100000</v>
+      </c>
+      <c r="F400" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="401" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A401">
+        <v>7201250141</v>
+      </c>
+      <c r="B401" t="s">
+        <v>407</v>
+      </c>
+      <c r="C401" t="s">
+        <v>418</v>
+      </c>
+      <c r="D401" t="s">
+        <v>352</v>
+      </c>
+      <c r="E401">
+        <v>125000</v>
+      </c>
+      <c r="F401" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="402" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A402">
+        <v>7201250141</v>
+      </c>
+      <c r="B402" t="s">
+        <v>407</v>
+      </c>
+      <c r="C402" t="s">
+        <v>419</v>
+      </c>
+      <c r="D402" t="s">
+        <v>420</v>
+      </c>
+      <c r="E402">
+        <v>250000</v>
+      </c>
+      <c r="F402" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="403" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A403">
+        <v>7201250141</v>
+      </c>
+      <c r="B403" t="s">
+        <v>421</v>
+      </c>
+      <c r="C403" t="s">
+        <v>422</v>
+      </c>
+      <c r="D403" t="s">
+        <v>352</v>
+      </c>
+      <c r="E403">
+        <v>20000000</v>
+      </c>
+      <c r="F403" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="404" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A404">
+        <v>7201250141</v>
+      </c>
+      <c r="B404" t="s">
+        <v>421</v>
+      </c>
+      <c r="C404" t="s">
+        <v>422</v>
+      </c>
+      <c r="D404" t="s">
+        <v>65</v>
+      </c>
+      <c r="E404">
+        <v>20000000</v>
+      </c>
+      <c r="F404" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="405" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A405">
+        <v>7201250141</v>
+      </c>
+      <c r="B405" t="s">
+        <v>421</v>
+      </c>
+      <c r="C405" t="s">
+        <v>423</v>
+      </c>
+      <c r="D405" t="s">
+        <v>65</v>
+      </c>
+      <c r="E405">
+        <v>50000000</v>
+      </c>
+      <c r="F405" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="406" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A406">
+        <v>7201250141</v>
+      </c>
+      <c r="B406" t="s">
+        <v>421</v>
+      </c>
+      <c r="C406" t="s">
+        <v>424</v>
+      </c>
+      <c r="D406" t="s">
+        <v>65</v>
+      </c>
+      <c r="E406">
+        <v>28000000</v>
+      </c>
+      <c r="F406" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="407" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A407">
+        <v>7201250141</v>
+      </c>
+      <c r="B407" t="s">
+        <v>421</v>
+      </c>
+      <c r="C407" t="s">
+        <v>425</v>
+      </c>
+      <c r="D407" t="s">
+        <v>65</v>
+      </c>
+      <c r="E407">
+        <v>22400000</v>
+      </c>
+      <c r="F407" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="408" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A408">
+        <v>7201250141</v>
+      </c>
+      <c r="B408" t="s">
+        <v>421</v>
+      </c>
+      <c r="C408" t="s">
+        <v>426</v>
+      </c>
+      <c r="D408" t="s">
+        <v>65</v>
+      </c>
+      <c r="E408">
+        <v>15400000</v>
+      </c>
+      <c r="F408" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="409" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A409">
+        <v>7201250141</v>
+      </c>
+      <c r="B409" t="s">
+        <v>421</v>
+      </c>
+      <c r="C409" t="s">
+        <v>427</v>
+      </c>
+      <c r="D409" t="s">
+        <v>65</v>
+      </c>
+      <c r="E409">
+        <v>32200000</v>
+      </c>
+      <c r="F409" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="410" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A410">
+        <v>7201250141</v>
+      </c>
+      <c r="B410" t="s">
+        <v>421</v>
+      </c>
+      <c r="C410" t="s">
+        <v>428</v>
+      </c>
+      <c r="D410" t="s">
+        <v>65</v>
+      </c>
+      <c r="E410">
+        <v>29400000</v>
+      </c>
+      <c r="F410" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="411" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A411">
+        <v>7201250141</v>
+      </c>
+      <c r="B411" t="s">
+        <v>421</v>
+      </c>
+      <c r="C411" t="s">
+        <v>429</v>
+      </c>
+      <c r="D411" t="s">
+        <v>65</v>
+      </c>
+      <c r="E411">
+        <v>59000000</v>
+      </c>
+      <c r="F411" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="412" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A412">
+        <v>7201250141</v>
+      </c>
+      <c r="B412" t="s">
+        <v>421</v>
+      </c>
+      <c r="C412" t="s">
+        <v>430</v>
+      </c>
+      <c r="D412" t="s">
+        <v>65</v>
+      </c>
+      <c r="E412">
+        <v>22400000</v>
+      </c>
+      <c r="F412" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="413" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A413">
+        <v>7201250141</v>
+      </c>
+      <c r="B413" t="s">
+        <v>421</v>
+      </c>
+      <c r="C413" t="s">
+        <v>431</v>
+      </c>
+      <c r="D413" t="s">
+        <v>65</v>
+      </c>
+      <c r="E413">
+        <v>27300000</v>
+      </c>
+      <c r="F413" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="414" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A414">
+        <v>7201250141</v>
+      </c>
+      <c r="B414" t="s">
+        <v>421</v>
+      </c>
+      <c r="C414" t="s">
+        <v>432</v>
+      </c>
+      <c r="D414" t="s">
+        <v>65</v>
+      </c>
+      <c r="E414">
+        <v>27300000</v>
+      </c>
+      <c r="F414" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="415" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A415" t="s">
+        <v>433</v>
+      </c>
+      <c r="B415" t="s">
+        <v>421</v>
+      </c>
+      <c r="C415" t="s">
+        <v>434</v>
+      </c>
+      <c r="D415" t="s">
+        <v>420</v>
+      </c>
+      <c r="E415">
+        <v>1000000</v>
+      </c>
+      <c r="F415" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="416" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A416">
+        <v>7201250141</v>
+      </c>
+      <c r="B416" t="s">
+        <v>267</v>
+      </c>
+      <c r="C416" t="s">
+        <v>435</v>
+      </c>
+      <c r="D416" t="s">
+        <v>37</v>
+      </c>
+      <c r="E416">
+        <v>7500</v>
+      </c>
+      <c r="F416" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="417" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A417">
+        <v>7201250141</v>
+      </c>
+      <c r="B417" t="s">
+        <v>267</v>
+      </c>
+      <c r="C417" t="s">
+        <v>436</v>
+      </c>
+      <c r="D417" t="s">
+        <v>37</v>
+      </c>
+      <c r="E417">
+        <v>53300</v>
+      </c>
+      <c r="F417" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="418" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A418">
+        <v>7201250141</v>
+      </c>
+      <c r="B418" t="s">
+        <v>267</v>
+      </c>
+      <c r="C418" t="s">
+        <v>437</v>
+      </c>
+      <c r="D418" t="s">
+        <v>37</v>
+      </c>
+      <c r="E418">
+        <v>32500</v>
+      </c>
+      <c r="F418" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="419" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A419">
+        <v>7201250141</v>
+      </c>
+      <c r="B419" t="s">
+        <v>267</v>
+      </c>
+      <c r="C419" t="s">
+        <v>438</v>
+      </c>
+      <c r="D419" t="s">
+        <v>37</v>
+      </c>
+      <c r="E419">
+        <v>84500</v>
+      </c>
+      <c r="F419" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="420" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A420">
+        <v>7201250141</v>
+      </c>
+      <c r="B420" t="s">
+        <v>267</v>
+      </c>
+      <c r="C420" t="s">
+        <v>439</v>
+      </c>
+      <c r="D420" t="s">
+        <v>37</v>
+      </c>
+      <c r="E420">
+        <v>26000</v>
+      </c>
+      <c r="F420" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="421" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A421">
+        <v>7201250141</v>
+      </c>
+      <c r="B421" t="s">
+        <v>267</v>
+      </c>
+      <c r="C421" t="s">
+        <v>440</v>
+      </c>
+      <c r="D421" t="s">
+        <v>37</v>
+      </c>
+      <c r="E421">
+        <v>32500</v>
+      </c>
+      <c r="F421" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="422" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A422">
+        <v>7201250141</v>
+      </c>
+      <c r="B422" t="s">
+        <v>267</v>
+      </c>
+      <c r="C422" t="s">
+        <v>441</v>
+      </c>
+      <c r="D422" t="s">
+        <v>37</v>
+      </c>
+      <c r="E422">
+        <v>45500</v>
+      </c>
+      <c r="F422" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="423" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A423">
+        <v>7201250141</v>
+      </c>
+      <c r="B423" t="s">
+        <v>267</v>
+      </c>
+      <c r="C423" t="s">
+        <v>442</v>
+      </c>
+      <c r="D423" t="s">
+        <v>37</v>
+      </c>
+      <c r="E423">
+        <v>9750</v>
+      </c>
+      <c r="F423" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="424" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A424">
+        <v>7201250141</v>
+      </c>
+      <c r="B424" t="s">
+        <v>267</v>
+      </c>
+      <c r="C424" t="s">
+        <v>443</v>
+      </c>
+      <c r="D424" t="s">
+        <v>37</v>
+      </c>
+      <c r="E424">
+        <v>31200</v>
+      </c>
+      <c r="F424" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="425" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A425">
+        <v>7201250141</v>
+      </c>
+      <c r="B425" t="s">
+        <v>267</v>
+      </c>
+      <c r="C425" t="s">
+        <v>444</v>
+      </c>
+      <c r="D425" t="s">
+        <v>37</v>
+      </c>
+      <c r="E425">
+        <v>32500</v>
+      </c>
+      <c r="F425" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="426" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A426">
+        <v>7201250141</v>
+      </c>
+      <c r="B426" t="s">
+        <v>267</v>
+      </c>
+      <c r="C426" t="s">
+        <v>445</v>
+      </c>
+      <c r="D426" t="s">
+        <v>37</v>
+      </c>
+      <c r="E426">
+        <v>32500</v>
+      </c>
+      <c r="F426" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="427" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A427">
+        <v>7201250141</v>
+      </c>
+      <c r="B427" t="s">
+        <v>267</v>
+      </c>
+      <c r="C427" t="s">
+        <v>446</v>
+      </c>
+      <c r="D427" t="s">
+        <v>37</v>
+      </c>
+      <c r="E427">
+        <v>19500</v>
+      </c>
+      <c r="F427" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="428" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A428">
+        <v>7201250141</v>
+      </c>
+      <c r="B428" t="s">
+        <v>267</v>
+      </c>
+      <c r="C428" t="s">
+        <v>447</v>
+      </c>
+      <c r="D428" t="s">
+        <v>37</v>
+      </c>
+      <c r="E428">
+        <v>13000</v>
+      </c>
+      <c r="F428" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="429" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A429">
+        <v>7201250141</v>
+      </c>
+      <c r="B429" t="s">
+        <v>267</v>
+      </c>
+      <c r="C429" t="s">
+        <v>448</v>
+      </c>
+      <c r="D429" t="s">
+        <v>37</v>
+      </c>
+      <c r="E429">
+        <v>9750</v>
+      </c>
+      <c r="F429" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="430" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A430">
+        <v>7201250141</v>
+      </c>
+      <c r="B430" t="s">
+        <v>267</v>
+      </c>
+      <c r="C430" t="s">
+        <v>449</v>
+      </c>
+      <c r="D430" t="s">
+        <v>37</v>
+      </c>
+      <c r="E430">
+        <v>19500</v>
+      </c>
+      <c r="F430" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="431" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A431">
+        <v>7201250141</v>
+      </c>
+      <c r="B431" t="s">
+        <v>267</v>
+      </c>
+      <c r="C431" t="s">
+        <v>450</v>
+      </c>
+      <c r="D431" t="s">
+        <v>37</v>
+      </c>
+      <c r="E431">
+        <v>9750</v>
+      </c>
+      <c r="F431" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="432" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A432">
+        <v>7201250141</v>
+      </c>
+      <c r="B432" t="s">
+        <v>267</v>
+      </c>
+      <c r="C432" t="s">
+        <v>451</v>
+      </c>
+      <c r="D432" t="s">
+        <v>37</v>
+      </c>
+      <c r="E432">
+        <v>9750</v>
+      </c>
+      <c r="F432" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="433" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A433">
+        <v>7201250141</v>
+      </c>
+      <c r="B433" t="s">
+        <v>267</v>
+      </c>
+      <c r="C433" t="s">
+        <v>452</v>
+      </c>
+      <c r="D433" t="s">
+        <v>37</v>
+      </c>
+      <c r="E433">
+        <v>15600</v>
+      </c>
+      <c r="F433" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="434" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A434">
+        <v>7201250141</v>
+      </c>
+      <c r="B434" t="s">
+        <v>267</v>
+      </c>
+      <c r="C434" t="s">
+        <v>453</v>
+      </c>
+      <c r="D434" t="s">
+        <v>37</v>
+      </c>
+      <c r="E434">
+        <v>32500</v>
+      </c>
+      <c r="F434" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="435" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A435">
+        <v>7201250141</v>
+      </c>
+      <c r="B435" t="s">
+        <v>267</v>
+      </c>
+      <c r="C435" t="s">
+        <v>454</v>
+      </c>
+      <c r="D435" t="s">
+        <v>37</v>
+      </c>
+      <c r="E435">
+        <v>32500</v>
+      </c>
+      <c r="F435" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="436" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A436">
+        <v>7201250141</v>
+      </c>
+      <c r="B436" t="s">
+        <v>267</v>
+      </c>
+      <c r="C436" t="s">
+        <v>455</v>
+      </c>
+      <c r="D436" t="s">
+        <v>37</v>
+      </c>
+      <c r="E436">
+        <v>32500</v>
+      </c>
+      <c r="F436" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="437" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A437">
+        <v>7201250141</v>
+      </c>
+      <c r="B437" t="s">
+        <v>267</v>
+      </c>
+      <c r="C437" t="s">
+        <v>456</v>
+      </c>
+      <c r="D437" t="s">
+        <v>37</v>
+      </c>
+      <c r="E437">
+        <v>1625000</v>
+      </c>
+      <c r="F437" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="438" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A438">
+        <v>7201250141</v>
+      </c>
+      <c r="B438" t="s">
+        <v>267</v>
+      </c>
+      <c r="C438" t="s">
+        <v>457</v>
+      </c>
+      <c r="D438" t="s">
+        <v>37</v>
+      </c>
+      <c r="E438">
+        <v>325000</v>
+      </c>
+      <c r="F438" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="439" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A439">
+        <v>7201250141</v>
+      </c>
+      <c r="B439" t="s">
+        <v>267</v>
+      </c>
+      <c r="C439" t="s">
+        <v>458</v>
+      </c>
+      <c r="D439" t="s">
+        <v>37</v>
+      </c>
+      <c r="E439">
+        <v>19500000</v>
+      </c>
+      <c r="F439" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="440" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A440">
+        <v>7201250141</v>
+      </c>
+      <c r="B440" t="s">
+        <v>459</v>
+      </c>
+      <c r="C440" t="s">
+        <v>458</v>
+      </c>
+      <c r="D440" t="s">
+        <v>37</v>
+      </c>
+      <c r="E440">
+        <v>19500000</v>
+      </c>
+      <c r="F440" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="441" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A441">
+        <v>7201250141</v>
+      </c>
+      <c r="B441" t="s">
+        <v>459</v>
+      </c>
+      <c r="C441" t="s">
+        <v>460</v>
+      </c>
+      <c r="D441" t="s">
+        <v>30</v>
+      </c>
+      <c r="E441">
+        <v>3250000</v>
+      </c>
+      <c r="F441" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="442" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A442">
+        <v>7201250141</v>
+      </c>
+      <c r="B442" t="s">
+        <v>459</v>
+      </c>
+      <c r="C442" t="s">
+        <v>461</v>
+      </c>
+      <c r="D442" t="s">
+        <v>30</v>
+      </c>
+      <c r="E442">
+        <v>3900000</v>
+      </c>
+      <c r="F442" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="443" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A443">
+        <v>7201250141</v>
+      </c>
+      <c r="B443" t="s">
+        <v>462</v>
+      </c>
+      <c r="C443" t="s">
+        <v>461</v>
+      </c>
+      <c r="D443" t="s">
+        <v>30</v>
+      </c>
+      <c r="E443">
+        <v>3900000</v>
+      </c>
+      <c r="F443" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="444" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A444">
+        <v>7201250141</v>
+      </c>
+      <c r="B444" t="s">
+        <v>462</v>
+      </c>
+      <c r="C444" t="s">
+        <v>463</v>
+      </c>
+      <c r="D444" t="s">
+        <v>30</v>
+      </c>
+      <c r="E444">
+        <v>5600000</v>
+      </c>
+      <c r="F444" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="445" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A445">
+        <v>7201250141</v>
+      </c>
+      <c r="B445" t="s">
+        <v>462</v>
+      </c>
+      <c r="C445" t="s">
+        <v>464</v>
+      </c>
+      <c r="D445" t="s">
+        <v>30</v>
+      </c>
+      <c r="E445">
+        <v>8400000</v>
+      </c>
+      <c r="F445" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="446" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A446">
+        <v>7201250141</v>
+      </c>
+      <c r="B446" t="s">
+        <v>462</v>
+      </c>
+      <c r="C446" t="s">
+        <v>465</v>
+      </c>
+      <c r="D446" t="s">
+        <v>30</v>
+      </c>
+      <c r="E446">
+        <v>7000000</v>
+      </c>
+      <c r="F446" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="447" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A447">
+        <v>7201250141</v>
+      </c>
+      <c r="B447" t="s">
+        <v>462</v>
+      </c>
+      <c r="C447" t="s">
+        <v>466</v>
+      </c>
+      <c r="D447" t="s">
+        <v>30</v>
+      </c>
+      <c r="E447">
+        <v>9100000</v>
+      </c>
+      <c r="F447" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="448" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A448">
+        <v>7201250141</v>
+      </c>
+      <c r="B448" t="s">
+        <v>462</v>
+      </c>
+      <c r="C448" t="s">
+        <v>467</v>
+      </c>
+      <c r="D448" t="s">
+        <v>30</v>
+      </c>
+      <c r="E448">
+        <v>10500000</v>
+      </c>
+      <c r="F448" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="449" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A449">
+        <v>7201250141</v>
+      </c>
+      <c r="B449" t="s">
+        <v>462</v>
+      </c>
+      <c r="C449" t="s">
+        <v>468</v>
+      </c>
+      <c r="D449" t="s">
+        <v>30</v>
+      </c>
+      <c r="E449">
+        <v>10500000</v>
+      </c>
+      <c r="F449" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="450" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A450">
+        <v>7201250141</v>
+      </c>
+      <c r="B450" t="s">
+        <v>462</v>
+      </c>
+      <c r="C450" t="s">
+        <v>469</v>
+      </c>
+      <c r="D450" t="s">
+        <v>30</v>
+      </c>
+      <c r="E450">
+        <v>14000000</v>
+      </c>
+      <c r="F450" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="451" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A451">
+        <v>7201250141</v>
+      </c>
+      <c r="B451" t="s">
+        <v>462</v>
+      </c>
+      <c r="C451" t="s">
+        <v>470</v>
+      </c>
+      <c r="D451" t="s">
+        <v>30</v>
+      </c>
+      <c r="E451">
+        <v>14000000</v>
+      </c>
+      <c r="F451" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="452" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A452">
+        <v>7201250141</v>
+      </c>
+      <c r="B452" t="s">
+        <v>462</v>
+      </c>
+      <c r="C452" t="s">
+        <v>471</v>
+      </c>
+      <c r="D452" t="s">
+        <v>30</v>
+      </c>
+      <c r="E452">
+        <v>25200000</v>
+      </c>
+      <c r="F452" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="453" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A453">
+        <v>7201250141</v>
+      </c>
+      <c r="B453" t="s">
+        <v>407</v>
+      </c>
+      <c r="C453" t="s">
+        <v>419</v>
+      </c>
+      <c r="D453" t="s">
+        <v>420</v>
+      </c>
+      <c r="E453">
+        <v>250000</v>
+      </c>
+      <c r="F453" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F453" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/database_penyimpanan_aman/database_master_referensi.xlsx
+++ b/database_penyimpanan_aman/database_master_referensi.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F456"/>
+  <dimension ref="A1:F454"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,7 +474,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -504,7 +504,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -564,7 +564,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -624,7 +624,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -654,7 +654,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -714,7 +714,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -894,7 +894,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -1164,7 +1164,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -1615,7 +1615,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -1885,7 +1885,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -1915,7 +1915,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -1975,7 +1975,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -2095,7 +2095,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -2125,7 +2125,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -2155,7 +2155,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -2305,7 +2305,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -2395,7 +2395,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -2425,7 +2425,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -2515,7 +2515,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -2575,7 +2575,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -2665,7 +2665,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -2725,7 +2725,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -2785,7 +2785,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -2815,7 +2815,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -2845,7 +2845,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -2935,7 +2935,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -2965,7 +2965,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -2995,7 +2995,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3085,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -3115,7 +3115,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -3145,7 +3145,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -3235,7 +3235,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -3325,7 +3325,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -3355,7 +3355,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -3385,7 +3385,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -3415,7 +3415,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -3445,7 +3445,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -3475,7 +3475,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -3535,7 +3535,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -3565,7 +3565,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -3595,7 +3595,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -3625,7 +3625,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -3655,7 +3655,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -3685,7 +3685,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -3745,7 +3745,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -3775,7 +3775,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -3805,7 +3805,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -3865,7 +3865,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -3895,7 +3895,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -3925,7 +3925,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4015,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -4045,7 +4045,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -4075,7 +4075,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -4105,7 +4105,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -4135,7 +4135,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -4165,7 +4165,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -4195,7 +4195,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -4225,7 +4225,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -4255,7 +4255,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -4315,7 +4315,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -4345,7 +4345,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -4375,7 +4375,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -4405,7 +4405,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -4435,7 +4435,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -4465,7 +4465,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -4495,7 +4495,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -4525,7 +4525,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -4555,7 +4555,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -4585,7 +4585,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -4615,7 +4615,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -4645,7 +4645,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -4675,7 +4675,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -4705,7 +4705,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -4735,7 +4735,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -4765,7 +4765,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -4795,7 +4795,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -4855,7 +4855,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -4885,7 +4885,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -4915,7 +4915,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -4945,7 +4945,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -4975,7 +4975,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -5005,7 +5005,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -5035,7 +5035,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -5065,7 +5065,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -5095,7 +5095,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -5125,7 +5125,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -5155,7 +5155,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -5185,7 +5185,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -5215,7 +5215,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -5245,7 +5245,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -5275,7 +5275,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -5335,7 +5335,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -5365,7 +5365,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -5395,7 +5395,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -5455,7 +5455,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -5485,7 +5485,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5545,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -5575,7 +5575,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -5605,7 +5605,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -5635,7 +5635,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -5665,7 +5665,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -5695,7 +5695,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -5725,7 +5725,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -5755,7 +5755,7 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -5785,7 +5785,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -5815,7 +5815,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -5845,7 +5845,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -5905,7 +5905,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -5935,7 +5935,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -5965,7 +5965,7 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -5995,7 +5995,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -6025,7 +6025,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -6055,7 +6055,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -6085,7 +6085,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -6115,7 +6115,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -6145,7 +6145,7 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -6175,7 +6175,7 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -6205,7 +6205,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -6235,7 +6235,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -6265,7 +6265,7 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -6295,7 +6295,7 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -6325,7 +6325,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -6355,7 +6355,7 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -6415,7 +6415,7 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -6445,7 +6445,7 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -6475,7 +6475,7 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -6505,7 +6505,7 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -6535,7 +6535,7 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -6565,7 +6565,7 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -6595,7 +6595,7 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -6625,7 +6625,7 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -6655,7 +6655,7 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -6685,7 +6685,7 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -6715,7 +6715,7 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -6745,7 +6745,7 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -6805,7 +6805,7 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -6835,7 +6835,7 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -6865,7 +6865,7 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -6895,7 +6895,7 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -6925,7 +6925,7 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -6955,7 +6955,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -6985,7 +6985,7 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -7015,7 +7015,7 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -7045,7 +7045,7 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -7075,7 +7075,7 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -7105,7 +7105,7 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -7135,7 +7135,7 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -7165,7 +7165,7 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -7195,7 +7195,7 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -7225,7 +7225,7 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -7255,7 +7255,7 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -7285,7 +7285,7 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -7315,7 +7315,7 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -7345,7 +7345,7 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -7375,7 +7375,7 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -7435,7 +7435,7 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -7465,7 +7465,7 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -7495,7 +7495,7 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -7555,7 +7555,7 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -7585,7 +7585,7 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -7615,7 +7615,7 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -7645,7 +7645,7 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -7675,7 +7675,7 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -7705,7 +7705,7 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -7735,7 +7735,7 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -7765,7 +7765,7 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -7795,7 +7795,7 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -7825,7 +7825,7 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -7855,7 +7855,7 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -7885,7 +7885,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -7915,7 +7915,7 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -7945,7 +7945,7 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -7967,15 +7967,15 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Ltr</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>750000</v>
+        <v>25000</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -7992,20 +7992,20 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+          <t>Besi Plat 3 mm (240 x 120 cm),</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Ltr</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>25000</v>
+        <v>1500000</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -8022,20 +8022,20 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+          <t>Besi Plat 2 mm,</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Ltr</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>25000</v>
+        <v>1200000</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -8052,7 +8052,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Besi Plat 3 mm (240 x 120 cm),</t>
+          <t>Cat Besi, 5kg</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -8061,11 +8061,11 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>1500000</v>
+        <v>344500</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -8082,7 +8082,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Besi Plat 2 mm,</t>
+          <t>Cat Kayu, 5kg</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -8091,11 +8091,11 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>1200000</v>
+        <v>344500</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -8112,7 +8112,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Cat Besi, 5kg</t>
+          <t>Cat Tembok, 5kg</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -8121,11 +8121,11 @@
         </is>
       </c>
       <c r="E257" t="n">
-        <v>344500</v>
+        <v>150000</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -8142,7 +8142,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Cat Kayu, 5kg</t>
+          <t>Minyak Tiner</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -8151,11 +8151,11 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>344500</v>
+        <v>195000</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -8172,20 +8172,20 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Cat Tembok, 5kg</t>
+          <t>Kawat bronjong galvanis, SNI</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>150000</v>
+        <v>37500</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -8202,7 +8202,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Minyak Tiner</t>
+          <t>Kawat Las, E-6010/ E-6011 (5 kg)</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -8211,11 +8211,11 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>195000</v>
+        <v>312000</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -8232,20 +8232,20 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Kawat bronjong galvanis, SNI</t>
+          <t>Kawat Las - E-6012 (5kg)</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>37500</v>
+        <v>250000</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -8262,7 +8262,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Kawat Las, E-6010/ E-6011 (5 kg)</t>
+          <t>Kawat Las - E-6013 (5kg)</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -8271,11 +8271,11 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>312000</v>
+        <v>250000</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Kawat Las - E-6012 (5kg)</t>
+          <t>Kawat Las - E-7024 (5kg)</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -8301,11 +8301,11 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>250000</v>
+        <v>450000</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Kawat Las - E-6013 (5kg)</t>
+          <t>Kawat Las - LB52U/E7018 (5kg)</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -8331,11 +8331,11 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>250000</v>
+        <v>400000</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -8352,20 +8352,20 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Kawat Las - E-7024 (5kg)</t>
+          <t>Kayu Balok, 6x12x400  Kayu kelas 1</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="E265" t="n">
-        <v>450000</v>
+        <v>4375000</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -8382,20 +8382,20 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Kawat Las - LB52U/E7018 (5kg)</t>
+          <t>Kayu Balok, 5x10x400 Kayu kelas 1</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="E266" t="n">
-        <v>400000</v>
+        <v>4375000</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -8412,7 +8412,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Kayu Balok, 6x12x400  Kayu kelas 1</t>
+          <t>Kayu Balok, 6x12x400  Kayu kelas 2</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -8421,11 +8421,11 @@
         </is>
       </c>
       <c r="E267" t="n">
-        <v>4375000</v>
+        <v>3125000</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -8442,7 +8442,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Kayu Balok, 5x10x400 Kayu kelas 1</t>
+          <t>Kayu Balok, 6x12x400  Kayu kelas 2</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -8451,11 +8451,11 @@
         </is>
       </c>
       <c r="E268" t="n">
-        <v>4375000</v>
+        <v>3125000</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -8472,7 +8472,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Kayu Balok, 6x12x400  Kayu kelas 2</t>
+          <t>Kayu Reng 2x3x400 Kayu kelas 1</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -8481,11 +8481,11 @@
         </is>
       </c>
       <c r="E269" t="n">
-        <v>3125000</v>
+        <v>4375000</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Kayu Balok, 6x12x400  Kayu kelas 2</t>
+          <t>Kayu Kaso/lata, 4x6x400 Kayu kelas 1</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -8511,11 +8511,11 @@
         </is>
       </c>
       <c r="E270" t="n">
-        <v>3125000</v>
+        <v>4375000</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -8532,7 +8532,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Kayu Reng 2x3x400 Kayu kelas 1</t>
+          <t>Kayu Kaso/lata, 5x5x400 Kayu kelas 1</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -8545,7 +8545,7 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -8562,7 +8562,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Kayu Kaso/lata, 4x6x400 Kayu kelas 1</t>
+          <t>Kayu Reng 2x3x400 Kayu kelas 2</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -8571,11 +8571,11 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>4375000</v>
+        <v>3125000</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -8592,7 +8592,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Kayu Kaso/lata, 5x5x400 Kayu kelas 1</t>
+          <t>Kayu Kaso/lata, 4x6x400 Kayu kelas 2</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -8601,11 +8601,11 @@
         </is>
       </c>
       <c r="E273" t="n">
-        <v>4375000</v>
+        <v>3125000</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -8622,7 +8622,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Kayu Reng 2x3x400 Kayu kelas 2</t>
+          <t>Kayu Kaso/lata, 5x5x400 Kayu kelas 2</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -8635,7 +8635,7 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -8652,7 +8652,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Kayu Kaso/lata, 4x6x400 Kayu kelas 2</t>
+          <t>Kayu Papan, 2x20x400 Kayu kelas 1</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -8661,11 +8661,11 @@
         </is>
       </c>
       <c r="E275" t="n">
-        <v>3125000</v>
+        <v>4375000</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -8682,7 +8682,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Kayu Kaso/lata, 5x5x400 Kayu kelas 2</t>
+          <t>Kayu Papan, 3x20x400 Kayu kelas 1</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -8691,11 +8691,11 @@
         </is>
       </c>
       <c r="E276" t="n">
-        <v>3125000</v>
+        <v>4375000</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Kayu Papan, 2x20x400 Kayu kelas 1</t>
+          <t>Kayu Papan, 2x20x400 Kayu kelas 2</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -8721,11 +8721,11 @@
         </is>
       </c>
       <c r="E277" t="n">
-        <v>4375000</v>
+        <v>3125000</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -8742,7 +8742,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Kayu Papan, 3x20x400 Kayu kelas 1</t>
+          <t>Kayu Papan, 3x20x400 Kayu kelas 2</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -8751,11 +8751,11 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>4375000</v>
+        <v>3125000</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -8772,20 +8772,20 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Kayu Papan, 2x20x400 Kayu kelas 2</t>
+          <t>Kuas 2"</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="E279" t="n">
-        <v>3125000</v>
+        <v>19500</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -8802,20 +8802,20 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Kayu Papan, 3x20x400 Kayu kelas 2</t>
+          <t>Kuas 3"</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="E280" t="n">
-        <v>3125000</v>
+        <v>26250</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -8832,7 +8832,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Kuas 2"</t>
+          <t>Pipa Besi 1,5"x2mmx 6meter,</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -8841,11 +8841,11 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>19500</v>
+        <v>562500</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -8862,7 +8862,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Kuas 3"</t>
+          <t>Pipa Besi 2"x2mmx6 meter,</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -8871,11 +8871,11 @@
         </is>
       </c>
       <c r="E282" t="n">
-        <v>26250</v>
+        <v>812000</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -8892,20 +8892,20 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Pipa Besi 1,5"x2mmx 6meter,</t>
+          <t>Pipa Besi 2"x2mmx6 meter, Pipa Galvanis ukuran 1"</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E283" t="n">
-        <v>562500</v>
+        <v>312500</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -8922,7 +8922,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Pipa Besi 2"x2mmx6 meter,</t>
+          <t>Pipa PVC AW 2"  (4m)</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -8931,11 +8931,11 @@
         </is>
       </c>
       <c r="E284" t="n">
-        <v>812000</v>
+        <v>243750</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -8952,20 +8952,20 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Pipa Besi 2"x2mmx6 meter, Pipa Galvanis ukuran 1"</t>
+          <t>Pipa PVC AW 1/2" (4m)</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="E285" t="n">
-        <v>312500</v>
+        <v>55500</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -8982,7 +8982,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Pipa PVC AW 2"  (4m)</t>
+          <t>Pipa PVC AW 3/4" (4m)</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -8991,11 +8991,11 @@
         </is>
       </c>
       <c r="E286" t="n">
-        <v>243750</v>
+        <v>72000</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -9012,7 +9012,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Pipa PVC AW 1/2" (4m)</t>
+          <t>Pipa PVC AW 1" (4m)</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -9021,11 +9021,11 @@
         </is>
       </c>
       <c r="E287" t="n">
-        <v>55500</v>
+        <v>75000</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -9042,7 +9042,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Pipa PVC AW 3/4" (4m)</t>
+          <t>Pipa PVC AW 4" (4m)</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -9051,11 +9051,11 @@
         </is>
       </c>
       <c r="E288" t="n">
-        <v>72000</v>
+        <v>500000</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Pipa PVC AW 1" (4m)</t>
+          <t>Pipa PVC AW 6" (4m)</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -9081,11 +9081,11 @@
         </is>
       </c>
       <c r="E289" t="n">
-        <v>75000</v>
+        <v>950000</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -9102,7 +9102,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Pipa PVC AW 4" (4m)</t>
+          <t>Pipa PVC AW 3"</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -9111,11 +9111,11 @@
         </is>
       </c>
       <c r="E290" t="n">
-        <v>500000</v>
+        <v>250000</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -9132,7 +9132,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Pipa PVC AW 6" (4m)</t>
+          <t>Pipa PVC AW 1 1/2"</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -9141,11 +9141,11 @@
         </is>
       </c>
       <c r="E291" t="n">
-        <v>950000</v>
+        <v>122500</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -9162,7 +9162,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Pipa PVC AW 3"</t>
+          <t>Knee PVC 2"</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -9171,11 +9171,11 @@
         </is>
       </c>
       <c r="E292" t="n">
-        <v>250000</v>
+        <v>22500</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -9192,7 +9192,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Pipa PVC AW 1 1/2"</t>
+          <t>Knee PVC 1/2"</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -9201,11 +9201,11 @@
         </is>
       </c>
       <c r="E293" t="n">
-        <v>122500</v>
+        <v>4500</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -9222,7 +9222,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Knee PVC 2"</t>
+          <t>Knee PVC 3/4"</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -9231,11 +9231,11 @@
         </is>
       </c>
       <c r="E294" t="n">
-        <v>22500</v>
+        <v>6000</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -9252,7 +9252,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Knee PVC 1/2"</t>
+          <t>Knee PVC 1"</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -9261,11 +9261,11 @@
         </is>
       </c>
       <c r="E295" t="n">
-        <v>4500</v>
+        <v>7500</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -9282,7 +9282,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Knee PVC 3/4"</t>
+          <t>Knee PVC 4"</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -9291,11 +9291,11 @@
         </is>
       </c>
       <c r="E296" t="n">
-        <v>6000</v>
+        <v>73125</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -9312,7 +9312,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Knee PVC 1"</t>
+          <t>Knee PVC 6"</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -9321,11 +9321,11 @@
         </is>
       </c>
       <c r="E297" t="n">
-        <v>7500</v>
+        <v>62500</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -9342,7 +9342,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Knee PVC 4"</t>
+          <t>Knee PVC 3"</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -9351,11 +9351,11 @@
         </is>
       </c>
       <c r="E298" t="n">
-        <v>73125</v>
+        <v>22500</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Knee PVC 6"</t>
+          <t>Knee PVC 1 1/2"</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -9381,11 +9381,11 @@
         </is>
       </c>
       <c r="E299" t="n">
-        <v>62500</v>
+        <v>12000</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -9402,7 +9402,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Knee PVC 3"</t>
+          <t>Tee  PVC 2"</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -9411,11 +9411,11 @@
         </is>
       </c>
       <c r="E300" t="n">
-        <v>22500</v>
+        <v>62500</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -9432,7 +9432,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Knee PVC 1 1/2"</t>
+          <t>Tee PVC 1/2"</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -9441,11 +9441,11 @@
         </is>
       </c>
       <c r="E301" t="n">
-        <v>12000</v>
+        <v>6000</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Tee  PVC 2"</t>
+          <t>Tee PVC 3/4"</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -9471,11 +9471,11 @@
         </is>
       </c>
       <c r="E302" t="n">
-        <v>62500</v>
+        <v>37500</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -9492,7 +9492,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Tee PVC 1/2"</t>
+          <t>Tee PVC 1"</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -9501,11 +9501,11 @@
         </is>
       </c>
       <c r="E303" t="n">
-        <v>6000</v>
+        <v>10000</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -9522,7 +9522,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Tee PVC 3/4"</t>
+          <t>Tee PVC 4"</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -9531,11 +9531,11 @@
         </is>
       </c>
       <c r="E304" t="n">
-        <v>37500</v>
+        <v>93750</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -9552,7 +9552,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Tee PVC 1"</t>
+          <t>Tee PVC 6"</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -9561,11 +9561,11 @@
         </is>
       </c>
       <c r="E305" t="n">
-        <v>10000</v>
+        <v>112500</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -9582,7 +9582,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Tee PVC 4"</t>
+          <t>Tee PVC 3"</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -9591,11 +9591,11 @@
         </is>
       </c>
       <c r="E306" t="n">
-        <v>93750</v>
+        <v>21250</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -9612,7 +9612,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Tee PVC 6"</t>
+          <t>Tee PVC 1 1/2"</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -9621,11 +9621,11 @@
         </is>
       </c>
       <c r="E307" t="n">
-        <v>112500</v>
+        <v>12500</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -9642,7 +9642,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Tee PVC 3"</t>
+          <t>Lem pipa PVC</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -9651,11 +9651,11 @@
         </is>
       </c>
       <c r="E308" t="n">
-        <v>21250</v>
+        <v>75000</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -9672,7 +9672,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Tee PVC 1 1/2"</t>
+          <t>Seal tape</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -9681,11 +9681,11 @@
         </is>
       </c>
       <c r="E309" t="n">
-        <v>12500</v>
+        <v>10000</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -9702,7 +9702,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Lem pipa PVC</t>
+          <t>Sock Drat luar PVC 1"</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -9711,11 +9711,11 @@
         </is>
       </c>
       <c r="E310" t="n">
-        <v>75000</v>
+        <v>13000</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -9732,7 +9732,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Seal tape</t>
+          <t>Sock Drat luar PVC 1/2"</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -9745,7 +9745,7 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -9762,7 +9762,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Sock Drat luar PVC 1"</t>
+          <t>Sock Operan 1" ke 3/4"</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -9771,11 +9771,11 @@
         </is>
       </c>
       <c r="E312" t="n">
-        <v>13000</v>
+        <v>12000</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Sock Drat luar PVC 1/2"</t>
+          <t>Sock Operan 1-1/2" - 2"</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -9801,11 +9801,11 @@
         </is>
       </c>
       <c r="E313" t="n">
-        <v>10000</v>
+        <v>28750</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -9822,7 +9822,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Sock Operan 1" ke 3/4"</t>
+          <t>Sock PVC 2"</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -9831,11 +9831,11 @@
         </is>
       </c>
       <c r="E314" t="n">
-        <v>12000</v>
+        <v>28750</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -9852,7 +9852,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Sock Operan 1-1/2" - 2"</t>
+          <t>Sock PVC 3/4"</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -9861,11 +9861,11 @@
         </is>
       </c>
       <c r="E315" t="n">
-        <v>28750</v>
+        <v>10000</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Sock PVC 2"</t>
+          <t>Sock PVC 4"</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -9891,11 +9891,11 @@
         </is>
       </c>
       <c r="E316" t="n">
-        <v>28750</v>
+        <v>50000</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -9912,7 +9912,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Sock PVC 3/4"</t>
+          <t>Plastik   rope 6 mm</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -9921,11 +9921,11 @@
         </is>
       </c>
       <c r="E317" t="n">
-        <v>10000</v>
+        <v>156250</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -9942,7 +9942,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Sock PVC 4"</t>
+          <t>kran 1/2"</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -9951,11 +9951,11 @@
         </is>
       </c>
       <c r="E318" t="n">
-        <v>50000</v>
+        <v>31250</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -9972,7 +9972,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Plastik   rope 6 mm</t>
+          <t>kran 3/4"</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -9981,11 +9981,11 @@
         </is>
       </c>
       <c r="E319" t="n">
-        <v>156250</v>
+        <v>43750</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -10002,7 +10002,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>kran 1/2"</t>
+          <t>stop kran 1/2"</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -10011,11 +10011,11 @@
         </is>
       </c>
       <c r="E320" t="n">
-        <v>31250</v>
+        <v>18750</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -10032,7 +10032,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>kran 3/4"</t>
+          <t>stop kran 3/4"</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -10041,11 +10041,11 @@
         </is>
       </c>
       <c r="E321" t="n">
-        <v>43750</v>
+        <v>25000</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -10062,7 +10062,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>stop kran 1/2"</t>
+          <t>Tawas</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -10071,11 +10071,11 @@
         </is>
       </c>
       <c r="E322" t="n">
-        <v>18750</v>
+        <v>20000</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -10092,7 +10092,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>stop kran 3/4"</t>
+          <t>HDPE Geomembrane 0.75mm</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -10101,11 +10101,11 @@
         </is>
       </c>
       <c r="E323" t="n">
-        <v>25000</v>
+        <v>70000</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -10122,7 +10122,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Tawas</t>
+          <t>Terpaulin A12</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -10131,11 +10131,11 @@
         </is>
       </c>
       <c r="E324" t="n">
-        <v>20000</v>
+        <v>31250</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -10152,7 +10152,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>HDPE Geomembrane 0.75mm</t>
+          <t>Thinner @ 5 Ltr</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -10161,11 +10161,11 @@
         </is>
       </c>
       <c r="E325" t="n">
-        <v>70000</v>
+        <v>181250</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -10182,20 +10182,20 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Terpaulin A12</t>
+          <t>Pasir</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="E326" t="n">
-        <v>31250</v>
+        <v>293750</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -10212,7 +10212,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Thinner @ 5 Ltr</t>
+          <t>Semen PC 50 kg</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -10221,11 +10221,11 @@
         </is>
       </c>
       <c r="E327" t="n">
-        <v>181250</v>
+        <v>120000</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -10242,7 +10242,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Pasir</t>
+          <t>Batu Split 3-5 atau 5-7</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -10251,11 +10251,11 @@
         </is>
       </c>
       <c r="E328" t="n">
-        <v>293750</v>
+        <v>450000</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -10272,20 +10272,20 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Semen PC 50 kg</t>
+          <t>Batu Agregate A</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="E329" t="n">
-        <v>120000</v>
+        <v>400000</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -10302,7 +10302,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Batu Split 3-5 atau 5-7</t>
+          <t>Batu Agregate B</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -10311,11 +10311,11 @@
         </is>
       </c>
       <c r="E330" t="n">
-        <v>450000</v>
+        <v>375000</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -10332,7 +10332,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Batu Agregate A</t>
+          <t>Sirtu</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -10341,11 +10341,11 @@
         </is>
       </c>
       <c r="E331" t="n">
-        <v>400000</v>
+        <v>300000</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -10362,7 +10362,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Batu Agregate B</t>
+          <t>Batu Kali</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -10371,11 +10371,11 @@
         </is>
       </c>
       <c r="E332" t="n">
-        <v>375000</v>
+        <v>325000</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -10392,7 +10392,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Sirtu</t>
+          <t>Tanah timbunan</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -10401,11 +10401,11 @@
         </is>
       </c>
       <c r="E333" t="n">
-        <v>300000</v>
+        <v>150000</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -10422,20 +10422,20 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Batu Kali</t>
+          <t>Paku Zeng</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="E334" t="n">
-        <v>325000</v>
+        <v>50000</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -10452,20 +10452,20 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Tanah timbunan</t>
+          <t>Paku Zeng</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="E335" t="n">
-        <v>150000</v>
+        <v>50000</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -10482,20 +10482,20 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Paku Zeng</t>
+          <t>Zeng Gelombang BJLS 0.2</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="E336" t="n">
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -10512,12 +10512,12 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Paku Zeng</t>
+          <t>Paku Tripleks</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="E337" t="n">
@@ -10525,7 +10525,7 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -10542,7 +10542,7 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Zeng Gelombang BJLS 0.2</t>
+          <t>Batu Bata,</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -10551,11 +10551,11 @@
         </is>
       </c>
       <c r="E338" t="n">
-        <v>75000</v>
+        <v>2000</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -10572,7 +10572,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Paku Tripleks</t>
+          <t>Paving Block</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -10581,11 +10581,11 @@
         </is>
       </c>
       <c r="E339" t="n">
-        <v>50000</v>
+        <v>7000</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -10602,7 +10602,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Batu Bata,</t>
+          <t>Baja Ringan C75 0.75mm @ 6 meter</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -10611,11 +10611,11 @@
         </is>
       </c>
       <c r="E340" t="n">
-        <v>2000</v>
+        <v>150000</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -10632,7 +10632,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Paving Block</t>
+          <t>Spandex thk. 0.3mm @6m</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -10641,11 +10641,11 @@
         </is>
       </c>
       <c r="E341" t="n">
-        <v>7000</v>
+        <v>300000</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -10662,7 +10662,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Baja Ringan C75 0.75mm @ 6 meter</t>
+          <t>Bubungan Spandex 0.3mm @3 m</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -10671,11 +10671,11 @@
         </is>
       </c>
       <c r="E342" t="n">
-        <v>150000</v>
+        <v>93750</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -10692,20 +10692,20 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Spandex thk. 0.3mm @6m</t>
+          <t>Baut baja ringan</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="E343" t="n">
-        <v>300000</v>
+        <v>162500</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -10722,7 +10722,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Bubungan Spandex 0.3mm @3 m</t>
+          <t>Besi 10mm SNI</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -10731,11 +10731,11 @@
         </is>
       </c>
       <c r="E344" t="n">
-        <v>93750</v>
+        <v>118750</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -10752,20 +10752,20 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Baut baja ringan</t>
+          <t>Besi 13mm SNI</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="E345" t="n">
-        <v>162500</v>
+        <v>250000</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -10782,20 +10782,20 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Besi 10mm SNI</t>
+          <t>Kawat bendrat</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="E346" t="n">
-        <v>118750</v>
+        <v>31250</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -10812,7 +10812,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Besi 13mm SNI</t>
+          <t>Cangkul</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -10821,11 +10821,11 @@
         </is>
       </c>
       <c r="E347" t="n">
-        <v>250000</v>
+        <v>93750</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -10842,20 +10842,20 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Kawat bendrat</t>
+          <t>Skop</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="E348" t="n">
-        <v>31250</v>
+        <v>93750</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -10872,7 +10872,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Cangkul</t>
+          <t>Sendok adukan</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -10881,11 +10881,11 @@
         </is>
       </c>
       <c r="E349" t="n">
-        <v>93750</v>
+        <v>37500</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -10902,7 +10902,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Skop</t>
+          <t>Jarum karung</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -10911,11 +10911,11 @@
         </is>
       </c>
       <c r="E350" t="n">
-        <v>93750</v>
+        <v>6250</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -10932,20 +10932,20 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Sendok adukan</t>
+          <t>Tali Rafia rope</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="E351" t="n">
-        <v>37500</v>
+        <v>31250</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -10962,7 +10962,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Jarum karung</t>
+          <t>Meteran @5m</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -10971,11 +10971,11 @@
         </is>
       </c>
       <c r="E352" t="n">
-        <v>6250</v>
+        <v>37500</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -10992,20 +10992,20 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Tali Rafia rope</t>
+          <t>Pompa air</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="E353" t="n">
-        <v>31250</v>
+        <v>1875000</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -11022,7 +11022,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Meteran @5m</t>
+          <t>Foot valve/klep</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -11031,11 +11031,11 @@
         </is>
       </c>
       <c r="E354" t="n">
-        <v>37500</v>
+        <v>125000</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -11052,20 +11052,20 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Pompa air</t>
+          <t>Kabel 2x1.5mm NYA/NYM @50m</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Roll</t>
         </is>
       </c>
       <c r="E355" t="n">
-        <v>1875000</v>
+        <v>712500</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -11082,20 +11082,20 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Foot valve/klep</t>
+          <t>Kabel 2x1.5mm NYA/NYM @50m</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Roll</t>
         </is>
       </c>
       <c r="E356" t="n">
-        <v>125000</v>
+        <v>712500</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -11112,20 +11112,20 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Kabel 2x1.5mm NYA/NYM @50m</t>
+          <t>Isolasi kabel</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>Roll</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="E357" t="n">
-        <v>712500</v>
+        <v>22500</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -11142,20 +11142,20 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Kabel 2x1.5mm NYA/NYM @50m</t>
+          <t>Gembok kunci</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>Roll</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="E358" t="n">
-        <v>712500</v>
+        <v>60033</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -11167,25 +11167,25 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Isolasi kabel</t>
+          <t>Fogging Harga termasuk personil, kebutuhan transportasi dari/ke lokasi pemboran serta PPE personil</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="E359" t="n">
-        <v>22500</v>
+        <v>1000000</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -11197,25 +11197,25 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Gembok kunci</t>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="E360" t="n">
-        <v>60033</v>
+        <v>7600000</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -11232,7 +11232,7 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Fogging Harga termasuk personil, kebutuhan transportasi dari/ke lokasi pemboran serta PPE personil</t>
+          <t>Mobilization/ Demobilization 20 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -11241,11 +11241,11 @@
         </is>
       </c>
       <c r="E361" t="n">
-        <v>1000000</v>
+        <v>7500000</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -11262,20 +11262,20 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="E362" t="n">
-        <v>7600000</v>
+        <v>17500000</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -11292,20 +11292,20 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization 20 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+          <t>Portacamp - Living camp,ukuran 40FT (8 sleepers)</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="E363" t="n">
-        <v>7500000</v>
+        <v>20000000</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -11322,7 +11322,7 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
+          <t>Portacamp - Living camp,  ukuran 20FT (4 sleepers)</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -11331,11 +11331,11 @@
         </is>
       </c>
       <c r="E364" t="n">
-        <v>17500000</v>
+        <v>10000000</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -11352,7 +11352,7 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Portacamp - Living camp,ukuran 40FT (8 sleepers)</t>
+          <t>Portacamp - Dining room, ukuran 20FT</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -11361,11 +11361,11 @@
         </is>
       </c>
       <c r="E365" t="n">
-        <v>20000000</v>
+        <v>7500000</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -11382,7 +11382,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Portacamp - Living camp,  ukuran 20FT (4 sleepers)</t>
+          <t>Portacamp - Kitchen ukuran 40FT</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -11395,7 +11395,7 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -11412,7 +11412,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Portacamp - Dining room, ukuran 20FT</t>
+          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -11421,11 +11421,11 @@
         </is>
       </c>
       <c r="E367" t="n">
-        <v>7500000</v>
+        <v>25000000</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -11442,20 +11442,20 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Portacamp - Kitchen ukuran 40FT</t>
+          <t>Food &amp; beverage, main course</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="E368" t="n">
-        <v>10000000</v>
+        <v>65000</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -11472,20 +11472,20 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
+          <t>Food &amp; beverage, snack coffee/ tea &amp; desert</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="E369" t="n">
-        <v>25000000</v>
+        <v>33000</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -11502,20 +11502,20 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Food &amp; beverage, main course</t>
+          <t>Laundry services</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="E370" t="n">
-        <v>65000</v>
+        <v>25000</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -11527,25 +11527,25 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Food &amp; beverage, snack coffee/ tea &amp; desert</t>
+          <t>Personnel GS in-charge di lokasi pemboran/ wellservices/ workover, personnel in charge</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="E371" t="n">
-        <v>33000</v>
+        <v>750000</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -11557,25 +11557,25 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Laundry services</t>
+          <t>Personnel GS in-charge di lokasi pemboran/ wellservices/ workover, personnel in charge</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="E372" t="n">
-        <v>25000</v>
+        <v>750000</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -11597,7 +11597,7 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="E373" t="n">
@@ -11605,7 +11605,7 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -11622,7 +11622,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Personnel GS in-charge di lokasi pemboran/ wellservices/ workover, personnel in charge</t>
+          <t>Helper Local (non Skilled)</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
@@ -11631,11 +11631,11 @@
         </is>
       </c>
       <c r="E374" t="n">
-        <v>750000</v>
+        <v>250000</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -11652,7 +11652,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Personnel GS in-charge di lokasi pemboran/ wellservices/ workover, personnel in charge</t>
+          <t>Helper Local (Skilled)</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
@@ -11661,11 +11661,11 @@
         </is>
       </c>
       <c r="E375" t="n">
-        <v>750000</v>
+        <v>350000</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -11682,7 +11682,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Helper Local (non Skilled)</t>
+          <t>Security - Local personnel</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
@@ -11691,11 +11691,11 @@
         </is>
       </c>
       <c r="E376" t="n">
-        <v>250000</v>
+        <v>275000</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -11712,7 +11712,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Helper Local (Skilled)</t>
+          <t>Welder (GTAW)</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
@@ -11721,11 +11721,11 @@
         </is>
       </c>
       <c r="E377" t="n">
-        <v>350000</v>
+        <v>500000</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -11742,7 +11742,7 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Security - Local personnel</t>
+          <t>Welder (SMAW)</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
@@ -11751,11 +11751,11 @@
         </is>
       </c>
       <c r="E378" t="n">
-        <v>275000</v>
+        <v>500000</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -11772,7 +11772,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Welder (GTAW)</t>
+          <t>Welder (Non Categories)</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
@@ -11781,11 +11781,11 @@
         </is>
       </c>
       <c r="E379" t="n">
-        <v>500000</v>
+        <v>325000</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -11802,7 +11802,7 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Welder (SMAW)</t>
+          <t>Operator Crane</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
@@ -11811,11 +11811,11 @@
         </is>
       </c>
       <c r="E380" t="n">
-        <v>500000</v>
+        <v>750000</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -11832,7 +11832,7 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Welder (Non Categories)</t>
+          <t>Rigger</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
@@ -11841,11 +11841,11 @@
         </is>
       </c>
       <c r="E381" t="n">
-        <v>325000</v>
+        <v>650000</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -11862,7 +11862,7 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Operator Crane</t>
+          <t>Operator Heavy Equipment (Motor Grader)</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
@@ -11871,11 +11871,11 @@
         </is>
       </c>
       <c r="E382" t="n">
-        <v>750000</v>
+        <v>500000</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -11892,7 +11892,7 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Rigger</t>
+          <t>Operator Heavy Equipment ( Excavator)</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
@@ -11901,11 +11901,11 @@
         </is>
       </c>
       <c r="E383" t="n">
-        <v>650000</v>
+        <v>500000</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -11922,7 +11922,7 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Operator Heavy Equipment (Motor Grader)</t>
+          <t>Operator Heavy Equipment ( Vibro Compactor)</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
@@ -11935,7 +11935,7 @@
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -11952,7 +11952,7 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Operator Heavy Equipment ( Excavator)</t>
+          <t>Operator Heavy Equipment (Fire Jeep)</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
@@ -11965,7 +11965,7 @@
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Operator Heavy Equipment ( Vibro Compactor)</t>
+          <t>Operator Heavy Equipment (Vacuum Truck)</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
@@ -11995,7 +11995,7 @@
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -12012,7 +12012,7 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Operator Heavy Equipment (Fire Jeep)</t>
+          <t>Operator Heavy Equipment (Forklift)</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
@@ -12025,7 +12025,7 @@
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -12042,7 +12042,7 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Operator Heavy Equipment (Vacuum Truck)</t>
+          <t>Mechanic/ Electrician</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
@@ -12051,11 +12051,11 @@
         </is>
       </c>
       <c r="E388" t="n">
-        <v>500000</v>
+        <v>600000</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -12067,25 +12067,25 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>MOVING AIR FREIGHT TRANSPORT</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Operator Heavy Equipment (Forklift)</t>
+          <t>Jabodetabek - Palembang/Lematang atau sebaliknya</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="E389" t="n">
-        <v>500000</v>
+        <v>150000</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -12097,25 +12097,25 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>MOVING AIR FREIGHT TRANSPORT</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Mechanic/ Electrician</t>
+          <t>Jabodetabek - Luwuk/ Senoro atau sebaliknya</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="E390" t="n">
-        <v>600000</v>
+        <v>200000</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -12132,7 +12132,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Jabodetabek - Palembang/Lematang atau sebaliknya</t>
+          <t>Jabodetabek - Balikpapan atau sebaliknya</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
@@ -12141,11 +12141,11 @@
         </is>
       </c>
       <c r="E391" t="n">
-        <v>150000</v>
+        <v>175000</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -12162,7 +12162,7 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Jabodetabek - Luwuk/ Senoro atau sebaliknya</t>
+          <t>Jabodetabek - Batam atau sebaliknya</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
@@ -12171,11 +12171,11 @@
         </is>
       </c>
       <c r="E392" t="n">
-        <v>200000</v>
+        <v>125000</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -12192,7 +12192,7 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Jabodetabek - Balikpapan atau sebaliknya</t>
+          <t>Batam - Luwuk/ Senoro atau sebaliknya</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
@@ -12201,11 +12201,11 @@
         </is>
       </c>
       <c r="E393" t="n">
-        <v>175000</v>
+        <v>150000</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -12222,7 +12222,7 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Jabodetabek - Batam atau sebaliknya</t>
+          <t>Balikpapan - Luwuk/ Senoro atau sebaliknya</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
@@ -12231,11 +12231,11 @@
         </is>
       </c>
       <c r="E394" t="n">
-        <v>125000</v>
+        <v>200000</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -12252,7 +12252,7 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Batam - Luwuk/ Senoro atau sebaliknya</t>
+          <t>Balikpapan - Batam atau sebaliknya</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
@@ -12261,11 +12261,11 @@
         </is>
       </c>
       <c r="E395" t="n">
-        <v>150000</v>
+        <v>200000</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -12282,7 +12282,7 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Balikpapan - Luwuk/ Senoro atau sebaliknya</t>
+          <t>Surabaya - Luwuk/ Senoro atau sebaliknya</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
@@ -12291,11 +12291,11 @@
         </is>
       </c>
       <c r="E396" t="n">
-        <v>200000</v>
+        <v>150000</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -12312,7 +12312,7 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Balikpapan - Batam atau sebaliknya</t>
+          <t>Surabaya - Balikpapan atau sebaliknya</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
@@ -12321,11 +12321,11 @@
         </is>
       </c>
       <c r="E397" t="n">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -12342,7 +12342,7 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Surabaya - Luwuk/ Senoro atau sebaliknya</t>
+          <t>Surabaya - Batam atau sebaliknya</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
@@ -12351,11 +12351,11 @@
         </is>
       </c>
       <c r="E398" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Surabaya - Balikpapan atau sebaliknya</t>
+          <t>Surabaya - Jabodetabek atau sebaliknya</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
@@ -12381,11 +12381,11 @@
         </is>
       </c>
       <c r="E399" t="n">
-        <v>100000</v>
+        <v>125000</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -12402,20 +12402,20 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Surabaya - Batam atau sebaliknya</t>
+          <t>Jasa repacking for Airfreight, estimasi ukuran pallet 100x100x100 cm</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Pallet</t>
         </is>
       </c>
       <c r="E400" t="n">
-        <v>100000</v>
+        <v>250000</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -12427,12 +12427,12 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>MOVING AIR FREIGHT TRANSPORT</t>
+          <t>MOVING SEA FREIGHT TRANSPORT</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Surabaya - Jabodetabek atau sebaliknya</t>
+          <t>Jabodetabek - Palembang/Lematang atau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
@@ -12441,11 +12441,11 @@
         </is>
       </c>
       <c r="E401" t="n">
-        <v>125000</v>
+        <v>20000000</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -12457,25 +12457,25 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>MOVING AIR FREIGHT TRANSPORT</t>
+          <t>MOVING SEA FREIGHT TRANSPORT</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Jasa repacking for Airfreight, estimasi ukuran pallet 100x100x100 cm</t>
+          <t>Jabodetabek - Palembang/Lematang atau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>Pallet</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="E402" t="n">
-        <v>250000</v>
+        <v>20000000</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -12492,20 +12492,20 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Jabodetabek - Palembang/Lematang atau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)</t>
+          <t>Jabodetabek - Luwuk/ Senoro atau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="E403" t="n">
-        <v>20000000</v>
+        <v>50000000</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -12522,7 +12522,7 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Jabodetabek - Palembang/Lematang atau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)</t>
+          <t>Jabodetabek - Balikpapan atau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
@@ -12531,11 +12531,11 @@
         </is>
       </c>
       <c r="E404" t="n">
-        <v>20000000</v>
+        <v>28000000</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -12552,7 +12552,7 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Jabodetabek - Luwuk/ Senoro atau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)</t>
+          <t>Jabodetabek - Batam atau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
@@ -12561,11 +12561,11 @@
         </is>
       </c>
       <c r="E405" t="n">
-        <v>50000000</v>
+        <v>22400000</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -12582,7 +12582,7 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Jabodetabek - Balikpapan atau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)</t>
+          <t>Jabodetabek - Surabaya atau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
@@ -12591,11 +12591,11 @@
         </is>
       </c>
       <c r="E406" t="n">
-        <v>28000000</v>
+        <v>15400000</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -12612,7 +12612,7 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Jabodetabek - Batam atau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)</t>
+          <t>Batam - Luwuk/ Senoro atau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
@@ -12621,11 +12621,11 @@
         </is>
       </c>
       <c r="E407" t="n">
-        <v>22400000</v>
+        <v>32200000</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Jabodetabek - Surabaya atau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)</t>
+          <t>Balikpapan - Luwuk/ Senoro atau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
@@ -12651,11 +12651,11 @@
         </is>
       </c>
       <c r="E408" t="n">
-        <v>15400000</v>
+        <v>29400000</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -12672,7 +12672,7 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Batam - Luwuk/ Senoro atau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)</t>
+          <t>Balikpapan - Batam atau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
@@ -12681,11 +12681,11 @@
         </is>
       </c>
       <c r="E409" t="n">
-        <v>32200000</v>
+        <v>59000000</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -12702,7 +12702,7 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Balikpapan - Luwuk/ Senoro atau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)</t>
+          <t>Surabaya - Luwuk/ Senoro atau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
@@ -12711,11 +12711,11 @@
         </is>
       </c>
       <c r="E410" t="n">
-        <v>29400000</v>
+        <v>22400000</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -12732,7 +12732,7 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Balikpapan - Batam atau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)</t>
+          <t>Surabaya - Balikpapanatau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
@@ -12741,11 +12741,11 @@
         </is>
       </c>
       <c r="E411" t="n">
-        <v>59000000</v>
+        <v>27300000</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -12762,7 +12762,7 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Surabaya - Luwuk/ Senoro atau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)</t>
+          <t>Surabaya - Batam atau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
@@ -12771,11 +12771,11 @@
         </is>
       </c>
       <c r="E412" t="n">
-        <v>22400000</v>
+        <v>27300000</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -12792,20 +12792,20 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Surabaya - Balikpapanatau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)</t>
+          <t>Jasa repacking for Seafreight, estimasi ukuran pallet 100x100x100 cm</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Pallet</t>
         </is>
       </c>
       <c r="E413" t="n">
-        <v>27300000</v>
+        <v>1000000</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -12817,25 +12817,25 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>MOVING SEA FREIGHT TRANSPORT</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Surabaya - Batam atau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)</t>
+          <t>Aqua 600 ml</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="E414" t="n">
-        <v>27300000</v>
+        <v>7500</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -12847,25 +12847,25 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>MOVING SEA FREIGHT TRANSPORT</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Jasa repacking for Seafreight, estimasi ukuran pallet 100x100x100 cm</t>
+          <t>Aqua Galon Segel</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>Pallet</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="E415" t="n">
-        <v>1000000</v>
+        <v>53300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -12882,7 +12882,7 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Aqua 600 ml</t>
+          <t>Indocafe Coffemix Renteng</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
@@ -12891,11 +12891,11 @@
         </is>
       </c>
       <c r="E416" t="n">
-        <v>7500</v>
+        <v>32500</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -12912,7 +12912,7 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Aqua Galon Segel</t>
+          <t>Kopi Kapal Api 380 g</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
@@ -12921,11 +12921,11 @@
         </is>
       </c>
       <c r="E417" t="n">
-        <v>53300</v>
+        <v>84500</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -12942,7 +12942,7 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Indocafe Coffemix Renteng</t>
+          <t>Nescafe Classic renteng</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
@@ -12951,11 +12951,11 @@
         </is>
       </c>
       <c r="E418" t="n">
-        <v>32500</v>
+        <v>26000</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -12972,7 +12972,7 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Kopi Kapal Api 380 g</t>
+          <t>Gulaku</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
@@ -12981,11 +12981,11 @@
         </is>
       </c>
       <c r="E419" t="n">
-        <v>84500</v>
+        <v>32500</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -13002,7 +13002,7 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Nescafe Classic renteng</t>
+          <t>Hand Soap</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
@@ -13011,11 +13011,11 @@
         </is>
       </c>
       <c r="E420" t="n">
-        <v>26000</v>
+        <v>45500</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -13032,7 +13032,7 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Gulaku</t>
+          <t>Pop Mie</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
@@ -13041,11 +13041,11 @@
         </is>
       </c>
       <c r="E421" t="n">
-        <v>32500</v>
+        <v>9750</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -13062,7 +13062,7 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Hand Soap</t>
+          <t>Stella Pengharum Ruangan</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
@@ -13071,11 +13071,11 @@
         </is>
       </c>
       <c r="E422" t="n">
-        <v>45500</v>
+        <v>31200</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -13092,7 +13092,7 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Pop Mie</t>
+          <t>Tisu Kering 200</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
@@ -13101,11 +13101,11 @@
         </is>
       </c>
       <c r="E423" t="n">
-        <v>9750</v>
+        <v>32500</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -13122,7 +13122,7 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Stella Pengharum Ruangan</t>
+          <t>Tisu Basah</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
@@ -13131,11 +13131,11 @@
         </is>
       </c>
       <c r="E424" t="n">
-        <v>31200</v>
+        <v>32500</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -13152,7 +13152,7 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Tisu Kering 200</t>
+          <t>Chitato 68 g</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
@@ -13161,11 +13161,11 @@
         </is>
       </c>
       <c r="E425" t="n">
-        <v>32500</v>
+        <v>19500</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -13182,7 +13182,7 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Tisu Basah</t>
+          <t>Pocari Sweat</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
@@ -13191,11 +13191,11 @@
         </is>
       </c>
       <c r="E426" t="n">
-        <v>32500</v>
+        <v>13000</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -13212,7 +13212,7 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Chitato 68 g</t>
+          <t>Teh Kotak</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
@@ -13221,11 +13221,11 @@
         </is>
       </c>
       <c r="E427" t="n">
-        <v>19500</v>
+        <v>9750</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -13242,7 +13242,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Pocari Sweat</t>
+          <t>Susu Beruang</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
@@ -13251,11 +13251,11 @@
         </is>
       </c>
       <c r="E428" t="n">
-        <v>13000</v>
+        <v>19500</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Teh Kotak</t>
+          <t>Fanta</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
@@ -13285,7 +13285,7 @@
       </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -13302,7 +13302,7 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Susu Beruang</t>
+          <t>Coca Cola</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
@@ -13311,11 +13311,11 @@
         </is>
       </c>
       <c r="E430" t="n">
-        <v>19500</v>
+        <v>9750</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -13332,7 +13332,7 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Fanta</t>
+          <t>Coffe Nescafe Kaleng 220 ml</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
@@ -13341,11 +13341,11 @@
         </is>
       </c>
       <c r="E431" t="n">
-        <v>9750</v>
+        <v>15600</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -13362,7 +13362,7 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Coca Cola</t>
+          <t>Roti Tawar Sari Roti</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
@@ -13371,11 +13371,11 @@
         </is>
       </c>
       <c r="E432" t="n">
-        <v>9750</v>
+        <v>32500</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -13392,7 +13392,7 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Coffe Nescafe Kaleng 220 ml</t>
+          <t>Roti Sari Roti Coklat</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
@@ -13401,11 +13401,11 @@
         </is>
       </c>
       <c r="E433" t="n">
-        <v>15600</v>
+        <v>32500</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -13422,7 +13422,7 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Roti Tawar Sari Roti</t>
+          <t>Roti Sari Roti Keju</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
@@ -13435,7 +13435,7 @@
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -13452,7 +13452,7 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Roti Sari Roti Coklat</t>
+          <t>Kabel NYM 2x2,5 mm @50 mtr</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
@@ -13461,11 +13461,11 @@
         </is>
       </c>
       <c r="E435" t="n">
-        <v>32500</v>
+        <v>1625000</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -13482,7 +13482,7 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Roti Sari Roti Keju</t>
+          <t>Balok Beton ukuran 40x40</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
@@ -13491,11 +13491,11 @@
         </is>
       </c>
       <c r="E436" t="n">
-        <v>32500</v>
+        <v>325000</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -13512,7 +13512,7 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Kabel NYM 2x2,5 mm @50 mtr</t>
+          <t>Pos Sweeper  2x2 meter</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
@@ -13521,11 +13521,11 @@
         </is>
       </c>
       <c r="E437" t="n">
-        <v>1625000</v>
+        <v>19500000</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -13537,12 +13537,12 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>JASA TRANSPORTASI DARI DAN KE BANDARA</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Balok Beton ukuran 40x40</t>
+          <t>Pos Sweeper  2x2 meter</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
@@ -13551,11 +13551,11 @@
         </is>
       </c>
       <c r="E438" t="n">
-        <v>325000</v>
+        <v>19500000</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -13572,20 +13572,20 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Pos Sweeper  2x2 meter</t>
+          <t>Jasa Transportasi dari dan ke Bandara Jasa transportasi menggunakan Pickup Air Port Cengkareng ke Jabodetabek dan sebaliknya</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="E439" t="n">
-        <v>19500000</v>
+        <v>3250000</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -13597,25 +13597,25 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>JASA TRANSPORTASI DARI DAN KE BANDARA</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Pos Sweeper  2x2 meter</t>
+          <t>Jasa Transportasi dari dan ke Bandara Jasa transportasi menggunakan Pickup Air Port Balikpapan ke Kota dan sebaliknya</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="E440" t="n">
-        <v>19500000</v>
+        <v>3900000</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -13632,7 +13632,7 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Jasa Transportasi dari dan ke Bandara Jasa transportasi menggunakan Pickup Air Port Cengkareng ke Jabodetabek dan sebaliknya</t>
+          <t>Jasa Transportasi dari dan ke Bandara Jasa transportasi menggunakan Pickup Air Port Balikpapan ke Kota dan sebaliknya</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
@@ -13641,11 +13641,11 @@
         </is>
       </c>
       <c r="E441" t="n">
-        <v>3250000</v>
+        <v>3900000</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Jasa Transportasi dari dan ke Bandara Jasa transportasi menggunakan Pickup Air Port Balikpapan ke Kota dan sebaliknya</t>
+          <t>Transportasi dari Surabaya ke Jabodetabek: Cold Diesel 4 Meter</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
@@ -13671,11 +13671,11 @@
         </is>
       </c>
       <c r="E442" t="n">
-        <v>3900000</v>
+        <v>5600000</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -13692,7 +13692,7 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Jasa Transportasi dari dan ke Bandara Jasa transportasi menggunakan Pickup Air Port Balikpapan ke Kota dan sebaliknya</t>
+          <t>Transportasi dari Surabaya ke Jabodetabek: Cold Diesel Long 6 Meter</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
@@ -13701,11 +13701,11 @@
         </is>
       </c>
       <c r="E443" t="n">
-        <v>3900000</v>
+        <v>8400000</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -13722,7 +13722,7 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Transportasi dari Surabaya ke Jabodetabek: Cold Diesel 4 Meter</t>
+          <t>Transportasi dari Surabaya ke Jabodetabek: Fuso Bak Max 6 ton</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
@@ -13731,11 +13731,11 @@
         </is>
       </c>
       <c r="E444" t="n">
-        <v>5600000</v>
+        <v>7000000</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -13752,7 +13752,7 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Transportasi dari Surabaya ke Jabodetabek: Cold Diesel Long 6 Meter</t>
+          <t>Transportasi dari Surabaya ke Jabodetabek: Fuso 8 Meter berat Max 10 ton</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
@@ -13761,11 +13761,11 @@
         </is>
       </c>
       <c r="E445" t="n">
-        <v>8400000</v>
+        <v>9100000</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -13782,7 +13782,7 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Transportasi dari Surabaya ke Jabodetabek: Fuso Bak Max 6 ton</t>
+          <t>Transportasi dari Surabaya ke Jabodetabek: Wbox Max 15 ton</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
@@ -13791,11 +13791,11 @@
         </is>
       </c>
       <c r="E446" t="n">
-        <v>7000000</v>
+        <v>10500000</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -13812,7 +13812,7 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Transportasi dari Surabaya ke Jabodetabek: Fuso 8 Meter berat Max 10 ton</t>
+          <t>Transportasi dari Surabaya ke Jabodetabek: Tronton Max 7 Meter Max 14 ton</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
@@ -13821,11 +13821,11 @@
         </is>
       </c>
       <c r="E447" t="n">
-        <v>9100000</v>
+        <v>10500000</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -13842,7 +13842,7 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Transportasi dari Surabaya ke Jabodetabek: Wbox Max 15 ton</t>
+          <t>Transportasi dari Surabaya ke Jabodetabek: Tronton Max 9,5 meter Max 20 ton</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
@@ -13851,11 +13851,11 @@
         </is>
       </c>
       <c r="E448" t="n">
-        <v>10500000</v>
+        <v>14000000</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -13872,7 +13872,7 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Transportasi dari Surabaya ke Jabodetabek: Tronton Max 7 Meter Max 14 ton</t>
+          <t>Transportasi dari Surabaya ke Jabodetabek: Trailler 20 feet</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
@@ -13881,11 +13881,11 @@
         </is>
       </c>
       <c r="E449" t="n">
-        <v>10500000</v>
+        <v>14000000</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -13902,7 +13902,7 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Transportasi dari Surabaya ke Jabodetabek: Tronton Max 9,5 meter Max 20 ton</t>
+          <t>Transportasi dari Surabaya ke Jabodetabek: Trailler 40 feet</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
@@ -13911,11 +13911,11 @@
         </is>
       </c>
       <c r="E450" t="n">
-        <v>14000000</v>
+        <v>25200000</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -13927,25 +13927,25 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>MOVING AIR FREIGHT TRANSPORT</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Transportasi dari Surabaya ke Jabodetabek: Trailler 20 feet</t>
+          <t>Jasa repacking for Airfreight, estimasi ukuran pallet 100x100x100 cm</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>Pallet</t>
         </is>
       </c>
       <c r="E451" t="n">
-        <v>14000000</v>
+        <v>250000</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -13957,25 +13957,25 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Transportasi dari Surabaya ke Jabodetabek: Trailler 40 feet</t>
+          <t>Provisional Sum (At Cost + 15% Fee)</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="E452" t="n">
-        <v>25200000</v>
+        <v>0</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -13987,25 +13987,25 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>MOVING AIR FREIGHT TRANSPORT</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Jasa repacking for Airfreight, estimasi ukuran pallet 100x100x100 cm</t>
+          <t>Aqua 600 ml</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>Pallet</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="E453" t="n">
-        <v>250000</v>
+        <v>7500</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
@@ -14017,85 +14017,25 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Provisional Sum (At Cost + 15% Fee)</t>
+          <t>Aqua 600 ml</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="E454" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
-          <t>2026-09-07 19:17:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="455">
-      <c r="A455" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
-      </c>
-      <c r="B455" t="inlineStr">
-        <is>
-          <t>PENGADAAN MATERIAL</t>
-        </is>
-      </c>
-      <c r="C455" t="inlineStr">
-        <is>
-          <t>Aqua 600 ml</t>
-        </is>
-      </c>
-      <c r="D455" t="inlineStr">
-        <is>
-          <t>Ea</t>
-        </is>
-      </c>
-      <c r="E455" t="n">
-        <v>7500</v>
-      </c>
-      <c r="F455" t="inlineStr">
-        <is>
-          <t>2026-09-07 19:17:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="456">
-      <c r="A456" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
-      </c>
-      <c r="B456" t="inlineStr">
-        <is>
-          <t>ESTIMATED SUM</t>
-        </is>
-      </c>
-      <c r="C456" t="inlineStr">
-        <is>
-          <t>Aqua 600 ml</t>
-        </is>
-      </c>
-      <c r="D456" t="inlineStr">
-        <is>
-          <t>Ea</t>
-        </is>
-      </c>
-      <c r="E456" t="n">
-        <v>7500</v>
-      </c>
-      <c r="F456" t="inlineStr">
-        <is>
-          <t>2026-09-07 19:17:47</t>
+          <t>2026-09-10 11:51:00</t>
         </is>
       </c>
     </row>
